--- a/apresentacoes/Devolucoes_Vale_tratada.xlsx
+++ b/apresentacoes/Devolucoes_Vale_tratada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ160"/>
+  <dimension ref="A1:AJ157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,8 +748,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ2" t="b">
-        <v>0</v>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -898,8 +900,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ3" t="b">
-        <v>0</v>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -1048,8 +1052,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ4" t="b">
-        <v>1</v>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -1198,8 +1204,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ5" t="b">
-        <v>1</v>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -1348,8 +1356,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ6" t="b">
-        <v>0</v>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1498,8 +1508,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ7" t="b">
-        <v>1</v>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1648,8 +1660,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ8" t="b">
-        <v>1</v>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1798,8 +1812,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ9" t="b">
-        <v>0</v>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1948,8 +1964,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ10" t="b">
-        <v>0</v>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -2098,8 +2116,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ11" t="b">
-        <v>0</v>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -2248,8 +2268,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ12" t="b">
-        <v>1</v>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -2398,8 +2420,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ13" t="b">
-        <v>1</v>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -2548,8 +2572,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ14" t="b">
-        <v>0</v>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -2699,8 +2725,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ15" t="b">
-        <v>0</v>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -2850,8 +2878,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ16" t="b">
-        <v>0</v>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -3001,8 +3031,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ17" t="b">
-        <v>0</v>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -3152,8 +3184,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ18" t="b">
-        <v>0</v>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -3303,8 +3337,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ19" t="b">
-        <v>0</v>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -3454,8 +3490,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ20" t="b">
-        <v>0</v>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -3605,8 +3643,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ21" t="b">
-        <v>1</v>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -3756,8 +3796,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ22" t="b">
-        <v>1</v>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -3907,8 +3949,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ23" t="b">
-        <v>1</v>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -4056,8 +4100,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ24" t="b">
-        <v>1</v>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -4205,8 +4251,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ25" t="b">
-        <v>1</v>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -4356,8 +4404,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ26" t="b">
-        <v>1</v>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -4507,8 +4557,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ27" t="b">
-        <v>1</v>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -4658,8 +4710,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ28" t="b">
-        <v>1</v>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -4811,8 +4865,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ29" t="b">
-        <v>0</v>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -4962,8 +5018,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ30" t="b">
-        <v>1</v>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -5113,8 +5171,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ31" t="b">
-        <v>0</v>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -5262,8 +5322,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ32" t="b">
-        <v>0</v>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -5413,8 +5475,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ33" t="b">
-        <v>1</v>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -5564,8 +5628,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ34" t="b">
-        <v>0</v>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -5713,8 +5779,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ35" t="b">
-        <v>0</v>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -5862,8 +5930,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ36" t="b">
-        <v>0</v>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -6011,8 +6081,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ37" t="b">
-        <v>0</v>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -6162,8 +6234,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ38" t="b">
-        <v>1</v>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -6313,8 +6387,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ39" t="b">
-        <v>0</v>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -6464,8 +6540,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ40" t="b">
-        <v>0</v>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -6615,8 +6693,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ41" t="b">
-        <v>1</v>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -6766,8 +6846,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ42" t="b">
-        <v>0</v>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -6915,8 +6997,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ43" t="b">
-        <v>0</v>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -7064,8 +7148,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ44" t="b">
-        <v>0</v>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -7215,8 +7301,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ45" t="b">
-        <v>0</v>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -7364,8 +7452,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ46" t="b">
-        <v>0</v>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -7515,8 +7605,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ47" t="b">
-        <v>0</v>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -7666,8 +7758,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ48" t="b">
-        <v>0</v>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -7817,8 +7911,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ49" t="b">
-        <v>0</v>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -7966,8 +8062,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ50" t="b">
-        <v>0</v>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -8115,8 +8213,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ51" t="b">
-        <v>0</v>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -8266,8 +8366,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ52" t="b">
-        <v>0</v>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -8415,8 +8517,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ53" t="b">
-        <v>0</v>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -8566,8 +8670,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ54" t="b">
-        <v>0</v>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -8717,8 +8823,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ55" t="b">
-        <v>0</v>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -8866,8 +8974,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ56" t="b">
-        <v>0</v>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -9017,8 +9127,10 @@
           <t>UNENTEL SOLUCOES TECNOLOGICAS LTDA</t>
         </is>
       </c>
-      <c r="AJ57" t="b">
-        <v>0</v>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -9169,8 +9281,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ58" t="b">
-        <v>0</v>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -9291,8 +9405,10 @@
       </c>
       <c r="AH59" t="inlineStr"/>
       <c r="AI59" t="inlineStr"/>
-      <c r="AJ59" t="b">
-        <v>0</v>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -9441,8 +9557,10 @@
           <t>UNENTEL SOLUCOES TECNOLOGICAS LTDA</t>
         </is>
       </c>
-      <c r="AJ60" t="b">
-        <v>0</v>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -9592,8 +9710,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ61" t="b">
-        <v>0</v>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -9738,8 +9858,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ62" t="b">
-        <v>0</v>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -9885,8 +10007,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ63" t="b">
-        <v>0</v>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -10036,8 +10160,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ64" t="b">
-        <v>0</v>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -10187,8 +10313,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ65" t="b">
-        <v>0</v>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -10338,8 +10466,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ66" t="b">
-        <v>1</v>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -10487,8 +10617,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ67" t="b">
-        <v>1</v>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -10638,8 +10770,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ68" t="b">
-        <v>0</v>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -10789,8 +10923,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ69" t="b">
-        <v>0</v>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -10940,8 +11076,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ70" t="b">
-        <v>0</v>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -11091,8 +11229,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ71" t="b">
-        <v>0</v>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -11243,8 +11383,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ72" t="b">
-        <v>0</v>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -11394,8 +11536,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ73" t="b">
-        <v>0</v>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -11545,8 +11689,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ74" t="b">
-        <v>0</v>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -11696,8 +11842,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ75" t="b">
-        <v>1</v>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -11847,8 +11995,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ76" t="b">
-        <v>1</v>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -11998,8 +12148,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ77" t="b">
-        <v>0</v>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -12149,8 +12301,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ78" t="b">
-        <v>0</v>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -12300,8 +12454,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ79" t="b">
-        <v>0</v>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -12451,8 +12607,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ80" t="b">
-        <v>0</v>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -12604,8 +12762,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ81" t="b">
-        <v>0</v>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -12755,8 +12915,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ82" t="b">
-        <v>0</v>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -12906,8 +13068,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ83" t="b">
-        <v>0</v>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="84">
@@ -13057,8 +13221,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ84" t="b">
-        <v>1</v>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -13208,8 +13374,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ85" t="b">
-        <v>0</v>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -13359,8 +13527,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ86" t="b">
-        <v>1</v>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -13510,8 +13680,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ87" t="b">
-        <v>1</v>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -13660,8 +13832,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ88" t="b">
-        <v>0</v>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -13811,8 +13985,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ89" t="b">
-        <v>0</v>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -13962,8 +14138,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ90" t="b">
-        <v>1</v>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -14113,8 +14291,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ91" t="b">
-        <v>0</v>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -14264,8 +14444,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ92" t="b">
-        <v>1</v>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
       </c>
     </row>
     <row r="93">
@@ -14415,8 +14597,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ93" t="b">
-        <v>1</v>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
       </c>
     </row>
     <row r="94">
@@ -14566,8 +14750,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ94" t="b">
-        <v>0</v>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -14717,8 +14903,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ95" t="b">
-        <v>0</v>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -14868,8 +15056,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ96" t="b">
-        <v>0</v>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="97">
@@ -15018,8 +15208,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ97" t="b">
-        <v>0</v>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -15168,8 +15360,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ98" t="b">
-        <v>0</v>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="99">
@@ -15318,8 +15512,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ99" t="b">
-        <v>0</v>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="100">
@@ -15468,8 +15664,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ100" t="b">
-        <v>0</v>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -15618,8 +15816,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ101" t="b">
-        <v>0</v>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -15766,8 +15966,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ102" t="b">
-        <v>0</v>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="103">
@@ -15916,8 +16118,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ103" t="b">
-        <v>0</v>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -16064,8 +16268,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ104" t="b">
-        <v>0</v>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="105">
@@ -16214,8 +16420,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ105" t="b">
-        <v>0</v>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="106">
@@ -16364,8 +16572,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ106" t="b">
-        <v>0</v>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -16514,8 +16724,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ107" t="b">
-        <v>0</v>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="108">
@@ -16665,8 +16877,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ108" t="b">
-        <v>0</v>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="109">
@@ -16785,8 +16999,10 @@
       </c>
       <c r="AH109" t="inlineStr"/>
       <c r="AI109" t="inlineStr"/>
-      <c r="AJ109" t="b">
-        <v>0</v>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="110">
@@ -16932,8 +17148,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ110" t="b">
-        <v>0</v>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="111">
@@ -17078,8 +17296,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ111" t="b">
-        <v>0</v>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="112">
@@ -17201,8 +17421,10 @@
       </c>
       <c r="AH112" t="inlineStr"/>
       <c r="AI112" t="inlineStr"/>
-      <c r="AJ112" t="b">
-        <v>0</v>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -17351,8 +17573,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ113" t="b">
-        <v>0</v>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="114">
@@ -17496,8 +17720,10 @@
           <t>TRANSPORTES DELLA VOLPE S A COMERCI</t>
         </is>
       </c>
-      <c r="AJ114" t="b">
-        <v>0</v>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="115">
@@ -17646,8 +17872,10 @@
           <t>ROLATEL COM DE ROLAMENTOS LT</t>
         </is>
       </c>
-      <c r="AJ115" t="b">
-        <v>0</v>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -17796,8 +18024,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ116" t="b">
-        <v>0</v>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="117">
@@ -17946,8 +18176,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ117" t="b">
-        <v>0</v>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="118">
@@ -18096,8 +18328,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ118" t="b">
-        <v>0</v>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -18246,8 +18480,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ119" t="b">
-        <v>0</v>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="120">
@@ -18396,8 +18632,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ120" t="b">
-        <v>0</v>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="121">
@@ -18546,8 +18784,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ121" t="b">
-        <v>0</v>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="122">
@@ -18696,8 +18936,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ122" t="b">
-        <v>0</v>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="123">
@@ -18844,8 +19086,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ123" t="b">
-        <v>0</v>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="124">
@@ -18994,8 +19238,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ124" t="b">
-        <v>0</v>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="125">
@@ -19114,8 +19360,10 @@
       </c>
       <c r="AH125" t="inlineStr"/>
       <c r="AI125" t="inlineStr"/>
-      <c r="AJ125" t="b">
-        <v>0</v>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="126">
@@ -19256,8 +19504,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ126" t="b">
-        <v>0</v>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="127">
@@ -19398,8 +19648,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ127" t="b">
-        <v>0</v>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -19540,8 +19792,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ128" t="b">
-        <v>0</v>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="129">
@@ -19686,8 +19940,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ129" t="b">
-        <v>0</v>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="130">
@@ -19832,8 +20088,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ130" t="b">
-        <v>0</v>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="131">
@@ -19978,8 +20236,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ131" t="b">
-        <v>0</v>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="132">
@@ -20124,8 +20384,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ132" t="b">
-        <v>0</v>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="133">
@@ -20270,8 +20532,10 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ133" t="b">
-        <v>0</v>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="134">
@@ -20390,8 +20654,10 @@
       </c>
       <c r="AH134" t="inlineStr"/>
       <c r="AI134" t="inlineStr"/>
-      <c r="AJ134" t="b">
-        <v>0</v>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="135">
@@ -20510,8 +20776,10 @@
       </c>
       <c r="AH135" t="inlineStr"/>
       <c r="AI135" t="inlineStr"/>
-      <c r="AJ135" t="b">
-        <v>0</v>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="136">
@@ -20630,8 +20898,10 @@
       </c>
       <c r="AH136" t="inlineStr"/>
       <c r="AI136" t="inlineStr"/>
-      <c r="AJ136" t="b">
-        <v>0</v>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="137">
@@ -20750,18 +21020,20 @@
       </c>
       <c r="AH137" t="inlineStr"/>
       <c r="AI137" t="inlineStr"/>
-      <c r="AJ137" t="b">
-        <v>0</v>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>40931</t>
+          <t>40934</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>1370818</v>
+        <v>1345715</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -20774,7 +21046,7 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2750680</v>
+        <v>19880</v>
       </c>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
@@ -20799,7 +21071,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>35260557582793000111550010027506801600929056</t>
+          <t>35260504483719000181550010000198801014347341</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -20808,9 +21080,7 @@
         </is>
       </c>
       <c r="M138" t="inlineStr"/>
-      <c r="N138" t="n">
-        <v>4512827951</v>
-      </c>
+      <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr">
         <is>
           <t>PARAUAPEBAS</t>
@@ -20822,12 +21092,12 @@
       <c r="Q138" t="inlineStr"/>
       <c r="R138" t="inlineStr">
         <is>
-          <t>FESTO  BRASIL LTDA</t>
+          <t>TRILHOS FERROVIARIOS LTDA</t>
         </is>
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>Unid.val.bloq. BR_CS.2238743 LINHA 10 BR</t>
+          <t>TRILHOS</t>
         </is>
       </c>
       <c r="T138" t="inlineStr">
@@ -20836,13 +21106,13 @@
         </is>
       </c>
       <c r="U138" t="n">
-        <v>300292000</v>
+        <v>300286000</v>
       </c>
       <c r="V138" t="n">
-        <v>6000177987</v>
+        <v>6000176656</v>
       </c>
       <c r="W138" s="1" t="n">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="X138" t="inlineStr">
         <is>
@@ -20850,7 +21120,7 @@
         </is>
       </c>
       <c r="Y138" t="n">
-        <v>14274.96</v>
+        <v>6584.94</v>
       </c>
       <c r="Z138" t="inlineStr">
         <is>
@@ -20867,12 +21137,12 @@
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="AD138" t="inlineStr">
         <is>
-          <t>SEM CADASTRO.</t>
+          <t>DELVOVER AO FORNECEDOR, SEM ESPACO NO ARMAZEM. CLIENTE N?O RESPONDE.</t>
         </is>
       </c>
       <c r="AE138" t="inlineStr">
@@ -20900,18 +21170,20 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ138" t="b">
-        <v>0</v>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>40932</t>
+          <t>40935</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1370767</v>
+        <v>1373906</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -20924,7 +21196,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2750344</v>
+        <v>832161</v>
       </c>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
@@ -20949,7 +21221,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>35260557582793000111550010027503441916055185</t>
+          <t>35260657599581000147550100008321611745969714</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -20959,7 +21231,7 @@
       </c>
       <c r="M139" t="inlineStr"/>
       <c r="N139" t="n">
-        <v>4513016302</v>
+        <v>4513157676</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
@@ -20972,12 +21244,12 @@
       <c r="Q139" t="inlineStr"/>
       <c r="R139" t="inlineStr">
         <is>
-          <t>FESTO  BRASIL LTDA</t>
+          <t>A.R.S. - INDUSTRIA E COMERCIO DE PA</t>
         </is>
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>ATUAD.SEMI-ROT DFPD-160-RP-90-RS60-F07e</t>
+          <t>PORCA SEXT M 16X2 CH 24 ZB-(4513157676)-</t>
         </is>
       </c>
       <c r="T139" t="inlineStr">
@@ -20986,7 +21258,7 @@
         </is>
       </c>
       <c r="U139" t="n">
-        <v>300290000</v>
+        <v>300292000</v>
       </c>
       <c r="V139" t="n">
         <v>6000177987</v>
@@ -21000,7 +21272,7 @@
         </is>
       </c>
       <c r="Y139" t="n">
-        <v>3111.84</v>
+        <v>2.09</v>
       </c>
       <c r="Z139" t="inlineStr">
         <is>
@@ -21050,18 +21322,20 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ139" t="b">
-        <v>0</v>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>40933</t>
+          <t>40936</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1370847</v>
+        <v>1373876</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -21074,7 +21348,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2750986</v>
+        <v>832157</v>
       </c>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
@@ -21099,7 +21373,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>35260557582793000111550010027509861602346481</t>
+          <t>35260657599581000147550100008321571940142103</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -21109,7 +21383,7 @@
       </c>
       <c r="M140" t="inlineStr"/>
       <c r="N140" t="n">
-        <v>4513156749</v>
+        <v>4513156502</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
@@ -21122,12 +21396,12 @@
       <c r="Q140" t="inlineStr"/>
       <c r="R140" t="inlineStr">
         <is>
-          <t>FESTO  BRASIL LTDA</t>
+          <t>A.R.S. - INDUSTRIA E COMERCIO DE PA</t>
         </is>
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>TUBO FLEXIVEL PUN-10X1,5-BL LINHA 10</t>
+          <t>PA MAQ LENT 1/4-20X3/4 BC-(4513156502)-(</t>
         </is>
       </c>
       <c r="T140" t="inlineStr">
@@ -21150,7 +21424,7 @@
         </is>
       </c>
       <c r="Y140" t="n">
-        <v>1243.29</v>
+        <v>4.69</v>
       </c>
       <c r="Z140" t="inlineStr">
         <is>
@@ -21200,18 +21474,20 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ140" t="b">
-        <v>0</v>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>40934</t>
+          <t>40937</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1345715</v>
+        <v>1373877</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -21224,7 +21500,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>19880</v>
+        <v>832439</v>
       </c>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
@@ -21249,7 +21525,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>35260504483719000181550010000198801014347341</t>
+          <t>35260657599581000147550100008324391399034843</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -21258,7 +21534,9 @@
         </is>
       </c>
       <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
+      <c r="N141" t="n">
+        <v>4513184897</v>
+      </c>
       <c r="O141" t="inlineStr">
         <is>
           <t>PARAUAPEBAS</t>
@@ -21270,12 +21548,12 @@
       <c r="Q141" t="inlineStr"/>
       <c r="R141" t="inlineStr">
         <is>
-          <t>TRILHOS FERROVIARIOS LTDA</t>
+          <t>A.R.S. - INDUSTRIA E COMERCIO DE PA</t>
         </is>
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>TRILHOS</t>
+          <t>PORCA SEXT G.8 3/8-16-(4513184897)-(10)</t>
         </is>
       </c>
       <c r="T141" t="inlineStr">
@@ -21284,13 +21562,13 @@
         </is>
       </c>
       <c r="U141" t="n">
-        <v>300286000</v>
+        <v>300292000</v>
       </c>
       <c r="V141" t="n">
-        <v>6000176656</v>
+        <v>6000177987</v>
       </c>
       <c r="W141" s="1" t="n">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="X141" t="inlineStr">
         <is>
@@ -21298,7 +21576,7 @@
         </is>
       </c>
       <c r="Y141" t="n">
-        <v>6584.94</v>
+        <v>29.82</v>
       </c>
       <c r="Z141" t="inlineStr">
         <is>
@@ -21315,12 +21593,12 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>.</t>
         </is>
       </c>
       <c r="AD141" t="inlineStr">
         <is>
-          <t>DELVOVER AO FORNECEDOR, SEM ESPACO NO ARMAZEM. CLIENTE N?O RESPONDE.</t>
+          <t>SEM CADASTRO.</t>
         </is>
       </c>
       <c r="AE141" t="inlineStr">
@@ -21348,18 +21626,20 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ141" t="b">
-        <v>0</v>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>40935</t>
+          <t>40938</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>1373906</v>
+        <v>1373725</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -21372,7 +21652,7 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>832161</v>
+        <v>832250</v>
       </c>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
@@ -21397,7 +21677,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>35260657599581000147550100008321611745969714</t>
+          <t>35260657599581000147550100008322501737668575</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -21407,7 +21687,7 @@
       </c>
       <c r="M142" t="inlineStr"/>
       <c r="N142" t="n">
-        <v>4513157676</v>
+        <v>4513169468</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
@@ -21425,7 +21705,7 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>PORCA SEXT M 16X2 CH 24 ZB-(4513157676)-</t>
+          <t>PA SEXT G.8 5/8-11X1.1/2  RI-(4513169468</t>
         </is>
       </c>
       <c r="T142" t="inlineStr">
@@ -21448,7 +21728,7 @@
         </is>
       </c>
       <c r="Y142" t="n">
-        <v>2.09</v>
+        <v>527.1799999999999</v>
       </c>
       <c r="Z142" t="inlineStr">
         <is>
@@ -21498,18 +21778,20 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ142" t="b">
-        <v>0</v>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>40936</t>
+          <t>40939</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1373876</v>
+        <v>1373833</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -21522,7 +21804,7 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>832157</v>
+        <v>832328</v>
       </c>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
@@ -21547,7 +21829,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>35260657599581000147550100008321571940142103</t>
+          <t>35260657599581000147550100008323281853076349</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -21557,7 +21839,7 @@
       </c>
       <c r="M143" t="inlineStr"/>
       <c r="N143" t="n">
-        <v>4513156502</v>
+        <v>4513176053</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
@@ -21575,7 +21857,7 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>PA MAQ LENT 1/4-20X3/4 BC-(4513156502)-(</t>
+          <t>PORCA SEXT G.5 1/2-13 CH 3/4-(4513176053</t>
         </is>
       </c>
       <c r="T143" t="inlineStr">
@@ -21598,7 +21880,7 @@
         </is>
       </c>
       <c r="Y143" t="n">
-        <v>4.69</v>
+        <v>22.15</v>
       </c>
       <c r="Z143" t="inlineStr">
         <is>
@@ -21648,18 +21930,20 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ143" t="b">
-        <v>0</v>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>40937</t>
+          <t>40940</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>1373877</v>
+        <v>1373872</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -21672,7 +21956,7 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>832439</v>
+        <v>832297</v>
       </c>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
@@ -21697,7 +21981,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>35260657599581000147550100008324391399034843</t>
+          <t>35260657599581000147550100008322971181221624</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -21707,7 +21991,7 @@
       </c>
       <c r="M144" t="inlineStr"/>
       <c r="N144" t="n">
-        <v>4513184897</v>
+        <v>4513176054</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
@@ -21725,7 +22009,7 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>PORCA SEXT G.8 3/8-16-(4513184897)-(10)</t>
+          <t>PA SX G.5 1/2-13X1.1/2 RI ZB-(4513176054</t>
         </is>
       </c>
       <c r="T144" t="inlineStr">
@@ -21748,7 +22032,7 @@
         </is>
       </c>
       <c r="Y144" t="n">
-        <v>29.82</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="Z144" t="inlineStr">
         <is>
@@ -21798,18 +22082,20 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ144" t="b">
-        <v>0</v>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>40938</t>
+          <t>40941</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>1373725</v>
+        <v>1373907</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -21822,7 +22108,7 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>832250</v>
+        <v>832187</v>
       </c>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
@@ -21847,7 +22133,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>35260657599581000147550100008322501737668575</t>
+          <t>35260657599581000147550100008321871884435103</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -21857,7 +22143,7 @@
       </c>
       <c r="M145" t="inlineStr"/>
       <c r="N145" t="n">
-        <v>4513169468</v>
+        <v>4513160425</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
@@ -21875,7 +22161,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>PA SEXT G.8 5/8-11X1.1/2  RI-(4513169468</t>
+          <t>ARRUELA LISA DE ACO DIN 125 A M 18-(4513</t>
         </is>
       </c>
       <c r="T145" t="inlineStr">
@@ -21898,7 +22184,7 @@
         </is>
       </c>
       <c r="Y145" t="n">
-        <v>527.1799999999999</v>
+        <v>11.72</v>
       </c>
       <c r="Z145" t="inlineStr">
         <is>
@@ -21948,38 +22234,30 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ145" t="b">
-        <v>0</v>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>40939</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>1373833</v>
-      </c>
+          <t>40942</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>TDV São Paulo - SP</t>
-        </is>
-      </c>
+      <c r="D146" t="inlineStr"/>
       <c r="E146" t="n">
-        <v>832328</v>
+        <v>19878</v>
       </c>
       <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>FRACIONADO</t>
-        </is>
-      </c>
+      <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -21997,7 +22275,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>35260657599581000147550100008323281853076349</t>
+          <t>41260611340390000165550040000198781801155209</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -22006,9 +22284,7 @@
         </is>
       </c>
       <c r="M146" t="inlineStr"/>
-      <c r="N146" t="n">
-        <v>4513176053</v>
-      </c>
+      <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr">
         <is>
           <t>PARAUAPEBAS</t>
@@ -22020,35 +22296,25 @@
       <c r="Q146" t="inlineStr"/>
       <c r="R146" t="inlineStr">
         <is>
-          <t>A.R.S. - INDUSTRIA E COMERCIO DE PA</t>
-        </is>
-      </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>PORCA SEXT G.5 1/2-13 CH 3/4-(4513176053</t>
-        </is>
-      </c>
+          <t>ECOFIBRA INDUSTRIA E COMERCIO DE CO</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr"/>
       <c r="T146" t="inlineStr">
         <is>
           <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
-      <c r="U146" t="n">
-        <v>300292000</v>
-      </c>
-      <c r="V146" t="n">
-        <v>6000177987</v>
-      </c>
-      <c r="W146" s="1" t="n">
-        <v>46184</v>
-      </c>
+      <c r="U146" t="inlineStr"/>
+      <c r="V146" t="inlineStr"/>
+      <c r="W146" t="inlineStr"/>
       <c r="X146" t="inlineStr">
         <is>
           <t>jsconceica</t>
         </is>
       </c>
       <c r="Y146" t="n">
-        <v>22.15</v>
+        <v>9584.99</v>
       </c>
       <c r="Z146" t="inlineStr">
         <is>
@@ -22065,12 +22331,12 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="AD146" t="inlineStr">
         <is>
-          <t>SEM CADASTRO.</t>
+          <t>DESTINO DIVERGENTE</t>
         </is>
       </c>
       <c r="AE146" t="inlineStr">
@@ -22088,48 +22354,32 @@
           <t>PARAUAPEBAS</t>
         </is>
       </c>
-      <c r="AH146" t="inlineStr">
-        <is>
-          <t>VALE S.A.</t>
-        </is>
-      </c>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>VALE SA</t>
-        </is>
-      </c>
-      <c r="AJ146" t="b">
-        <v>0</v>
+      <c r="AH146" t="inlineStr"/>
+      <c r="AI146" t="inlineStr"/>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>40940</t>
-        </is>
-      </c>
-      <c r="B147" t="n">
-        <v>1373872</v>
-      </c>
+          <t>40945</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>TDV São Paulo - SP</t>
-        </is>
-      </c>
+      <c r="D147" t="inlineStr"/>
       <c r="E147" t="n">
-        <v>832297</v>
+        <v>241473</v>
       </c>
       <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>FRACIONADO</t>
-        </is>
-      </c>
+      <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -22147,7 +22397,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>35260657599581000147550100008322971181221624</t>
+          <t>31260629799921000490550000002414731266548790</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -22156,49 +22406,37 @@
         </is>
       </c>
       <c r="M147" t="inlineStr"/>
-      <c r="N147" t="n">
-        <v>4513176054</v>
-      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr">
         <is>
           <t>PARAUAPEBAS</t>
         </is>
       </c>
       <c r="P147" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="Q147" t="inlineStr"/>
       <c r="R147" t="inlineStr">
         <is>
-          <t>A.R.S. - INDUSTRIA E COMERCIO DE PA</t>
-        </is>
-      </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>PA SX G.5 1/2-13X1.1/2 RI ZB-(4513176054</t>
-        </is>
-      </c>
+          <t>ESAB IND E COM LTDA</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr"/>
       <c r="T147" t="inlineStr">
         <is>
           <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
-      <c r="U147" t="n">
-        <v>300292000</v>
-      </c>
-      <c r="V147" t="n">
-        <v>6000177987</v>
-      </c>
-      <c r="W147" s="1" t="n">
-        <v>46184</v>
-      </c>
+      <c r="U147" t="inlineStr"/>
+      <c r="V147" t="inlineStr"/>
+      <c r="W147" t="inlineStr"/>
       <c r="X147" t="inlineStr">
         <is>
           <t>jsconceica</t>
         </is>
       </c>
       <c r="Y147" t="n">
-        <v>76.68000000000001</v>
+        <v>267397.26</v>
       </c>
       <c r="Z147" t="inlineStr">
         <is>
@@ -22211,16 +22449,16 @@
         </is>
       </c>
       <c r="AB147" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="AD147" t="inlineStr">
         <is>
-          <t>SEM CADASTRO.</t>
+          <t>RECUSADO DEVIDO A DATA REMESSA SER FUTURA E SEM ALINHAMENTO DA VALE</t>
         </is>
       </c>
       <c r="AE147" t="inlineStr">
@@ -22238,48 +22476,32 @@
           <t>PARAUAPEBAS</t>
         </is>
       </c>
-      <c r="AH147" t="inlineStr">
-        <is>
-          <t>VALE S.A.</t>
-        </is>
-      </c>
-      <c r="AI147" t="inlineStr">
-        <is>
-          <t>VALE SA</t>
-        </is>
-      </c>
-      <c r="AJ147" t="b">
-        <v>0</v>
+      <c r="AH147" t="inlineStr"/>
+      <c r="AI147" t="inlineStr"/>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>40941</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>1373907</v>
-      </c>
+          <t>40946</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>TDV São Paulo - SP</t>
-        </is>
-      </c>
+      <c r="D148" t="inlineStr"/>
       <c r="E148" t="n">
-        <v>832187</v>
+        <v>241562</v>
       </c>
       <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>FRACIONADO</t>
-        </is>
-      </c>
+      <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -22297,7 +22519,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>35260657599581000147550100008321871884435103</t>
+          <t>31260629799921000490550000002415621553848879</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -22306,49 +22528,37 @@
         </is>
       </c>
       <c r="M148" t="inlineStr"/>
-      <c r="N148" t="n">
-        <v>4513160425</v>
-      </c>
+      <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr">
         <is>
           <t>PARAUAPEBAS</t>
         </is>
       </c>
       <c r="P148" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="Q148" t="inlineStr"/>
       <c r="R148" t="inlineStr">
         <is>
-          <t>A.R.S. - INDUSTRIA E COMERCIO DE PA</t>
-        </is>
-      </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>ARRUELA LISA DE ACO DIN 125 A M 18-(4513</t>
-        </is>
-      </c>
+          <t>ESAB IND E COM LTDA</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr"/>
       <c r="T148" t="inlineStr">
         <is>
           <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
-      <c r="U148" t="n">
-        <v>300292000</v>
-      </c>
-      <c r="V148" t="n">
-        <v>6000177987</v>
-      </c>
-      <c r="W148" s="1" t="n">
-        <v>46184</v>
-      </c>
+      <c r="U148" t="inlineStr"/>
+      <c r="V148" t="inlineStr"/>
+      <c r="W148" t="inlineStr"/>
       <c r="X148" t="inlineStr">
         <is>
           <t>jsconceica</t>
         </is>
       </c>
       <c r="Y148" t="n">
-        <v>11.72</v>
+        <v>178264.84</v>
       </c>
       <c r="Z148" t="inlineStr">
         <is>
@@ -22361,16 +22571,16 @@
         </is>
       </c>
       <c r="AB148" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="AD148" t="inlineStr">
         <is>
-          <t>SEM CADASTRO.</t>
+          <t>RECUSADO DEVIDO A DATA REMESSA SER FUTURA E SEM ALINHAMENTO DA VALE</t>
         </is>
       </c>
       <c r="AE148" t="inlineStr">
@@ -22388,24 +22598,18 @@
           <t>PARAUAPEBAS</t>
         </is>
       </c>
-      <c r="AH148" t="inlineStr">
-        <is>
-          <t>VALE S.A.</t>
-        </is>
-      </c>
-      <c r="AI148" t="inlineStr">
-        <is>
-          <t>VALE SA</t>
-        </is>
-      </c>
-      <c r="AJ148" t="b">
-        <v>0</v>
+      <c r="AH148" t="inlineStr"/>
+      <c r="AI148" t="inlineStr"/>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>40942</t>
+          <t>40977</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -22416,7 +22620,7 @@
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="n">
-        <v>19878</v>
+        <v>857543</v>
       </c>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr"/>
@@ -22437,7 +22641,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>41260611340390000165550040000198781801155209</t>
+          <t>35260600536772003249550010008575431753933138</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -22453,18 +22657,18 @@
         </is>
       </c>
       <c r="P149" s="1" t="n">
-        <v>46212</v>
+        <v>46217</v>
       </c>
       <c r="Q149" t="inlineStr"/>
       <c r="R149" t="inlineStr">
         <is>
-          <t>ECOFIBRA INDUSTRIA E COMERCIO DE CO</t>
+          <t>ECOLAB QUIMICA LTDA</t>
         </is>
       </c>
       <c r="S149" t="inlineStr"/>
       <c r="T149" t="inlineStr">
         <is>
-          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
+          <t>DEVOLUCAO INDEVIDA</t>
         </is>
       </c>
       <c r="U149" t="inlineStr"/>
@@ -22472,11 +22676,11 @@
       <c r="W149" t="inlineStr"/>
       <c r="X149" t="inlineStr">
         <is>
-          <t>jsconceica</t>
+          <t>erisoares</t>
         </is>
       </c>
       <c r="Y149" t="n">
-        <v>9584.99</v>
+        <v>215462.1</v>
       </c>
       <c r="Z149" t="inlineStr">
         <is>
@@ -22489,16 +22693,16 @@
         </is>
       </c>
       <c r="AB149" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="AD149" t="inlineStr">
         <is>
-          <t>DESTINO DIVERGENTE</t>
+          <t>MATERIAL DEVOLVIDO DEVIDO O CLIENTE ESTA SEM EQUIPAMENTO PRA DESCARREGAR, FAZER ALINHAMENTO COM CLIENTE E AREA.</t>
         </is>
       </c>
       <c r="AE149" t="inlineStr">
@@ -22508,7 +22712,7 @@
       </c>
       <c r="AF149" t="inlineStr">
         <is>
-          <t>9 - 12 Dias</t>
+          <t>0 - 8 Dias</t>
         </is>
       </c>
       <c r="AG149" t="inlineStr">
@@ -22518,28 +22722,40 @@
       </c>
       <c r="AH149" t="inlineStr"/>
       <c r="AI149" t="inlineStr"/>
-      <c r="AJ149" t="b">
-        <v>0</v>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>40945</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr"/>
+          <t>40219</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>1194154</v>
+      </c>
       <c r="C150" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>TDV Contagem MG</t>
+        </is>
+      </c>
       <c r="E150" t="n">
-        <v>241473</v>
+        <v>2593</v>
       </c>
       <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>FRACIONADO</t>
+        </is>
+      </c>
       <c r="H150" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -22547,17 +22763,17 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Parauapebas - PA</t>
+          <t>São Luíz - MA</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>PARAUAPEBAS</t>
+          <t>SAO LUIS</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>31260629799921000490550000002414731266548790</t>
+          <t>31260415801747000116550030000025931705512966</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -22566,41 +22782,53 @@
         </is>
       </c>
       <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
+      <c r="N150" t="n">
+        <v>4101104740</v>
+      </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>PARAUAPEBAS</t>
+          <t>SAO LUIS</t>
         </is>
       </c>
       <c r="P150" s="1" t="n">
-        <v>46213</v>
+        <v>46136</v>
       </c>
       <c r="Q150" t="inlineStr"/>
       <c r="R150" t="inlineStr">
         <is>
-          <t>ESAB IND E COM LTDA</t>
-        </is>
-      </c>
-      <c r="S150" t="inlineStr"/>
+          <t>SEVEN SUPRIMENTOS INDUSTRIAIS LTDA</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>MANGUEIRA  P/COMPRESSOR PARAGUSO</t>
+        </is>
+      </c>
       <c r="T150" t="inlineStr">
         <is>
-          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
-        </is>
-      </c>
-      <c r="U150" t="inlineStr"/>
-      <c r="V150" t="inlineStr"/>
-      <c r="W150" t="inlineStr"/>
+          <t>NOTA FISCAL DIVERGENTE</t>
+        </is>
+      </c>
+      <c r="U150" t="n">
+        <v>300254000</v>
+      </c>
+      <c r="V150" t="n">
+        <v>6000153276</v>
+      </c>
+      <c r="W150" s="1" t="n">
+        <v>46122</v>
+      </c>
       <c r="X150" t="inlineStr">
         <is>
-          <t>jsconceica</t>
+          <t>dluz</t>
         </is>
       </c>
       <c r="Y150" t="n">
-        <v>267397.26</v>
+        <v>702.84</v>
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>No Prazo</t>
+          <t>Atrasado</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -22609,7 +22837,7 @@
         </is>
       </c>
       <c r="AB150" t="n">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="AC150" t="inlineStr">
         <is>
@@ -22618,48 +22846,68 @@
       </c>
       <c r="AD150" t="inlineStr">
         <is>
-          <t>RECUSADO DEVIDO A DATA REMESSA SER FUTURA E SEM ALINHAMENTO DA VALE</t>
+          <t>NF CONSTA DIVERGENCIA (INAPTA),NECESSARIO REGULARIZACAO DO XML. O FORNECEDOR DEVERA ABRIR CHAMADO NA FERRAMENTA V360</t>
         </is>
       </c>
       <c r="AE150" t="inlineStr">
         <is>
-          <t>IPATINGA/MG</t>
+          <t>SAO LUIS</t>
         </is>
       </c>
       <c r="AF150" t="inlineStr">
         <is>
-          <t>9 - 12 Dias</t>
+          <t>Acima de 12 Dias</t>
         </is>
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>PARAUAPEBAS</t>
-        </is>
-      </c>
-      <c r="AH150" t="inlineStr"/>
-      <c r="AI150" t="inlineStr"/>
-      <c r="AJ150" t="b">
-        <v>0</v>
+          <t>SAO LUIS</t>
+        </is>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>VALE S A</t>
+        </is>
+      </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>SEVEN SUPRIMENTOS INDUSTRIAIS LTDA</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>40946</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr"/>
+          <t>40547</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>392391</v>
+      </c>
       <c r="C151" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>TDV São Luiz - MA</t>
+        </is>
+      </c>
       <c r="E151" t="n">
-        <v>241562</v>
+        <v>33540</v>
       </c>
       <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>FRACIONADO</t>
+        </is>
+      </c>
       <c r="H151" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -22667,17 +22915,17 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Parauapebas - PA</t>
+          <t>São Luíz - MA</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>PARAUAPEBAS</t>
+          <t>SAO LUIS</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>31260629799921000490550000002415621553848879</t>
+          <t>35250500017952000118550010000335401611802796</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -22686,25 +22934,31 @@
         </is>
       </c>
       <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
+      <c r="N151" t="n">
+        <v>4100989446</v>
+      </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>PARAUAPEBAS</t>
+          <t>SAO LUIS</t>
         </is>
       </c>
       <c r="P151" s="1" t="n">
-        <v>46213</v>
+        <v>46171</v>
       </c>
       <c r="Q151" t="inlineStr"/>
       <c r="R151" t="inlineStr">
         <is>
-          <t>ESAB IND E COM LTDA</t>
-        </is>
-      </c>
-      <c r="S151" t="inlineStr"/>
+          <t>MOLYGRAFIT INDUSTRIA E COMERCIO LTD</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>SERVIÇO DE TRANSPORTE</t>
+        </is>
+      </c>
       <c r="T151" t="inlineStr">
         <is>
-          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
+          <t>NOTA FISCAL DIVERGENTE</t>
         </is>
       </c>
       <c r="U151" t="inlineStr"/>
@@ -22712,15 +22966,15 @@
       <c r="W151" t="inlineStr"/>
       <c r="X151" t="inlineStr">
         <is>
-          <t>jsconceica</t>
+          <t>dluz</t>
         </is>
       </c>
       <c r="Y151" t="n">
-        <v>178264.84</v>
+        <v>1029.23</v>
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>No Prazo</t>
+          <t>Atrasado</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -22729,7 +22983,7 @@
         </is>
       </c>
       <c r="AB151" t="n">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="AC151" t="inlineStr">
         <is>
@@ -22738,48 +22992,68 @@
       </c>
       <c r="AD151" t="inlineStr">
         <is>
-          <t>RECUSADO DEVIDO A DATA REMESSA SER FUTURA E SEM ALINHAMENTO DA VALE</t>
+          <t>FIZEMOS A TENTATIVA DE REENTREGA COM MESMA NF , JUNTO DA NF COMPLEMENTAR (33689) FONFORME TRATATIVAS , POREM NOTA CONTINUA INAPTA.</t>
         </is>
       </c>
       <c r="AE151" t="inlineStr">
         <is>
-          <t>IPATINGA/MG</t>
+          <t>SAO LUIS</t>
         </is>
       </c>
       <c r="AF151" t="inlineStr">
         <is>
-          <t>9 - 12 Dias</t>
+          <t>Acima de 12 Dias</t>
         </is>
       </c>
       <c r="AG151" t="inlineStr">
         <is>
-          <t>PARAUAPEBAS</t>
-        </is>
-      </c>
-      <c r="AH151" t="inlineStr"/>
-      <c r="AI151" t="inlineStr"/>
-      <c r="AJ151" t="b">
-        <v>0</v>
+          <t>SAO LUIS</t>
+        </is>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>VALE S A</t>
+        </is>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>MOLYGRAFIT INDUSTRIA E COMERCIO LTD</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>40977</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr"/>
+          <t>40810</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>1365998</v>
+      </c>
       <c r="C152" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>TDV Contagem MG</t>
+        </is>
+      </c>
       <c r="E152" t="n">
-        <v>857543</v>
+        <v>8466</v>
       </c>
       <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>FRACIONADO</t>
+        </is>
+      </c>
       <c r="H152" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -22787,17 +23061,17 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Parauapebas - PA</t>
+          <t>São Luíz - MA</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>PARAUAPEBAS</t>
+          <t>SAO LUIS</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>35260600536772003249550010008575431753933138</t>
+          <t>31260343711951000505550010000084661325509470</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -22809,38 +23083,48 @@
       <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr">
         <is>
-          <t>PARAUAPEBAS</t>
+          <t>SAO LUIS</t>
         </is>
       </c>
       <c r="P152" s="1" t="n">
-        <v>46217</v>
+        <v>46196</v>
       </c>
       <c r="Q152" t="inlineStr"/>
       <c r="R152" t="inlineStr">
         <is>
-          <t>ECOLAB QUIMICA LTDA</t>
-        </is>
-      </c>
-      <c r="S152" t="inlineStr"/>
+          <t>FLSMIDTH INDUSTRIAL SOLUTIONS LTDA</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>PARTES</t>
+        </is>
+      </c>
       <c r="T152" t="inlineStr">
         <is>
-          <t>DEVOLUCAO INDEVIDA</t>
-        </is>
-      </c>
-      <c r="U152" t="inlineStr"/>
-      <c r="V152" t="inlineStr"/>
-      <c r="W152" t="inlineStr"/>
+          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
+        </is>
+      </c>
+      <c r="U152" t="n">
+        <v>300292000</v>
+      </c>
+      <c r="V152" t="n">
+        <v>6000181717</v>
+      </c>
+      <c r="W152" s="1" t="n">
+        <v>46195</v>
+      </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>erisoares</t>
+          <t>proliveira</t>
         </is>
       </c>
       <c r="Y152" t="n">
-        <v>215462.1</v>
+        <v>1281886.36</v>
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>No Prazo</t>
+          <t>Atrasado</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -22849,47 +23133,57 @@
         </is>
       </c>
       <c r="AB152" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="AD152" t="inlineStr">
         <is>
-          <t>MATERIAL DEVOLVIDO DEVIDO O CLIENTE ESTA SEM EQUIPAMENTO PRA DESCARREGAR, FAZER ALINHAMENTO COM CLIENTE E AREA.</t>
+          <t>O FORNECEDOR DEVERA ABRIR CHAMADO NA FERRAMENTA V360</t>
         </is>
       </c>
       <c r="AE152" t="inlineStr">
         <is>
-          <t>IPATINGA/MG</t>
+          <t>SAO LUIS</t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
         <is>
-          <t>0 - 8 Dias</t>
+          <t>Acima de 12 Dias</t>
         </is>
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>PARAUAPEBAS</t>
-        </is>
-      </c>
-      <c r="AH152" t="inlineStr"/>
-      <c r="AI152" t="inlineStr"/>
-      <c r="AJ152" t="b">
-        <v>0</v>
+          <t>SAO LUIS</t>
+        </is>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>VALE SA</t>
+        </is>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>VALE SA</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>40219</t>
+          <t>40811</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>1194154</v>
+        <v>1328744</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -22898,16 +23192,16 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>TDV Contagem MG</t>
+          <t>TDV Fortaleza - CE</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>2593</v>
+        <v>27357</v>
       </c>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
-          <t>FRACIONADO</t>
+          <t>LOTACAO</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -22927,7 +23221,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>31260415801747000116550030000025931705512966</t>
+          <t>21260633592510037821550030000273571654701090</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -22937,7 +23231,7 @@
       </c>
       <c r="M153" t="inlineStr"/>
       <c r="N153" t="n">
-        <v>4101104740</v>
+        <v>4512553116</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
@@ -22945,40 +23239,36 @@
         </is>
       </c>
       <c r="P153" s="1" t="n">
-        <v>46136</v>
+        <v>46196</v>
       </c>
       <c r="Q153" t="inlineStr"/>
-      <c r="R153" t="inlineStr">
-        <is>
-          <t>SEVEN SUPRIMENTOS INDUSTRIAIS LTDA</t>
-        </is>
-      </c>
+      <c r="R153" t="inlineStr"/>
       <c r="S153" t="inlineStr">
         <is>
-          <t>MANGUEIRA  P/COMPRESSOR PARAGUSO</t>
+          <t>RODA FERVRIA 42POL 252,1MM</t>
         </is>
       </c>
       <c r="T153" t="inlineStr">
         <is>
-          <t>NOTA FISCAL DIVERGENTE</t>
+          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
       <c r="U153" t="n">
-        <v>300254000</v>
+        <v>300297000</v>
       </c>
       <c r="V153" t="n">
-        <v>6000153276</v>
+        <v>6000180276</v>
       </c>
       <c r="W153" s="1" t="n">
-        <v>46122</v>
+        <v>46190</v>
       </c>
       <c r="X153" t="inlineStr">
         <is>
-          <t>dluz</t>
+          <t>proliveira</t>
         </is>
       </c>
       <c r="Y153" t="n">
-        <v>702.84</v>
+        <v>318009.11</v>
       </c>
       <c r="Z153" t="inlineStr">
         <is>
@@ -22991,55 +23281,57 @@
         </is>
       </c>
       <c r="AB153" t="n">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="AC153" t="inlineStr">
         <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>RECUSADO DEVIDO A INCAPACIDADE PARA DESCARGA DO MATERIAL DE FORMA SEGURA. MATERIL CARREGADO SEM ESTAR PALETIZADO, DIRETAMENTE NO ASSOALHO DO VEICULO.</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>SAO LUIS</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>Acima de 12 Dias</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>SAO LUIS</t>
+        </is>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>VALE S A</t>
+        </is>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>VALE SA</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
           <t>NÃO</t>
         </is>
-      </c>
-      <c r="AD153" t="inlineStr">
-        <is>
-          <t>NF CONSTA DIVERGENCIA (INAPTA),NECESSARIO REGULARIZACAO DO XML. O FORNECEDOR DEVERA ABRIR CHAMADO NA FERRAMENTA V360</t>
-        </is>
-      </c>
-      <c r="AE153" t="inlineStr">
-        <is>
-          <t>SAO LUIS</t>
-        </is>
-      </c>
-      <c r="AF153" t="inlineStr">
-        <is>
-          <t>Acima de 12 Dias</t>
-        </is>
-      </c>
-      <c r="AG153" t="inlineStr">
-        <is>
-          <t>SAO LUIS</t>
-        </is>
-      </c>
-      <c r="AH153" t="inlineStr">
-        <is>
-          <t>VALE S A</t>
-        </is>
-      </c>
-      <c r="AI153" t="inlineStr">
-        <is>
-          <t>SEVEN SUPRIMENTOS INDUSTRIAIS LTDA</t>
-        </is>
-      </c>
-      <c r="AJ153" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>40547</t>
+          <t>40828</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>392391</v>
+        <v>1328772</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -23048,16 +23340,16 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>TDV São Luiz - MA</t>
+          <t>TDV Fortaleza - CE</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>33540</v>
+        <v>27356</v>
       </c>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr">
         <is>
-          <t>FRACIONADO</t>
+          <t>LOTACAO</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -23077,7 +23369,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>35250500017952000118550010000335401611802796</t>
+          <t>21260633592510037821550030000273561817592450</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -23087,7 +23379,7 @@
       </c>
       <c r="M154" t="inlineStr"/>
       <c r="N154" t="n">
-        <v>4100989446</v>
+        <v>4512553116</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
@@ -23095,34 +23387,36 @@
         </is>
       </c>
       <c r="P154" s="1" t="n">
-        <v>46171</v>
+        <v>46197</v>
       </c>
       <c r="Q154" t="inlineStr"/>
-      <c r="R154" t="inlineStr">
-        <is>
-          <t>MOLYGRAFIT INDUSTRIA E COMERCIO LTD</t>
-        </is>
-      </c>
+      <c r="R154" t="inlineStr"/>
       <c r="S154" t="inlineStr">
         <is>
-          <t>SERVIÇO DE TRANSPORTE</t>
+          <t>RODA FERVRIA 42POL 252,1MM</t>
         </is>
       </c>
       <c r="T154" t="inlineStr">
         <is>
-          <t>NOTA FISCAL DIVERGENTE</t>
-        </is>
-      </c>
-      <c r="U154" t="inlineStr"/>
-      <c r="V154" t="inlineStr"/>
-      <c r="W154" t="inlineStr"/>
+          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
+        </is>
+      </c>
+      <c r="U154" t="n">
+        <v>300292000</v>
+      </c>
+      <c r="V154" t="n">
+        <v>6000177916</v>
+      </c>
+      <c r="W154" s="1" t="n">
+        <v>46184</v>
+      </c>
       <c r="X154" t="inlineStr">
         <is>
-          <t>dluz</t>
+          <t>proliveira</t>
         </is>
       </c>
       <c r="Y154" t="n">
-        <v>1029.23</v>
+        <v>289099.19</v>
       </c>
       <c r="Z154" t="inlineStr">
         <is>
@@ -23135,55 +23429,57 @@
         </is>
       </c>
       <c r="AB154" t="n">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="AC154" t="inlineStr">
         <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="AD154" t="inlineStr">
+        <is>
+          <t>RECUSADO DEVIDO A INCAPACIDADE DO MATERIAL PARA DESCARREGAR COM EMPILHADEIRA</t>
+        </is>
+      </c>
+      <c r="AE154" t="inlineStr">
+        <is>
+          <t>SAO LUIS</t>
+        </is>
+      </c>
+      <c r="AF154" t="inlineStr">
+        <is>
+          <t>Acima de 12 Dias</t>
+        </is>
+      </c>
+      <c r="AG154" t="inlineStr">
+        <is>
+          <t>SAO LUIS</t>
+        </is>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>VALE S A</t>
+        </is>
+      </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>VALE SA</t>
+        </is>
+      </c>
+      <c r="AJ154" t="inlineStr">
+        <is>
           <t>NÃO</t>
         </is>
-      </c>
-      <c r="AD154" t="inlineStr">
-        <is>
-          <t>FIZEMOS A TENTATIVA DE REENTREGA COM MESMA NF , JUNTO DA NF COMPLEMENTAR (33689) FONFORME TRATATIVAS , POREM NOTA CONTINUA INAPTA.</t>
-        </is>
-      </c>
-      <c r="AE154" t="inlineStr">
-        <is>
-          <t>SAO LUIS</t>
-        </is>
-      </c>
-      <c r="AF154" t="inlineStr">
-        <is>
-          <t>Acima de 12 Dias</t>
-        </is>
-      </c>
-      <c r="AG154" t="inlineStr">
-        <is>
-          <t>SAO LUIS</t>
-        </is>
-      </c>
-      <c r="AH154" t="inlineStr">
-        <is>
-          <t>VALE S A</t>
-        </is>
-      </c>
-      <c r="AI154" t="inlineStr">
-        <is>
-          <t>MOLYGRAFIT INDUSTRIA E COMERCIO LTD</t>
-        </is>
-      </c>
-      <c r="AJ154" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>40810</t>
+          <t>40829</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>1365998</v>
+        <v>1328771</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -23192,16 +23488,16 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>TDV Contagem MG</t>
+          <t>TDV Fortaleza - CE</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>8466</v>
+        <v>27355</v>
       </c>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr">
         <is>
-          <t>FRACIONADO</t>
+          <t>LOTACAO</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -23221,7 +23517,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>31260343711951000505550010000084661325509470</t>
+          <t>21260633592510037821550030000273551780304343</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -23230,24 +23526,22 @@
         </is>
       </c>
       <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
+      <c r="N155" t="n">
+        <v>4512553116</v>
+      </c>
       <c r="O155" t="inlineStr">
         <is>
           <t>SAO LUIS</t>
         </is>
       </c>
       <c r="P155" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="Q155" t="inlineStr"/>
-      <c r="R155" t="inlineStr">
-        <is>
-          <t>FLSMIDTH INDUSTRIAL SOLUTIONS LTDA</t>
-        </is>
-      </c>
+      <c r="R155" t="inlineStr"/>
       <c r="S155" t="inlineStr">
         <is>
-          <t>PARTES</t>
+          <t>RODA FERVRIA 42POL 252,1MM</t>
         </is>
       </c>
       <c r="T155" t="inlineStr">
@@ -23259,10 +23553,10 @@
         <v>300292000</v>
       </c>
       <c r="V155" t="n">
-        <v>6000181717</v>
+        <v>6000177916</v>
       </c>
       <c r="W155" s="1" t="n">
-        <v>46195</v>
+        <v>46184</v>
       </c>
       <c r="X155" t="inlineStr">
         <is>
@@ -23270,7 +23564,7 @@
         </is>
       </c>
       <c r="Y155" t="n">
-        <v>1281886.36</v>
+        <v>318009.11</v>
       </c>
       <c r="Z155" t="inlineStr">
         <is>
@@ -23283,55 +23577,57 @@
         </is>
       </c>
       <c r="AB155" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AC155" t="inlineStr">
         <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>RECUSADO DEVIDO A INCAPACIDADE DO MATERIAL PARA DESCARREGAR COM EMPILHADEIRA</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>SAO LUIS</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>Acima de 12 Dias</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>SAO LUIS</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>VALE S A</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>VALE SA</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
           <t>NÃO</t>
         </is>
-      </c>
-      <c r="AD155" t="inlineStr">
-        <is>
-          <t>O FORNECEDOR DEVERA ABRIR CHAMADO NA FERRAMENTA V360</t>
-        </is>
-      </c>
-      <c r="AE155" t="inlineStr">
-        <is>
-          <t>SAO LUIS</t>
-        </is>
-      </c>
-      <c r="AF155" t="inlineStr">
-        <is>
-          <t>Acima de 12 Dias</t>
-        </is>
-      </c>
-      <c r="AG155" t="inlineStr">
-        <is>
-          <t>SAO LUIS</t>
-        </is>
-      </c>
-      <c r="AH155" t="inlineStr">
-        <is>
-          <t>VALE SA</t>
-        </is>
-      </c>
-      <c r="AI155" t="inlineStr">
-        <is>
-          <t>VALE SA</t>
-        </is>
-      </c>
-      <c r="AJ155" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>40811</t>
+          <t>40835</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>1328744</v>
+        <v>1331164</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -23340,16 +23636,16 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>TDV Fortaleza - CE</t>
+          <t>TDV Serra- ES</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>27357</v>
+        <v>24102</v>
       </c>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr">
         <is>
-          <t>LOTACAO</t>
+          <t>FRACIONADO</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -23369,7 +23665,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>21260633592510037821550030000273571654701090</t>
+          <t>32260501595865000100550010000241021803691646</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -23378,22 +23674,24 @@
         </is>
       </c>
       <c r="M156" t="inlineStr"/>
-      <c r="N156" t="n">
-        <v>4512553116</v>
-      </c>
+      <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr">
         <is>
           <t>SAO LUIS</t>
         </is>
       </c>
       <c r="P156" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="Q156" t="inlineStr"/>
-      <c r="R156" t="inlineStr"/>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>CSV LTDA</t>
+        </is>
+      </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>RODA FERVRIA 42POL 252,1MM</t>
+          <t>BTN003</t>
         </is>
       </c>
       <c r="T156" t="inlineStr">
@@ -23402,13 +23700,13 @@
         </is>
       </c>
       <c r="U156" t="n">
-        <v>300297000</v>
+        <v>300289000</v>
       </c>
       <c r="V156" t="n">
-        <v>6000180276</v>
+        <v>6000178002</v>
       </c>
       <c r="W156" s="1" t="n">
-        <v>46190</v>
+        <v>46184</v>
       </c>
       <c r="X156" t="inlineStr">
         <is>
@@ -23416,7 +23714,7 @@
         </is>
       </c>
       <c r="Y156" t="n">
-        <v>318009.11</v>
+        <v>46150</v>
       </c>
       <c r="Z156" t="inlineStr">
         <is>
@@ -23429,7 +23727,7 @@
         </is>
       </c>
       <c r="AB156" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AC156" t="inlineStr">
         <is>
@@ -23438,7 +23736,7 @@
       </c>
       <c r="AD156" t="inlineStr">
         <is>
-          <t>RECUSADO DEVIDO A INCAPACIDADE PARA DESCARGA DO MATERIAL DE FORMA SEGURA. MATERIL CARREGADO SEM ESTAR PALETIZADO, DIRETAMENTE NO ASSOALHO DO VEICULO.</t>
+          <t>NAO RECEBIDO POR FALTA DA EQUIPE NO LOCAL PARA REALIZAR O DESCARREGAMENTO</t>
         </is>
       </c>
       <c r="AE156" t="inlineStr">
@@ -23466,38 +23764,30 @@
           <t>VALE SA</t>
         </is>
       </c>
-      <c r="AJ156" t="b">
-        <v>0</v>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>40828</t>
-        </is>
-      </c>
-      <c r="B157" t="n">
-        <v>1328772</v>
-      </c>
+          <t>41002</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>TDV Fortaleza - CE</t>
-        </is>
-      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="n">
-        <v>27356</v>
+        <v>65592</v>
       </c>
       <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>LOTACAO</t>
-        </is>
-      </c>
+      <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -23515,7 +23805,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>21260633592510037821550030000273561817592450</t>
+          <t>35260759511741000180550010000655921682706407</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -23524,49 +23814,41 @@
         </is>
       </c>
       <c r="M157" t="inlineStr"/>
-      <c r="N157" t="n">
-        <v>4512553116</v>
-      </c>
+      <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr">
         <is>
           <t>SAO LUIS</t>
         </is>
       </c>
       <c r="P157" s="1" t="n">
-        <v>46197</v>
+        <v>46223</v>
       </c>
       <c r="Q157" t="inlineStr"/>
-      <c r="R157" t="inlineStr"/>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>RODA FERVRIA 42POL 252,1MM</t>
-        </is>
-      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>ARGA FACIL DE DESCALVADO LTDA</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr"/>
       <c r="T157" t="inlineStr">
         <is>
           <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
-      <c r="U157" t="n">
-        <v>300292000</v>
-      </c>
-      <c r="V157" t="n">
-        <v>6000177916</v>
-      </c>
-      <c r="W157" s="1" t="n">
-        <v>46184</v>
-      </c>
+      <c r="U157" t="inlineStr"/>
+      <c r="V157" t="inlineStr"/>
+      <c r="W157" t="inlineStr"/>
       <c r="X157" t="inlineStr">
         <is>
           <t>proliveira</t>
         </is>
       </c>
       <c r="Y157" t="n">
-        <v>289099.19</v>
+        <v>5775</v>
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>No Prazo</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -23575,7 +23857,7 @@
         </is>
       </c>
       <c r="AB157" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="AC157" t="inlineStr">
         <is>
@@ -23584,7 +23866,7 @@
       </c>
       <c r="AD157" t="inlineStr">
         <is>
-          <t>RECUSADO DEVIDO A INCAPACIDADE DO MATERIAL PARA DESCARREGAR COM EMPILHADEIRA</t>
+          <t>NF DEVOLVIDA DEVIDO O MATERIAL NAO ESTA PALETIZADO</t>
         </is>
       </c>
       <c r="AE157" t="inlineStr">
@@ -23594,7 +23876,7 @@
       </c>
       <c r="AF157" t="inlineStr">
         <is>
-          <t>Acima de 12 Dias</t>
+          <t>0 - 8 Dias</t>
         </is>
       </c>
       <c r="AG157" t="inlineStr">
@@ -23602,432 +23884,12 @@
           <t>SAO LUIS</t>
         </is>
       </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>VALE S A</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>VALE SA</t>
-        </is>
-      </c>
-      <c r="AJ157" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>40829</t>
-        </is>
-      </c>
-      <c r="B158" t="n">
-        <v>1328771</v>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Devolução</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>TDV Fortaleza - CE</t>
-        </is>
-      </c>
-      <c r="E158" t="n">
-        <v>27355</v>
-      </c>
-      <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>LOTACAO</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>São Luíz - MA</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>SAO LUIS</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>21260633592510037821550030000273551780304343</t>
-        </is>
-      </c>
-      <c r="L158" t="inlineStr">
-        <is>
-          <t>VALE</t>
-        </is>
-      </c>
-      <c r="M158" t="inlineStr"/>
-      <c r="N158" t="n">
-        <v>4512553116</v>
-      </c>
-      <c r="O158" t="inlineStr">
-        <is>
-          <t>SAO LUIS</t>
-        </is>
-      </c>
-      <c r="P158" s="1" t="n">
-        <v>46197</v>
-      </c>
-      <c r="Q158" t="inlineStr"/>
-      <c r="R158" t="inlineStr"/>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>RODA FERVRIA 42POL 252,1MM</t>
-        </is>
-      </c>
-      <c r="T158" t="inlineStr">
-        <is>
-          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
-        </is>
-      </c>
-      <c r="U158" t="n">
-        <v>300292000</v>
-      </c>
-      <c r="V158" t="n">
-        <v>6000177916</v>
-      </c>
-      <c r="W158" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="X158" t="inlineStr">
-        <is>
-          <t>proliveira</t>
-        </is>
-      </c>
-      <c r="Y158" t="n">
-        <v>318009.11</v>
-      </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>Atrasado</t>
-        </is>
-      </c>
-      <c r="AA158" t="inlineStr">
-        <is>
-          <t>Em Aberto</t>
-        </is>
-      </c>
-      <c r="AB158" t="n">
-        <v>27</v>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="AD158" t="inlineStr">
-        <is>
-          <t>RECUSADO DEVIDO A INCAPACIDADE DO MATERIAL PARA DESCARREGAR COM EMPILHADEIRA</t>
-        </is>
-      </c>
-      <c r="AE158" t="inlineStr">
-        <is>
-          <t>SAO LUIS</t>
-        </is>
-      </c>
-      <c r="AF158" t="inlineStr">
-        <is>
-          <t>Acima de 12 Dias</t>
-        </is>
-      </c>
-      <c r="AG158" t="inlineStr">
-        <is>
-          <t>SAO LUIS</t>
-        </is>
-      </c>
-      <c r="AH158" t="inlineStr">
-        <is>
-          <t>VALE S A</t>
-        </is>
-      </c>
-      <c r="AI158" t="inlineStr">
-        <is>
-          <t>VALE SA</t>
-        </is>
-      </c>
-      <c r="AJ158" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>40835</t>
-        </is>
-      </c>
-      <c r="B159" t="n">
-        <v>1331164</v>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Devolução</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>TDV Serra- ES</t>
-        </is>
-      </c>
-      <c r="E159" t="n">
-        <v>24102</v>
-      </c>
-      <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>FRACIONADO</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>São Luíz - MA</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>SAO LUIS</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>32260501595865000100550010000241021803691646</t>
-        </is>
-      </c>
-      <c r="L159" t="inlineStr">
-        <is>
-          <t>VALE</t>
-        </is>
-      </c>
-      <c r="M159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
-      <c r="O159" t="inlineStr">
-        <is>
-          <t>SAO LUIS</t>
-        </is>
-      </c>
-      <c r="P159" s="1" t="n">
-        <v>46197</v>
-      </c>
-      <c r="Q159" t="inlineStr"/>
-      <c r="R159" t="inlineStr">
-        <is>
-          <t>CSV LTDA</t>
-        </is>
-      </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>BTN003</t>
-        </is>
-      </c>
-      <c r="T159" t="inlineStr">
-        <is>
-          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
-        </is>
-      </c>
-      <c r="U159" t="n">
-        <v>300289000</v>
-      </c>
-      <c r="V159" t="n">
-        <v>6000178002</v>
-      </c>
-      <c r="W159" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="X159" t="inlineStr">
-        <is>
-          <t>proliveira</t>
-        </is>
-      </c>
-      <c r="Y159" t="n">
-        <v>46150</v>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>Atrasado</t>
-        </is>
-      </c>
-      <c r="AA159" t="inlineStr">
-        <is>
-          <t>Em Aberto</t>
-        </is>
-      </c>
-      <c r="AB159" t="n">
-        <v>27</v>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="AD159" t="inlineStr">
-        <is>
-          <t>NAO RECEBIDO POR FALTA DA EQUIPE NO LOCAL PARA REALIZAR O DESCARREGAMENTO</t>
-        </is>
-      </c>
-      <c r="AE159" t="inlineStr">
-        <is>
-          <t>SAO LUIS</t>
-        </is>
-      </c>
-      <c r="AF159" t="inlineStr">
-        <is>
-          <t>Acima de 12 Dias</t>
-        </is>
-      </c>
-      <c r="AG159" t="inlineStr">
-        <is>
-          <t>SAO LUIS</t>
-        </is>
-      </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>VALE S A</t>
-        </is>
-      </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>VALE SA</t>
-        </is>
-      </c>
-      <c r="AJ159" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>41002</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr"/>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Devolução</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr"/>
-      <c r="E160" t="n">
-        <v>65592</v>
-      </c>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>São Luíz - MA</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>SAO LUIS</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>35260759511741000180550010000655921682706407</t>
-        </is>
-      </c>
-      <c r="L160" t="inlineStr">
-        <is>
-          <t>VALE</t>
-        </is>
-      </c>
-      <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
-      <c r="O160" t="inlineStr">
-        <is>
-          <t>SAO LUIS</t>
-        </is>
-      </c>
-      <c r="P160" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="Q160" t="inlineStr"/>
-      <c r="R160" t="inlineStr">
-        <is>
-          <t>ARGA FACIL DE DESCALVADO LTDA</t>
-        </is>
-      </c>
-      <c r="S160" t="inlineStr"/>
-      <c r="T160" t="inlineStr">
-        <is>
-          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
-        </is>
-      </c>
-      <c r="U160" t="inlineStr"/>
-      <c r="V160" t="inlineStr"/>
-      <c r="W160" t="inlineStr"/>
-      <c r="X160" t="inlineStr">
-        <is>
-          <t>proliveira</t>
-        </is>
-      </c>
-      <c r="Y160" t="n">
-        <v>5775</v>
-      </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>No Prazo</t>
-        </is>
-      </c>
-      <c r="AA160" t="inlineStr">
-        <is>
-          <t>Em Aberto</t>
-        </is>
-      </c>
-      <c r="AB160" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="AD160" t="inlineStr">
-        <is>
-          <t>NF DEVOLVIDA DEVIDO O MATERIAL NAO ESTA PALETIZADO</t>
-        </is>
-      </c>
-      <c r="AE160" t="inlineStr">
-        <is>
-          <t>SAO LUIS</t>
-        </is>
-      </c>
-      <c r="AF160" t="inlineStr">
-        <is>
-          <t>0 - 8 Dias</t>
-        </is>
-      </c>
-      <c r="AG160" t="inlineStr">
-        <is>
-          <t>SAO LUIS</t>
-        </is>
-      </c>
-      <c r="AH160" t="inlineStr"/>
-      <c r="AI160" t="inlineStr"/>
-      <c r="AJ160" t="b">
-        <v>0</v>
+      <c r="AH157" t="inlineStr"/>
+      <c r="AI157" t="inlineStr"/>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/apresentacoes/Devolucoes_Vale_tratada.xlsx
+++ b/apresentacoes/Devolucoes_Vale_tratada.xlsx
@@ -21289,7 +21289,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="AD139" t="inlineStr">
@@ -21441,7 +21441,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="AD140" t="inlineStr">
@@ -21593,7 +21593,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="AD141" t="inlineStr">
@@ -21745,7 +21745,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="AD142" t="inlineStr">
@@ -21897,7 +21897,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="AD143" t="inlineStr">
@@ -22049,7 +22049,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="AD144" t="inlineStr">
@@ -22201,7 +22201,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="AD145" t="inlineStr">

--- a/apresentacoes/Devolucoes_Vale_tratada.xlsx
+++ b/apresentacoes/Devolucoes_Vale_tratada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI129"/>
+  <dimension ref="A1:AI131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7343,11 +7343,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>39935</t>
+          <t>39850</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1141437</v>
+        <v>1121173</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -7356,11 +7356,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>TDV São Paulo - SP</t>
+          <t>TDV Contagem MG</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>8008645</v>
+        <v>6798</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>35260154651716001150550000080086451981210555</t>
+          <t>31260138684304000198550010000067981160598130</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -7394,26 +7394,24 @@
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" t="n">
-        <v>4512652547</v>
-      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
           <t>CONTAGEM</t>
         </is>
       </c>
       <c r="P48" s="1" t="n">
-        <v>46102</v>
+        <v>46099</v>
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
-          <t>SUPRICORP SUPRIMENTOS LTDA</t>
+          <t>UNIACO LTDA</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>PILHA ALCALINA PALITO AAA C/2 UNS ELGIN</t>
+          <t>CALHA DE CHUVA</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -7422,13 +7420,13 @@
         </is>
       </c>
       <c r="U48" t="n">
-        <v>300242000</v>
+        <v>300237000</v>
       </c>
       <c r="V48" t="n">
-        <v>6000144592</v>
+        <v>6000144681</v>
       </c>
       <c r="W48" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -7436,7 +7434,7 @@
         </is>
       </c>
       <c r="Y48" t="n">
-        <v>371.61</v>
+        <v>1000</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
@@ -7449,7 +7447,7 @@
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
@@ -7458,8 +7456,8 @@
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>PEDIDO CANCELADO.
-23/03-EMAIL SINALIZADO AGUARDANDO RETORNO</t>
+          <t>MATERIAL  NAO PERTENCE AO ARMAZEM DE JANGADA, O MATERIAL TEM QUE SER ENTREGUE EM AREA COM A INDENTIFICACAO DO RESPONSAVEL DO MATERIAL.
+25/03-EMAIL SINALIZADO AGUARDANDO RETORNO</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr">
@@ -7474,7 +7472,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>OURO PRETO</t>
+          <t>BRUMADINHO</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
@@ -7491,11 +7489,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>39936</t>
+          <t>39935</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1141520</v>
+        <v>1141437</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7508,7 +7506,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>8008651</v>
+        <v>8008645</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
@@ -7533,7 +7531,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>35260154651716001150550000080086511981212490</t>
+          <t>35260154651716001150550000080086451981210555</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -7543,7 +7541,7 @@
       </c>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="n">
-        <v>4512648872</v>
+        <v>4512652547</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -7561,7 +7559,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>DETERGENTE NEUTRO 5LT SANTOP</t>
+          <t>PILHA ALCALINA PALITO AAA C/2 UNS ELGIN</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -7570,13 +7568,13 @@
         </is>
       </c>
       <c r="U49" t="n">
-        <v>300241000</v>
+        <v>300242000</v>
       </c>
       <c r="V49" t="n">
-        <v>6000152773</v>
+        <v>6000144592</v>
       </c>
       <c r="W49" s="1" t="n">
-        <v>46121</v>
+        <v>46100</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -7584,7 +7582,7 @@
         </is>
       </c>
       <c r="Y49" t="n">
-        <v>37.34</v>
+        <v>371.61</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
@@ -7607,7 +7605,7 @@
       <c r="AD49" t="inlineStr">
         <is>
           <t>PEDIDO CANCELADO.
-05/06-EMAIL SINALIZADO 23/03</t>
+23/03-EMAIL SINALIZADO AGUARDANDO RETORNO</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr">
@@ -7639,11 +7637,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>39937</t>
+          <t>39936</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1141561</v>
+        <v>1141520</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7656,7 +7654,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>8008654</v>
+        <v>8008651</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
@@ -7681,7 +7679,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>35260154651716001150550000080086541981459463</t>
+          <t>35260154651716001150550000080086511981212490</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -7691,7 +7689,7 @@
       </c>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="n">
-        <v>4512648457</v>
+        <v>4512648872</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -7709,7 +7707,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>APOIO P/MOUSE C/APOIO ERGON MP-50 C3TECH</t>
+          <t>DETERGENTE NEUTRO 5LT SANTOP</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
@@ -7718,13 +7716,13 @@
         </is>
       </c>
       <c r="U50" t="n">
-        <v>300242000</v>
+        <v>300241000</v>
       </c>
       <c r="V50" t="n">
-        <v>6000144592</v>
+        <v>6000152773</v>
       </c>
       <c r="W50" s="1" t="n">
-        <v>46100</v>
+        <v>46121</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -7732,7 +7730,7 @@
         </is>
       </c>
       <c r="Y50" t="n">
-        <v>271.63</v>
+        <v>37.34</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
@@ -7787,11 +7785,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>39938</t>
+          <t>39937</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1141430</v>
+        <v>1141561</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7804,7 +7802,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>8008600</v>
+        <v>8008654</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
@@ -7829,7 +7827,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>35260154651716001150550000080086001981193004</t>
+          <t>35260154651716001150550000080086541981459463</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -7839,7 +7837,7 @@
       </c>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="n">
-        <v>4512652479</v>
+        <v>4512648457</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -7857,7 +7855,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>PILHA RECARREGAVEL 1.2V AA 2000MAH C/2</t>
+          <t>APOIO P/MOUSE C/APOIO ERGON MP-50 C3TECH</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
@@ -7880,7 +7878,7 @@
         </is>
       </c>
       <c r="Y51" t="n">
-        <v>459.53</v>
+        <v>271.63</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
@@ -7935,11 +7933,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>40021</t>
+          <t>39938</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1148722</v>
+        <v>1141430</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7948,11 +7946,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>TDV Contagem MG</t>
+          <t>TDV São Paulo - SP</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>29895</v>
+        <v>8008600</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
@@ -7977,7 +7975,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>31260331228009000188550010000298951388375076</t>
+          <t>35260154651716001150550000080086001981193004</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -7987,7 +7985,7 @@
       </c>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="n">
-        <v>4512920695</v>
+        <v>4512652479</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -7995,214 +7993,214 @@
         </is>
       </c>
       <c r="P52" s="1" t="n">
-        <v>46108</v>
+        <v>46102</v>
       </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr">
         <is>
+          <t>SUPRICORP SUPRIMENTOS LTDA</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>PILHA RECARREGAVEL 1.2V AA 2000MAH C/2</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
+        </is>
+      </c>
+      <c r="U52" t="n">
+        <v>300242000</v>
+      </c>
+      <c r="V52" t="n">
+        <v>6000144592</v>
+      </c>
+      <c r="W52" s="1" t="n">
+        <v>46100</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>andias</t>
+        </is>
+      </c>
+      <c r="Y52" t="n">
+        <v>459.53</v>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>Em Aberto</t>
+        </is>
+      </c>
+      <c r="AB52" t="n">
+        <v>122</v>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>PEDIDO CANCELADO.
+05/06-EMAIL SINALIZADO 23/03</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>Acima de 12 Dias</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>OURO PRETO</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>VALE SA</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>VALE SA</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>40021</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1148722</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Devolução</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>TDV Contagem MG</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>29895</v>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>FRACIONADO</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Contagem MG</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>31260331228009000188550010000298951388375076</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>VALE</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="n">
+        <v>4512920695</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="P53" s="1" t="n">
+        <v>46108</v>
+      </c>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr">
+        <is>
           <t>DEL REY RUBBER BORRACHA E POLIURETA</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>TUBO ACO PU DN18X6000MM 150LBS FX-FS</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
-      <c r="U52" t="n">
+      <c r="U53" t="n">
         <v>300246000</v>
       </c>
-      <c r="V52" t="n">
+      <c r="V53" t="n">
         <v>6000147599</v>
       </c>
-      <c r="W52" s="1" t="n">
+      <c r="W53" s="1" t="n">
         <v>46107</v>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>andias</t>
         </is>
       </c>
-      <c r="Y52" t="n">
+      <c r="Y53" t="n">
         <v>29665.65</v>
       </c>
-      <c r="Z52" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>Atrasado</t>
         </is>
       </c>
-      <c r="AA52" t="inlineStr">
+      <c r="AA53" t="inlineStr">
         <is>
           <t>Em Aberto</t>
         </is>
       </c>
-      <c r="AB52" t="n">
+      <c r="AB53" t="n">
         <v>116</v>
       </c>
-      <c r="AC52" t="inlineStr">
+      <c r="AC53" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="AD52" t="inlineStr">
+      <c r="AD53" t="inlineStr">
         <is>
           <t>NOTA RECUSADA, MATERIAL NO MEIO DO CAMINH?O E A EMPILHADEIRA N?O CONSEGUE PEGAR COM A TARA TOTAL.
 05/06-EMAIL SINALIZADO 01/04
 01-04 - E-MAIL SINALIZADO AO FORNECEDOR .</t>
         </is>
       </c>
-      <c r="AE52" t="inlineStr">
-        <is>
-          <t>CONTAGEM</t>
-        </is>
-      </c>
-      <c r="AF52" t="inlineStr">
-        <is>
-          <t>Acima de 12 Dias</t>
-        </is>
-      </c>
-      <c r="AG52" t="inlineStr">
-        <is>
-          <t>NOVA LIMA</t>
-        </is>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>VALE SA</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>VALE SA</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>40036</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>1162816</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Devolução</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>TDV Contagem MG</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>285807</v>
-      </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>FRACIONADO</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Contagem MG</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>CONTAGEM</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>31260317185315000153550010002858071335925104</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>VALE</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="n">
-        <v>4101171543</v>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>CONTAGEM</t>
-        </is>
-      </c>
-      <c r="P53" s="1" t="n">
-        <v>46111</v>
-      </c>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>ACOCON INDUSTRIA E COMERCIO LTDA</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>PERFIL L LAM A-36   6,35  76,20  76,20-X</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
-        </is>
-      </c>
-      <c r="U53" t="n">
-        <v>300245000</v>
-      </c>
-      <c r="V53" t="n">
-        <v>6000152852</v>
-      </c>
-      <c r="W53" s="1" t="n">
-        <v>46121</v>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>andias</t>
-        </is>
-      </c>
-      <c r="Y53" t="n">
-        <v>360.8</v>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>Atrasado</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>Em Aberto</t>
-        </is>
-      </c>
-      <c r="AB53" t="n">
-        <v>113</v>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="AD53" t="inlineStr">
-        <is>
-          <t>NF RECUSADA DEVIDO METRAGEM INCOMPATIVEL, ENTREGAR EM AREA.
-05/06- EMAIL SINALIZADO 11/03</t>
-        </is>
-      </c>
       <c r="AE53" t="inlineStr">
         <is>
           <t>CONTAGEM</t>
@@ -8232,11 +8230,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>40059</t>
+          <t>40036</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1170366</v>
+        <v>1162816</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -8245,11 +8243,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>TDV São Paulo - SP</t>
+          <t>TDV Contagem MG</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>274700</v>
+        <v>285807</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
@@ -8274,7 +8272,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>35260357029431004780550150002747001845521932</t>
+          <t>31260317185315000153550010002858071335925104</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -8284,7 +8282,7 @@
       </c>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="n">
-        <v>4101114909</v>
+        <v>4101171543</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -8292,17 +8290,17 @@
         </is>
       </c>
       <c r="P54" s="1" t="n">
-        <v>46114</v>
+        <v>46111</v>
       </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr">
         <is>
-          <t>ATLAS COPCO BRASIL LTDA</t>
+          <t>ACOCON INDUSTRIA E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>SECADOR F4170+ W 460/60 -13431512 -COX81</t>
+          <t>PERFIL L LAM A-36   6,35  76,20  76,20-X</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -8311,10 +8309,10 @@
         </is>
       </c>
       <c r="U54" t="n">
-        <v>300247000</v>
+        <v>300245000</v>
       </c>
       <c r="V54" t="n">
-        <v>6000152779</v>
+        <v>6000152852</v>
       </c>
       <c r="W54" s="1" t="n">
         <v>46121</v>
@@ -8325,7 +8323,7 @@
         </is>
       </c>
       <c r="Y54" t="n">
-        <v>376108.82</v>
+        <v>360.8</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
@@ -8338,7 +8336,7 @@
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
@@ -8347,8 +8345,8 @@
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>SEM EQUIPAMENTO PARA DESCARREGAR NA AREA.
-05/06-EMAIL SINALIZANDO 10/04</t>
+          <t>NF RECUSADA DEVIDO METRAGEM INCOMPATIVEL, ENTREGAR EM AREA.
+05/06- EMAIL SINALIZADO 11/03</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr">
@@ -8380,11 +8378,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>40135</t>
+          <t>40059</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1197891</v>
+        <v>1170366</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -8393,11 +8391,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>TDV Contagem MG</t>
+          <t>TDV São Paulo - SP</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>286471</v>
+        <v>274700</v>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
@@ -8422,7 +8420,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>31260417185315000153550010002864711335925101</t>
+          <t>35260357029431004780550150002747001845521932</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -8432,7 +8430,7 @@
       </c>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="n">
-        <v>4101179935</v>
+        <v>4101114909</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -8440,17 +8438,17 @@
         </is>
       </c>
       <c r="P55" s="1" t="n">
-        <v>46123</v>
+        <v>46114</v>
       </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr">
         <is>
-          <t>ACOCON INDUSTRIA E COMERCIO LTDA</t>
+          <t>ATLAS COPCO BRASIL LTDA</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>REDONDO LAM 1020  50,80-X 6000</t>
+          <t>SECADOR F4170+ W 460/60 -13431512 -COX81</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
@@ -8459,13 +8457,13 @@
         </is>
       </c>
       <c r="U55" t="n">
-        <v>300255000</v>
+        <v>300247000</v>
       </c>
       <c r="V55" t="n">
-        <v>6000153440</v>
+        <v>6000152779</v>
       </c>
       <c r="W55" s="1" t="n">
-        <v>46122</v>
+        <v>46121</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -8473,7 +8471,7 @@
         </is>
       </c>
       <c r="Y55" t="n">
-        <v>1522.9</v>
+        <v>376108.82</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
@@ -8486,7 +8484,7 @@
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
@@ -8495,8 +8493,8 @@
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>RECUSADO ,MATERIAL MEDE 6 METROS E NAO ESTA PALETIZADO.
-05/06-EMAIL SINALIZANDO 14/04</t>
+          <t>SEM EQUIPAMENTO PARA DESCARREGAR NA AREA.
+05/06-EMAIL SINALIZANDO 10/04</t>
         </is>
       </c>
       <c r="AE55" t="inlineStr">
@@ -8528,11 +8526,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>40136</t>
+          <t>40135</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1169142</v>
+        <v>1197891</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -8545,7 +8543,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>35778</v>
+        <v>286471</v>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
@@ -8570,7 +8568,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>31260301527393000159550010000357781670978183</t>
+          <t>31260417185315000153550010002864711335925101</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -8580,7 +8578,7 @@
       </c>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="n">
-        <v>4512762683</v>
+        <v>4101179935</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -8593,12 +8591,12 @@
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr">
         <is>
-          <t>POLLYRUBBER INDUSTRIA S.A.</t>
+          <t>ACOCON INDUSTRIA E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>MANGOTE EM BORRACHA</t>
+          <t>REDONDO LAM 1020  50,80-X 6000</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
@@ -8621,7 +8619,7 @@
         </is>
       </c>
       <c r="Y56" t="n">
-        <v>17498.89</v>
+        <v>1522.9</v>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
@@ -8643,7 +8641,7 @@
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>RECUSADO. MATERIAL MEDE 6 METROS E NAO ESTA PALETIZADO.
+          <t>RECUSADO ,MATERIAL MEDE 6 METROS E NAO ESTA PALETIZADO.
 05/06-EMAIL SINALIZANDO 14/04</t>
         </is>
       </c>
@@ -8676,11 +8674,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>40140</t>
+          <t>40136</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1190582</v>
+        <v>1169142</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8689,11 +8687,11 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>TDV Ribeirão Preto - SP</t>
+          <t>TDV Contagem MG</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>24040</v>
+        <v>35778</v>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
@@ -8718,7 +8716,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>35260367590265000168550010000240401000081739</t>
+          <t>31260301527393000159550010000357781670978183</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -8728,7 +8726,7 @@
       </c>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="n">
-        <v>4512862100</v>
+        <v>4512762683</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -8736,17 +8734,17 @@
         </is>
       </c>
       <c r="P57" s="1" t="n">
-        <v>46126</v>
+        <v>46123</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr">
         <is>
-          <t>SANTA RITA SOLUCOES TUBULARES LTDA</t>
+          <t>POLLYRUBBER INDUSTRIA S.A.</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>TUBO LONGITUDINAL PL 18" (457MM) SCH XS</t>
+          <t>MANGOTE EM BORRACHA</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
@@ -8755,13 +8753,13 @@
         </is>
       </c>
       <c r="U57" t="n">
-        <v>300253000</v>
+        <v>300255000</v>
       </c>
       <c r="V57" t="n">
-        <v>6000151372</v>
+        <v>6000153440</v>
       </c>
       <c r="W57" s="1" t="n">
-        <v>46118</v>
+        <v>46122</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -8769,7 +8767,7 @@
         </is>
       </c>
       <c r="Y57" t="n">
-        <v>8447.809999999999</v>
+        <v>17498.89</v>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
@@ -8782,7 +8780,7 @@
         </is>
       </c>
       <c r="AB57" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
@@ -8791,8 +8789,8 @@
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>MATERIAL FORA DO PADRAO DE RECEBIMENTO.
-05/06-EMAIL SINALIZANDO 20/04</t>
+          <t>RECUSADO. MATERIAL MEDE 6 METROS E NAO ESTA PALETIZADO.
+05/06-EMAIL SINALIZANDO 14/04</t>
         </is>
       </c>
       <c r="AE57" t="inlineStr">
@@ -8807,7 +8805,7 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>ITABIRITO</t>
+          <t>NOVA LIMA</t>
         </is>
       </c>
       <c r="AH57" t="inlineStr">
@@ -8824,11 +8822,11 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>40141</t>
+          <t>40140</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1189346</v>
+        <v>1190582</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8837,11 +8835,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>TDV São Paulo - SP</t>
+          <t>TDV Ribeirão Preto - SP</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>8718</v>
+        <v>24040</v>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
@@ -8866,7 +8864,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>35260337425216000109550010000087181439991645</t>
+          <t>35260367590265000168550010000240401000081739</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -8876,7 +8874,7 @@
       </c>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="n">
-        <v>4512987386</v>
+        <v>4512862100</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -8889,12 +8887,12 @@
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr">
         <is>
-          <t>ALIANZA TUBOS COMERCIO IMPORTACAO E</t>
+          <t>SANTA RITA SOLUCOES TUBULARES LTDA</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>TUBO DE ACO SC PR N 219,10 X 8,18 NBR 55</t>
+          <t>TUBO LONGITUDINAL PL 18" (457MM) SCH XS</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
@@ -8903,13 +8901,13 @@
         </is>
       </c>
       <c r="U58" t="n">
-        <v>300252000</v>
+        <v>300253000</v>
       </c>
       <c r="V58" t="n">
-        <v>6000153989</v>
+        <v>6000151372</v>
       </c>
       <c r="W58" s="1" t="n">
-        <v>46123</v>
+        <v>46118</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -8917,7 +8915,7 @@
         </is>
       </c>
       <c r="Y58" t="n">
-        <v>4340.34</v>
+        <v>8447.809999999999</v>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
@@ -8940,7 +8938,7 @@
       <c r="AD58" t="inlineStr">
         <is>
           <t>MATERIAL FORA DO PADRAO DE RECEBIMENTO.
-05/06-EMAIL SINALIZANDO 16/04</t>
+05/06-EMAIL SINALIZANDO 20/04</t>
         </is>
       </c>
       <c r="AE58" t="inlineStr">
@@ -8972,11 +8970,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>40142</t>
+          <t>40141</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1189360</v>
+        <v>1189346</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8989,7 +8987,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>8710</v>
+        <v>8718</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
@@ -9014,7 +9012,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>35260337425216000109550010000087101539492332</t>
+          <t>35260337425216000109550010000087181439991645</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -9024,7 +9022,7 @@
       </c>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="n">
-        <v>4512926894</v>
+        <v>4512987386</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -9034,9 +9032,7 @@
       <c r="P59" s="1" t="n">
         <v>46126</v>
       </c>
-      <c r="Q59" s="1" t="n">
-        <v>45562.49097222222</v>
-      </c>
+      <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr">
         <is>
           <t>ALIANZA TUBOS COMERCIO IMPORTACAO E</t>
@@ -9044,7 +9040,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>TUBO DE ACO SC PR N 88,90 X 5,49 A106/06</t>
+          <t>TUBO DE ACO SC PR N 219,10 X 8,18 NBR 55</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
@@ -9056,10 +9052,10 @@
         <v>300252000</v>
       </c>
       <c r="V59" t="n">
-        <v>6000157262</v>
+        <v>6000153989</v>
       </c>
       <c r="W59" s="1" t="n">
-        <v>46135</v>
+        <v>46123</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -9067,7 +9063,7 @@
         </is>
       </c>
       <c r="Y59" t="n">
-        <v>1878.82</v>
+        <v>4340.34</v>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
@@ -9090,7 +9086,7 @@
       <c r="AD59" t="inlineStr">
         <is>
           <t>MATERIAL FORA DO PADRAO DE RECEBIMENTO.
-05/06- EMAIL SINALIZANDO 16/04</t>
+05/06-EMAIL SINALIZANDO 16/04</t>
         </is>
       </c>
       <c r="AE59" t="inlineStr">
@@ -9122,11 +9118,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>40143</t>
+          <t>40142</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1204829</v>
+        <v>1189360</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -9139,7 +9135,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>8756</v>
+        <v>8710</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
@@ -9164,7 +9160,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>35260437425216000109550010000087561735707896</t>
+          <t>35260337425216000109550010000087101539492332</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -9174,7 +9170,7 @@
       </c>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="n">
-        <v>4513007234</v>
+        <v>4512926894</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -9184,7 +9180,9 @@
       <c r="P60" s="1" t="n">
         <v>46126</v>
       </c>
-      <c r="Q60" t="inlineStr"/>
+      <c r="Q60" s="1" t="n">
+        <v>45562.49097222222</v>
+      </c>
       <c r="R60" t="inlineStr">
         <is>
           <t>ALIANZA TUBOS COMERCIO IMPORTACAO E</t>
@@ -9192,7 +9190,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>TUBO DE ACO SC PR N 168,30 X 7,11 A106/0</t>
+          <t>TUBO DE ACO SC PR N 88,90 X 5,49 A106/06</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
@@ -9204,10 +9202,10 @@
         <v>300252000</v>
       </c>
       <c r="V60" t="n">
-        <v>6000153989</v>
+        <v>6000157262</v>
       </c>
       <c r="W60" s="1" t="n">
-        <v>46123</v>
+        <v>46135</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -9215,7 +9213,7 @@
         </is>
       </c>
       <c r="Y60" t="n">
-        <v>2979.3</v>
+        <v>1878.82</v>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
@@ -9237,8 +9235,8 @@
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>MATERIAL FORA DO PADRAODE RECEBIMENTO
-03/06-EMAIL ENVIADO 16/04</t>
+          <t>MATERIAL FORA DO PADRAO DE RECEBIMENTO.
+05/06- EMAIL SINALIZANDO 16/04</t>
         </is>
       </c>
       <c r="AE60" t="inlineStr">
@@ -9270,11 +9268,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>40145</t>
+          <t>40143</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1189344</v>
+        <v>1204829</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -9287,7 +9285,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>8719</v>
+        <v>8756</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
@@ -9312,7 +9310,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>35260337425216000109550010000087191489796495</t>
+          <t>35260437425216000109550010000087561735707896</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -9322,7 +9320,7 @@
       </c>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="n">
-        <v>4512987906</v>
+        <v>4513007234</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -9340,7 +9338,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>TUBO DE ACO SC PR N 168,30 X 7,11 NBR 55</t>
+          <t>TUBO DE ACO SC PR N 168,30 X 7,11 A106/0</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
@@ -9352,10 +9350,10 @@
         <v>300252000</v>
       </c>
       <c r="V61" t="n">
-        <v>6000157262</v>
+        <v>6000153989</v>
       </c>
       <c r="W61" s="1" t="n">
-        <v>46135</v>
+        <v>46123</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -9385,7 +9383,7 @@
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>MATERIAL FORA DO PADRAO DE RECEBIMENTO
+          <t>MATERIAL FORA DO PADRAODE RECEBIMENTO
 03/06-EMAIL ENVIADO 16/04</t>
         </is>
       </c>
@@ -9418,11 +9416,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>40184</t>
+          <t>40145</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1209703</v>
+        <v>1189344</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -9431,11 +9429,11 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>TDV Contagem MG</t>
+          <t>TDV São Paulo - SP</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>80800</v>
+        <v>8719</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
@@ -9460,7 +9458,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>31260326389015000187550010000808001184473414</t>
+          <t>35260337425216000109550010000087191489796495</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -9470,7 +9468,7 @@
       </c>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="n">
-        <v>49276</v>
+        <v>4512987906</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -9478,17 +9476,17 @@
         </is>
       </c>
       <c r="P62" s="1" t="n">
-        <v>46130</v>
+        <v>46126</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr">
         <is>
-          <t>DATA ENGENHARIA LTDA</t>
+          <t>ALIANZA TUBOS COMERCIO IMPORTACAO E</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>CONJUNTO COMPLETO FREIO BFK 458-90-10 16</t>
+          <t>TUBO DE ACO SC PR N 168,30 X 7,11 NBR 55</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
@@ -9497,13 +9495,13 @@
         </is>
       </c>
       <c r="U62" t="n">
-        <v>300255000</v>
+        <v>300252000</v>
       </c>
       <c r="V62" t="n">
-        <v>6000157904</v>
+        <v>6000157262</v>
       </c>
       <c r="W62" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -9511,7 +9509,7 @@
         </is>
       </c>
       <c r="Y62" t="n">
-        <v>100000</v>
+        <v>2979.3</v>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
@@ -9524,7 +9522,7 @@
         </is>
       </c>
       <c r="AB62" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
@@ -9533,8 +9531,8 @@
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>DEVOLUC?O POR FALTA DE MAQUINARIO ESPECIFICO PARA DESCARGA.
-03/06-EMAIL ENVIADO 20/04</t>
+          <t>MATERIAL FORA DO PADRAO DE RECEBIMENTO
+03/06-EMAIL ENVIADO 16/04</t>
         </is>
       </c>
       <c r="AE62" t="inlineStr">
@@ -9549,7 +9547,7 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>OURO PRETO</t>
+          <t>ITABIRITO</t>
         </is>
       </c>
       <c r="AH62" t="inlineStr">
@@ -9566,11 +9564,11 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>40255</t>
+          <t>40176</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1229795</v>
+        <v>1212952</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -9579,11 +9577,11 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>TDV Contagem MG</t>
+          <t>TDV São Paulo - SP</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>33632</v>
+        <v>447301</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
@@ -9608,7 +9606,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>31260402690411000181550010000336321289218606</t>
+          <t>35260349050164000112550010004473011632007547</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -9618,7 +9616,7 @@
       </c>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="n">
-        <v>4101184591</v>
+        <v>4512882197</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -9626,17 +9624,17 @@
         </is>
       </c>
       <c r="P63" s="1" t="n">
-        <v>46140</v>
+        <v>46127</v>
       </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr">
         <is>
-          <t>CITYTUBOS COMERCIO DE TUBOS LTDA</t>
+          <t>SIDER COMERCIAL  INDUSTRIAL LTDA</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>TB PT NBR 5580 3" X 3.35</t>
+          <t>PORCA SEXT 6V8190</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
@@ -9645,21 +9643,21 @@
         </is>
       </c>
       <c r="U63" t="n">
-        <v>300261000</v>
+        <v>300257000</v>
       </c>
       <c r="V63" t="n">
-        <v>6000163297</v>
+        <v>6000154577</v>
       </c>
       <c r="W63" s="1" t="n">
-        <v>46149</v>
+        <v>46126</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>jisantos</t>
+          <t>andias</t>
         </is>
       </c>
       <c r="Y63" t="n">
-        <v>754</v>
+        <v>3.41</v>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
@@ -9672,16 +9670,17 @@
         </is>
       </c>
       <c r="AB63" t="n">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>NF RECUSADA DEVIDO OS TUBOS ESTAREM MAL ACONDICIONADOS EM CIMA DO CAMINH?O, APRESENTANDO RISCO NA DESCARGA.</t>
+          <t>REJEITADO POR DUPLICIDADE DE DOCUMENTO.
+03-06-EMAIL ENVIADO 20/04</t>
         </is>
       </c>
       <c r="AE63" t="inlineStr">
@@ -9696,7 +9695,7 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>NOVA LIMA</t>
+          <t>BRUMADINHO</t>
         </is>
       </c>
       <c r="AH63" t="inlineStr">
@@ -9713,11 +9712,11 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>40292</t>
+          <t>40184</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1229265</v>
+        <v>1209703</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9726,11 +9725,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>TDV São Paulo - SP</t>
+          <t>TDV Contagem MG</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>193261</v>
+        <v>80800</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
@@ -9755,7 +9754,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>35260408624328000190550010001932611011821700</t>
+          <t>31260326389015000187550010000808001184473414</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -9765,7 +9764,7 @@
       </c>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="n">
-        <v>4101177719</v>
+        <v>49276</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -9773,17 +9772,17 @@
         </is>
       </c>
       <c r="P64" s="1" t="n">
-        <v>46141</v>
+        <v>46130</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr">
         <is>
-          <t>DINAMICA MATERIAIS HIDRAULICOS LTD</t>
+          <t>DATA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>TUBO DE COND A/C PRETO C/C NBR-5580 M X</t>
+          <t>CONJUNTO COMPLETO FREIO BFK 458-90-10 16</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
@@ -9792,13 +9791,13 @@
         </is>
       </c>
       <c r="U64" t="n">
-        <v>300264000</v>
+        <v>300255000</v>
       </c>
       <c r="V64" t="n">
-        <v>6000163804</v>
+        <v>6000157904</v>
       </c>
       <c r="W64" s="1" t="n">
-        <v>46150</v>
+        <v>46134</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -9806,7 +9805,7 @@
         </is>
       </c>
       <c r="Y64" t="n">
-        <v>1010.2</v>
+        <v>100000</v>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
@@ -9819,7 +9818,7 @@
         </is>
       </c>
       <c r="AB64" t="n">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
@@ -9828,8 +9827,8 @@
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>MATERIAL N?O ESTA PALETIZADO E AMARRADO.
-06/085-EMAIL SINALIZADO AGUARDANDO RETORNO</t>
+          <t>DEVOLUC?O POR FALTA DE MAQUINARIO ESPECIFICO PARA DESCARGA.
+03/06-EMAIL ENVIADO 20/04</t>
         </is>
       </c>
       <c r="AE64" t="inlineStr">
@@ -9844,7 +9843,7 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>NOVA LIMA</t>
+          <t>OURO PRETO</t>
         </is>
       </c>
       <c r="AH64" t="inlineStr">
@@ -9861,11 +9860,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>40346</t>
+          <t>40255</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1232626</v>
+        <v>1229795</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9874,11 +9873,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>TDV Piracicaba - SP</t>
+          <t>TDV Contagem MG</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>216683</v>
+        <v>33632</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
@@ -9903,7 +9902,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>35260351482776000126550020002166831840679534</t>
+          <t>31260402690411000181550010000336321289218606</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -9913,7 +9912,7 @@
       </c>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="n">
-        <v>4101161955</v>
+        <v>4101184591</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -9921,17 +9920,17 @@
         </is>
       </c>
       <c r="P65" s="1" t="n">
-        <v>46150</v>
+        <v>46140</v>
       </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr">
         <is>
-          <t>IMBIL INDUSTRIA E MANUTENCAO DE BOM</t>
+          <t>CITYTUBOS COMERCIO DE TUBOS LTDA</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>BOMBA IS-M/G 300X250 AE M6 (BOCAL DE DES</t>
+          <t>TB PT NBR 5580 3" X 3.35</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
@@ -9940,21 +9939,21 @@
         </is>
       </c>
       <c r="U65" t="n">
-        <v>300271000</v>
+        <v>300261000</v>
       </c>
       <c r="V65" t="n">
-        <v>6000163740</v>
+        <v>6000163297</v>
       </c>
       <c r="W65" s="1" t="n">
         <v>46149</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>andias</t>
+          <t>jisantos</t>
         </is>
       </c>
       <c r="Y65" t="n">
-        <v>300000</v>
+        <v>754</v>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
@@ -9967,17 +9966,16 @@
         </is>
       </c>
       <c r="AB65" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>MATERIAL RECUSADO ESTA VINCULADO A NF ,POIS O PEDIDO FOI GERADO POR SOLICITACAO DO CHAMADO,PARA REGULARIZAR O RECEBIMENTO DA NOTA 205858 DO PEDIDO 4101048986 QUE APRESENTOU ERRO.
-13/05-EMAIL ENVIADO AGUARDANDO RETORNO, ULTIMA COBRANCA 02/06</t>
+          <t>NF RECUSADA DEVIDO OS TUBOS ESTAREM MAL ACONDICIONADOS EM CIMA DO CAMINH?O, APRESENTANDO RISCO NA DESCARGA.</t>
         </is>
       </c>
       <c r="AE65" t="inlineStr">
@@ -10009,11 +10007,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>40517</t>
+          <t>40292</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>528188</v>
+        <v>1229265</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -10022,11 +10020,11 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>TDV Contagem MG</t>
+          <t>TDV São Paulo - SP</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>21819</v>
+        <v>193261</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
@@ -10051,7 +10049,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>31250871442115000184550010000218191282682886</t>
+          <t>35260408624328000190550010001932611011821700</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -10061,7 +10059,7 @@
       </c>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="n">
-        <v>4512216187</v>
+        <v>4101177719</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -10069,17 +10067,17 @@
         </is>
       </c>
       <c r="P66" s="1" t="n">
-        <v>46167</v>
+        <v>46141</v>
       </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr">
         <is>
-          <t>SIMAO SERGIO RIBEIRO</t>
+          <t>DINAMICA MATERIAIS HIDRAULICOS LTD</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>THINNER ANJO ECO 5L</t>
+          <t>TUBO DE COND A/C PRETO C/C NBR-5580 M X</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
@@ -10088,21 +10086,21 @@
         </is>
       </c>
       <c r="U66" t="n">
-        <v>300109000</v>
+        <v>300264000</v>
       </c>
       <c r="V66" t="n">
-        <v>6000170950</v>
+        <v>6000163804</v>
       </c>
       <c r="W66" s="1" t="n">
-        <v>46165</v>
+        <v>46150</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>lgsantos</t>
+          <t>andias</t>
         </is>
       </c>
       <c r="Y66" t="n">
-        <v>1057.85</v>
+        <v>1010.2</v>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
@@ -10115,17 +10113,17 @@
         </is>
       </c>
       <c r="AB66" t="n">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>FORA DO PASSAPORTE. MOTORISTA: JEFERSON SILVA. PLACA: SUP4E70 // 
-EM TRATATIVA JUNTO AO PVV @ANDREZA.</t>
+          <t>MATERIAL N?O ESTA PALETIZADO E AMARRADO.
+06/085-EMAIL SINALIZADO AGUARDANDO RETORNO</t>
         </is>
       </c>
       <c r="AE66" t="inlineStr">
@@ -10140,7 +10138,7 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>OURO PRETO</t>
+          <t>NOVA LIMA</t>
         </is>
       </c>
       <c r="AH66" t="inlineStr">
@@ -10157,11 +10155,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>40625</t>
+          <t>40346</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1336063</v>
+        <v>1232626</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -10170,11 +10168,11 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>TDV Araquari - SC</t>
+          <t>TDV Piracicaba - SP</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>33434</v>
+        <v>216683</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
@@ -10199,7 +10197,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>42260510507244000119550010000334341729345220</t>
+          <t>35260351482776000126550020002166831840679534</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -10209,7 +10207,7 @@
       </c>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="n">
-        <v>4101172639</v>
+        <v>4101161955</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -10217,17 +10215,17 @@
         </is>
       </c>
       <c r="P67" s="1" t="n">
-        <v>46177</v>
+        <v>46150</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr">
         <is>
-          <t>BAHER INDUSTRIA E COMERCIO DE MAQUI</t>
+          <t>IMBIL INDUSTRIA E MANUTENCAO DE BOM</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>CONSOLE TECNICO ERGONOMICO BAHER LINHA P</t>
+          <t>BOMBA IS-M/G 300X250 AE M6 (BOCAL DE DES</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
@@ -10236,13 +10234,13 @@
         </is>
       </c>
       <c r="U67" t="n">
-        <v>300286000</v>
+        <v>300271000</v>
       </c>
       <c r="V67" t="n">
-        <v>6000173962</v>
+        <v>6000163740</v>
       </c>
       <c r="W67" s="1" t="n">
-        <v>46174</v>
+        <v>46149</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -10250,7 +10248,7 @@
         </is>
       </c>
       <c r="Y67" t="n">
-        <v>203203.39</v>
+        <v>300000</v>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
@@ -10263,17 +10261,17 @@
         </is>
       </c>
       <c r="AB67" t="n">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>MATERIAL RECUSADO POR SER MAIOR DO QUE A EMPILHADEIRA PODE PEGAR IMPEDINDO A DESCARGA DO MESMO NO LOCAL DE ENTREGA.
-09/06 - E-MAIL ENVIADO .</t>
+          <t>MATERIAL RECUSADO ESTA VINCULADO A NF ,POIS O PEDIDO FOI GERADO POR SOLICITACAO DO CHAMADO,PARA REGULARIZAR O RECEBIMENTO DA NOTA 205858 DO PEDIDO 4101048986 QUE APRESENTOU ERRO.
+13/05-EMAIL ENVIADO AGUARDANDO RETORNO, ULTIMA COBRANCA 02/06</t>
         </is>
       </c>
       <c r="AE67" t="inlineStr">
@@ -10305,11 +10303,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>40703</t>
+          <t>40517</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1375700</v>
+        <v>528188</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -10322,7 +10320,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2890</v>
+        <v>21819</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
@@ -10347,7 +10345,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>31260305896430000157550010000028901000206644</t>
+          <t>31250871442115000184550010000218191282682886</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -10357,7 +10355,7 @@
       </c>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="n">
-        <v>4101155100</v>
+        <v>4512216187</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -10365,17 +10363,17 @@
         </is>
       </c>
       <c r="P68" s="1" t="n">
-        <v>46184</v>
+        <v>46167</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr">
         <is>
-          <t>TECNOFUSOS INDUSTRIA E COMERCIO LTD</t>
+          <t>SIMAO SERGIO RIBEIRO</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>Parafuso Cab.Sextavada M48 x 360mm R.P 1</t>
+          <t>THINNER ANJO ECO 5L</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
@@ -10384,21 +10382,21 @@
         </is>
       </c>
       <c r="U68" t="n">
-        <v>300292000</v>
+        <v>300109000</v>
       </c>
       <c r="V68" t="n">
-        <v>6000182432</v>
+        <v>6000170950</v>
       </c>
       <c r="W68" s="1" t="n">
-        <v>46196</v>
+        <v>46165</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>andias</t>
+          <t>lgsantos</t>
         </is>
       </c>
       <c r="Y68" t="n">
-        <v>2495</v>
+        <v>1057.85</v>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
@@ -10411,7 +10409,7 @@
         </is>
       </c>
       <c r="AB68" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
@@ -10420,8 +10418,8 @@
       </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>NOTA INAPTA. MOTORISTA CLEBER EUSTAQUIO. PLACA: QKO1D40.
-17/06 AGUARDANDO RETORNO VALE.</t>
+          <t>FORA DO PASSAPORTE. MOTORISTA: JEFERSON SILVA. PLACA: SUP4E70 // 
+EM TRATATIVA JUNTO AO PVV @ANDREZA.</t>
         </is>
       </c>
       <c r="AE68" t="inlineStr">
@@ -10453,11 +10451,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>40740</t>
+          <t>40625</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1349525</v>
+        <v>1336063</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -10466,11 +10464,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>TDV Rio de Janeiro - RJ</t>
+          <t>TDV Araquari - SC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1112110</v>
+        <v>33434</v>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
@@ -10495,7 +10493,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>33260550567288000744550040011121101168473870</t>
+          <t>42260510507244000119550010000334341729345220</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -10505,7 +10503,7 @@
       </c>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="n">
-        <v>4513076977</v>
+        <v>4101172639</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -10513,17 +10511,17 @@
         </is>
       </c>
       <c r="P69" s="1" t="n">
-        <v>46190</v>
+        <v>46177</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr">
         <is>
-          <t>SOCIEDADE MICHELIN DE PARTICIPACOES</t>
+          <t>BAHER INDUSTRIA E COMERCIO DE MAQUI</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>PNEU 29.5R</t>
+          <t>CONSOLE TECNICO ERGONOMICO BAHER LINHA P</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
@@ -10532,21 +10530,21 @@
         </is>
       </c>
       <c r="U69" t="n">
-        <v>300296000</v>
+        <v>300286000</v>
       </c>
       <c r="V69" t="n">
-        <v>6000179557</v>
+        <v>6000173962</v>
       </c>
       <c r="W69" s="1" t="n">
-        <v>46189</v>
+        <v>46174</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>mvssilva</t>
+          <t>andias</t>
         </is>
       </c>
       <c r="Y69" t="n">
-        <v>117821.86</v>
+        <v>203203.39</v>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
@@ -10559,7 +10557,7 @@
         </is>
       </c>
       <c r="AB69" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
@@ -10568,7 +10566,8 @@
       </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>NOTA FISCAL RECUSADA, MATERIAL PAROU DO CENTRO 4143 DEVE SER ENTREGUE NA AREA.</t>
+          <t>MATERIAL RECUSADO POR SER MAIOR DO QUE A EMPILHADEIRA PODE PEGAR IMPEDINDO A DESCARGA DO MESMO NO LOCAL DE ENTREGA.
+09/06 - E-MAIL ENVIADO .</t>
         </is>
       </c>
       <c r="AE69" t="inlineStr">
@@ -10600,11 +10599,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>40741</t>
+          <t>40703</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1084585</v>
+        <v>1375700</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -10613,11 +10612,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>TDV Rio de Janeiro - RJ</t>
+          <t>TDV Contagem MG</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1098397</v>
+        <v>2890</v>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
@@ -10642,7 +10641,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>33260250567288000744550040010983971165237497</t>
+          <t>31260305896430000157550010000028901000206644</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -10652,7 +10651,7 @@
       </c>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="n">
-        <v>4142886970</v>
+        <v>4101155100</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -10660,17 +10659,17 @@
         </is>
       </c>
       <c r="P70" s="1" t="n">
-        <v>46190</v>
+        <v>46184</v>
       </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr">
         <is>
-          <t>SOCIEDADE MICHELIN DE PARTICIPACOES</t>
+          <t>TECNOFUSOS INDUSTRIA E COMERCIO LTD</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>PNEU 24</t>
+          <t>Parafuso Cab.Sextavada M48 x 360mm R.P 1</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
@@ -10679,21 +10678,21 @@
         </is>
       </c>
       <c r="U70" t="n">
-        <v>300290000</v>
+        <v>300292000</v>
       </c>
       <c r="V70" t="n">
-        <v>6000175263</v>
+        <v>6000182432</v>
       </c>
       <c r="W70" s="1" t="n">
-        <v>46176</v>
+        <v>46196</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>mvssilva</t>
+          <t>andias</t>
         </is>
       </c>
       <c r="Y70" t="n">
-        <v>71242.55</v>
+        <v>2495</v>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
@@ -10706,16 +10705,17 @@
         </is>
       </c>
       <c r="AB70" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="AD70" t="inlineStr">
         <is>
-          <t>NOTA FISCAL RECUSA, MATERIAL PNEUS DO CENTRO 4143 DEVE SER ENTREGUE NA AREA.</t>
+          <t>NOTA INAPTA. MOTORISTA CLEBER EUSTAQUIO. PLACA: QKO1D40.
+17/06 AGUARDANDO RETORNO VALE.</t>
         </is>
       </c>
       <c r="AE70" t="inlineStr">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>NOVA LIMA</t>
+          <t>OURO PRETO</t>
         </is>
       </c>
       <c r="AH70" t="inlineStr">
@@ -10747,11 +10747,11 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>40745</t>
+          <t>40740</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1378572</v>
+        <v>1349525</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -10760,11 +10760,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>TDV São Paulo - SP</t>
+          <t>TDV Rio de Janeiro - RJ</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1343784</v>
+        <v>1112110</v>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>35260644357085001026550010013437841317059860</t>
+          <t>33260550567288000744550040011121101168473870</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="n">
-        <v>4513161671</v>
+        <v>4513076977</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -10812,12 +10812,12 @@
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr">
         <is>
-          <t>HIDRAU TORQUE INDUSTRIA COMERCIO IM</t>
+          <t>SOCIEDADE MICHELIN DE PARTICIPACOES</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>15252779-PNEU SUPORTE LEVE 23.5-25</t>
+          <t>PNEU 29.5R</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
@@ -10829,18 +10829,18 @@
         <v>300296000</v>
       </c>
       <c r="V71" t="n">
-        <v>6000179485</v>
+        <v>6000179557</v>
       </c>
       <c r="W71" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>allana</t>
+          <t>mvssilva</t>
         </is>
       </c>
       <c r="Y71" t="n">
-        <v>126311.62</v>
+        <v>117821.86</v>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
@@ -10862,12 +10862,12 @@
       </c>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>NOTA RECUSADA MATERIAL COM CENTRO DE HZT KIT DEVE SER ENTREGUE NA AREA .</t>
+          <t>NOTA FISCAL RECUSADA, MATERIAL PAROU DO CENTRO 4143 DEVE SER ENTREGUE NA AREA.</t>
         </is>
       </c>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>CONTAGEM/MG</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
@@ -10894,11 +10894,11 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>40751</t>
+          <t>40741</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1369066</v>
+        <v>1084585</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10907,11 +10907,11 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>TDV Contagem MG</t>
+          <t>TDV Rio de Janeiro - RJ</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>26006</v>
+        <v>1098397</v>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>31260332651494000160550000000260061731636280</t>
+          <t>33260250567288000744550040010983971165237497</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -10946,7 +10946,7 @@
       </c>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="n">
-        <v>4101177871</v>
+        <v>4142886970</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -10954,17 +10954,17 @@
         </is>
       </c>
       <c r="P72" s="1" t="n">
-        <v>46191</v>
+        <v>46190</v>
       </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr">
         <is>
-          <t>UNIUN EQUIPAMENTOS E FERRAMENTAS MR</t>
+          <t>SOCIEDADE MICHELIN DE PARTICIPACOES</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>SOQUETE SEXTAVADO IMPACTO   3/4 X 1/4</t>
+          <t>PNEU 24</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
@@ -10973,21 +10973,21 @@
         </is>
       </c>
       <c r="U72" t="n">
-        <v>300292000</v>
+        <v>300290000</v>
       </c>
       <c r="V72" t="n">
-        <v>6000181699</v>
+        <v>6000175263</v>
       </c>
       <c r="W72" s="1" t="n">
-        <v>46193</v>
+        <v>46176</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>rfernanso</t>
+          <t>mvssilva</t>
         </is>
       </c>
       <c r="Y72" t="n">
-        <v>12574.4</v>
+        <v>71242.55</v>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
@@ -11000,21 +11000,21 @@
         </is>
       </c>
       <c r="AB72" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="AD72" t="inlineStr">
         <is>
-          <t>NOTA FISCAL FORA DO PASSAPORTE. MOTORISTA: CLEBER EUSTAQUIO. PLACA:QKO1D40.</t>
+          <t>NOTA FISCAL RECUSA, MATERIAL PNEUS DO CENTRO 4143 DEVE SER ENTREGUE NA AREA.</t>
         </is>
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>CONTAGEM/MG</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>OURO PRETO</t>
+          <t>NOVA LIMA</t>
         </is>
       </c>
       <c r="AH72" t="inlineStr">
@@ -11041,11 +11041,11 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>40767</t>
+          <t>40745</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1378634</v>
+        <v>1378572</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -11054,11 +11054,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>TDV Araquari - SC</t>
+          <t>TDV São Paulo - SP</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>18686</v>
+        <v>1343784</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
@@ -11083,7 +11083,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>42260542284562000235550010000186861021484450</t>
+          <t>35260644357085001026550010013437841317059860</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -11093,7 +11093,7 @@
       </c>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="n">
-        <v>4512914217</v>
+        <v>4513161671</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -11101,17 +11101,17 @@
         </is>
       </c>
       <c r="P73" s="1" t="n">
-        <v>46192</v>
+        <v>46190</v>
       </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr">
         <is>
-          <t>PLASSER DO BRASIL COMERCIO IND E RE</t>
+          <t>HIDRAU TORQUE INDUSTRIA COMERCIO IM</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>61.04.212 PINO DE CORRENTE</t>
+          <t>15252779-PNEU SUPORTE LEVE 23.5-25</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
@@ -11120,21 +11120,21 @@
         </is>
       </c>
       <c r="U73" t="n">
-        <v>300294000</v>
+        <v>300296000</v>
       </c>
       <c r="V73" t="n">
-        <v>6000179064</v>
+        <v>6000179485</v>
       </c>
       <c r="W73" s="1" t="n">
-        <v>46186</v>
+        <v>46188</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>rfernanso</t>
+          <t>allana</t>
         </is>
       </c>
       <c r="Y73" t="n">
-        <v>23032.76</v>
+        <v>126311.62</v>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
@@ -11147,16 +11147,16 @@
         </is>
       </c>
       <c r="AB73" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>MATERIAL DE 160KG FOI EM VEICULO DE PASSEIO ONDE N?O FOI POSSIVEL OPERAR COM A EMPILHADEIRA. MOTORISTA:ANTONIO CELIO. PLACA:QWY9G87.</t>
+          <t>NOTA RECUSADA MATERIAL COM CENTRO DE HZT KIT DEVE SER ENTREGUE NA AREA .</t>
         </is>
       </c>
       <c r="AE73" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>GOVERNADOR VALADARES</t>
+          <t>NOVA LIMA</t>
         </is>
       </c>
       <c r="AH73" t="inlineStr">
@@ -11188,11 +11188,11 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>40774</t>
+          <t>40751</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1057514</v>
+        <v>1369066</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -11201,11 +11201,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>TDV Piracicaba - SP</t>
+          <t>TDV Contagem MG</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>18714</v>
+        <v>26006</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>35260229514960000151550010000187141118292253</t>
+          <t>31260332651494000160550000000260061731636280</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -11239,24 +11239,26 @@
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+      <c r="N74" t="n">
+        <v>4101177871</v>
+      </c>
       <c r="O74" t="inlineStr">
         <is>
           <t>CONTAGEM</t>
         </is>
       </c>
       <c r="P74" s="1" t="n">
-        <v>46193</v>
+        <v>46191</v>
       </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr">
         <is>
-          <t>BRG INDUSTRIA E COMERCIO DE MANCAIS</t>
+          <t>UNIUN EQUIPAMENTOS E FERRAMENTAS MR</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>SERVIÇO DE TRANSPORTE</t>
+          <t>SOQUETE SEXTAVADO IMPACTO   3/4 X 1/4</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
@@ -11265,13 +11267,13 @@
         </is>
       </c>
       <c r="U74" t="n">
-        <v>300223000</v>
+        <v>300292000</v>
       </c>
       <c r="V74" t="n">
-        <v>6000133073</v>
+        <v>6000181699</v>
       </c>
       <c r="W74" s="1" t="n">
-        <v>46073</v>
+        <v>46193</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -11279,7 +11281,7 @@
         </is>
       </c>
       <c r="Y74" t="n">
-        <v>2915.84</v>
+        <v>12574.4</v>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
@@ -11292,7 +11294,7 @@
         </is>
       </c>
       <c r="AB74" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
@@ -11301,7 +11303,7 @@
       </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>FORA DO PASSAPORTE. MOTORISTA:FRANCISCO GERALDO. PLACA:OQP1E86.</t>
+          <t>NOTA FISCAL FORA DO PASSAPORTE. MOTORISTA: CLEBER EUSTAQUIO. PLACA:QKO1D40.</t>
         </is>
       </c>
       <c r="AE74" t="inlineStr">
@@ -11316,7 +11318,7 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>CONGONHAS</t>
+          <t>OURO PRETO</t>
         </is>
       </c>
       <c r="AH74" t="inlineStr">
@@ -11333,11 +11335,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>40775</t>
+          <t>40767</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1386712</v>
+        <v>1378634</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -11346,16 +11348,16 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>TDV Rio de Janeiro - RJ</t>
+          <t>TDV Araquari - SC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>98955</v>
+        <v>18686</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>LOTACAO</t>
+          <t>FRACIONADO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -11375,7 +11377,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>31260633592510044798550030000989551114967957</t>
+          <t>42260542284562000235550010000186861021484450</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -11385,7 +11387,7 @@
       </c>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="n">
-        <v>4512896531</v>
+        <v>4512914217</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -11393,17 +11395,17 @@
         </is>
       </c>
       <c r="P75" s="1" t="n">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr">
         <is>
-          <t>DIVERSOS</t>
+          <t>PLASSER DO BRASIL COMERCIO IND E RE</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>CORREIA T</t>
+          <t>61.04.212 PINO DE CORRENTE</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
@@ -11412,21 +11414,21 @@
         </is>
       </c>
       <c r="U75" t="n">
-        <v>300295000</v>
+        <v>300294000</v>
       </c>
       <c r="V75" t="n">
-        <v>6000178553</v>
+        <v>6000179064</v>
       </c>
       <c r="W75" s="1" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>mvssilva</t>
+          <t>rfernanso</t>
         </is>
       </c>
       <c r="Y75" t="n">
-        <v>25654.52</v>
+        <v>23032.76</v>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
@@ -11439,7 +11441,7 @@
         </is>
       </c>
       <c r="AB75" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
@@ -11448,12 +11450,12 @@
       </c>
       <c r="AD75" t="inlineStr">
         <is>
-          <t>ESTOQUE EM S?O GONCALO DO RIO ABAIXO ( BRUCUTU )</t>
+          <t>MATERIAL DE 160KG FOI EM VEICULO DE PASSEIO ONDE N?O FOI POSSIVEL OPERAR COM A EMPILHADEIRA. MOTORISTA:ANTONIO CELIO. PLACA:QWY9G87.</t>
         </is>
       </c>
       <c r="AE75" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>CONTAGEM/MG</t>
         </is>
       </c>
       <c r="AF75" t="inlineStr">
@@ -11463,7 +11465,7 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>SAO GONCALO DO RIO ABAIXO</t>
+          <t>GOVERNADOR VALADARES</t>
         </is>
       </c>
       <c r="AH75" t="inlineStr">
@@ -11480,11 +11482,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>40793</t>
+          <t>40774</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1388729</v>
+        <v>1057514</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -11493,11 +11495,11 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>TDV São Paulo - SP</t>
+          <t>TDV Piracicaba - SP</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>19925</v>
+        <v>18714</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
@@ -11522,7 +11524,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>35260604483719000181550010000199251540262338</t>
+          <t>35260229514960000151550010000187141118292253</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -11538,17 +11540,17 @@
         </is>
       </c>
       <c r="P76" s="1" t="n">
-        <v>46195</v>
+        <v>46193</v>
       </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr">
         <is>
-          <t>TRILHOS FERROVIARIOS LTDA</t>
+          <t>BRG INDUSTRIA E COMERCIO DE MANCAIS</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>TRILHOS</t>
+          <t>SERVIÇO DE TRANSPORTE</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
@@ -11557,13 +11559,13 @@
         </is>
       </c>
       <c r="U76" t="n">
-        <v>300294000</v>
+        <v>300223000</v>
       </c>
       <c r="V76" t="n">
-        <v>6000181110</v>
+        <v>6000133073</v>
       </c>
       <c r="W76" s="1" t="n">
-        <v>46196</v>
+        <v>46073</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -11571,7 +11573,7 @@
         </is>
       </c>
       <c r="Y76" t="n">
-        <v>44492.85</v>
+        <v>2915.84</v>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
@@ -11584,16 +11586,16 @@
         </is>
       </c>
       <c r="AB76" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>MATERIAL SEM CONDIC?ES DE DESCARGA NO ARMAZEM DE BAR?O. MOTORISTA: WEBERT SILVIO JUNIO APARECIDO.PLACA:QQT0C42.</t>
+          <t>FORA DO PASSAPORTE. MOTORISTA:FRANCISCO GERALDO. PLACA:OQP1E86.</t>
         </is>
       </c>
       <c r="AE76" t="inlineStr">
@@ -11608,7 +11610,7 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>BARAO DE COCAIS</t>
+          <t>CONGONHAS</t>
         </is>
       </c>
       <c r="AH76" t="inlineStr">
@@ -11625,11 +11627,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>40814</t>
+          <t>40775</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1385757</v>
+        <v>1386712</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -11638,16 +11640,16 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>TDV São Paulo - SP</t>
+          <t>TDV Rio de Janeiro - RJ</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>17236</v>
+        <v>98955</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>FRACIONADO</t>
+          <t>LOTACAO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -11667,7 +11669,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>35260604552842000107550010000172361019303890</t>
+          <t>31260633592510044798550030000989551114967957</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -11677,7 +11679,7 @@
       </c>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="n">
-        <v>4513210303</v>
+        <v>4512896531</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
@@ -11685,17 +11687,17 @@
         </is>
       </c>
       <c r="P77" s="1" t="n">
-        <v>46196</v>
+        <v>46193</v>
       </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr">
         <is>
-          <t>POWER MASTER - TECNOLOGIA EM ACIONA</t>
+          <t>DIVERSOS</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>ELEMENTO ELASTICO E97</t>
+          <t>CORREIA T</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
@@ -11704,21 +11706,21 @@
         </is>
       </c>
       <c r="U77" t="n">
-        <v>300294000</v>
+        <v>300295000</v>
       </c>
       <c r="V77" t="n">
-        <v>6000181114</v>
+        <v>6000178553</v>
       </c>
       <c r="W77" s="1" t="n">
-        <v>46196</v>
+        <v>46185</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>rfernanso</t>
+          <t>mvssilva</t>
         </is>
       </c>
       <c r="Y77" t="n">
-        <v>210.97</v>
+        <v>25654.52</v>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
@@ -11731,7 +11733,7 @@
         </is>
       </c>
       <c r="AB77" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
@@ -11740,12 +11742,12 @@
       </c>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>FORA DO PASSAPORTE. MOTORISTA:ELI TOMAZ. PVV8D31.</t>
+          <t>ESTOQUE EM S?O GONCALO DO RIO ABAIXO ( BRUCUTU )</t>
         </is>
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>CONTAGEM/MG</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
@@ -11755,7 +11757,7 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>OURO PRETO</t>
+          <t>SAO GONCALO DO RIO ABAIXO</t>
         </is>
       </c>
       <c r="AH77" t="inlineStr">
@@ -11772,11 +11774,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>40830</t>
+          <t>40793</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1400589</v>
+        <v>1388729</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -11785,11 +11787,11 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>TDV Contagem MG</t>
+          <t>TDV São Paulo - SP</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>165499</v>
+        <v>19925</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
@@ -11814,7 +11816,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>31260602226707000146550010001654991335925103</t>
+          <t>35260604483719000181550010000199251540262338</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -11823,26 +11825,24 @@
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" t="n">
-        <v>4513140471</v>
-      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr">
         <is>
           <t>CONTAGEM</t>
         </is>
       </c>
       <c r="P78" s="1" t="n">
-        <v>46197</v>
+        <v>46195</v>
       </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr">
         <is>
-          <t>PIPE SISTEMAS TUBULARES LTDA</t>
+          <t>TRILHOS FERROVIARIOS LTDA</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>TUBO PIPE COR AC-40  368 X  4,75 X  6000</t>
+          <t>TRILHOS</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -11851,21 +11851,21 @@
         </is>
       </c>
       <c r="U78" t="n">
-        <v>300299000</v>
+        <v>300294000</v>
       </c>
       <c r="V78" t="n">
-        <v>6000182526</v>
+        <v>6000181110</v>
       </c>
       <c r="W78" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>mvssilva</t>
+          <t>rfernanso</t>
         </is>
       </c>
       <c r="Y78" t="n">
-        <v>23160.83</v>
+        <v>44492.85</v>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         </is>
       </c>
       <c r="AB78" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
@@ -11887,12 +11887,12 @@
       </c>
       <c r="AD78" t="inlineStr">
         <is>
-          <t>FOI ALINHADO ENTRE USUARIO (BRENO LOPES) COM A DELLA VOLPE QUE ESSES TUBOS TEM QUE SER DIRETO NA AREA PARA RECEBIMENTO.CARGA LOTACAO.</t>
+          <t>MATERIAL SEM CONDIC?ES DE DESCARGA NO ARMAZEM DE BAR?O. MOTORISTA: WEBERT SILVIO JUNIO APARECIDO.PLACA:QQT0C42.</t>
         </is>
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>CONTAGEM/MG</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>NOVA LIMA</t>
+          <t>BARAO DE COCAIS</t>
         </is>
       </c>
       <c r="AH78" t="inlineStr">
@@ -11919,11 +11919,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>40839</t>
+          <t>40814</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1398444</v>
+        <v>1385757</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>20049</v>
+        <v>17236</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>35260457281743000102550010000200491151212390</t>
+          <t>35260604552842000107550010000172361019303890</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -11971,7 +11971,7 @@
       </c>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="n">
-        <v>4101153628</v>
+        <v>4513210303</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -11979,17 +11979,17 @@
         </is>
       </c>
       <c r="P79" s="1" t="n">
-        <v>46198</v>
+        <v>46196</v>
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr">
         <is>
-          <t>A EXPONENCIAL ESTANTES E MOVEIS DE</t>
+          <t>POWER MASTER - TECNOLOGIA EM ACIONA</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>AC ARMARIO RECI</t>
+          <t>ELEMENTO ELASTICO E97</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
@@ -11998,21 +11998,21 @@
         </is>
       </c>
       <c r="U79" t="n">
-        <v>300297000</v>
+        <v>300294000</v>
       </c>
       <c r="V79" t="n">
-        <v>6000182520</v>
+        <v>6000181114</v>
       </c>
       <c r="W79" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>mvssilva</t>
+          <t>rfernanso</t>
         </is>
       </c>
       <c r="Y79" t="n">
-        <v>13110</v>
+        <v>210.97</v>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         </is>
       </c>
       <c r="AB79" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
@@ -12034,12 +12034,12 @@
       </c>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>NOTA FISCAL INAPTA.</t>
+          <t>FORA DO PASSAPORTE. MOTORISTA:ELI TOMAZ. PVV8D31.</t>
         </is>
       </c>
       <c r="AE79" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>CONTAGEM/MG</t>
         </is>
       </c>
       <c r="AF79" t="inlineStr">
@@ -12049,7 +12049,7 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>MARIANA</t>
+          <t>OURO PRETO</t>
         </is>
       </c>
       <c r="AH79" t="inlineStr">
@@ -12066,11 +12066,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>40846</t>
+          <t>40830</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1389618</v>
+        <v>1400589</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -12079,11 +12079,11 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>TDV Serra- ES</t>
+          <t>TDV Contagem MG</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1569225</v>
+        <v>165499</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
@@ -12108,7 +12108,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>32260646044053004607550010015692251038241990</t>
+          <t>31260602226707000146550010001654991335925103</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="n">
-        <v>4513192045</v>
+        <v>4513140471</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -12126,17 +12126,17 @@
         </is>
       </c>
       <c r="P80" s="1" t="n">
-        <v>46199</v>
+        <v>46197</v>
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr">
         <is>
-          <t>NORTEL SUPRIMENTOS INDUSTRIAIS S/A</t>
+          <t>PIPE SISTEMAS TUBULARES LTDA</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>CHAVE DESALIN ROL 500V 2NA+2NF ZV12H500</t>
+          <t>TUBO PIPE COR AC-40  368 X  4,75 X  6000</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
@@ -12145,21 +12145,21 @@
         </is>
       </c>
       <c r="U80" t="n">
-        <v>300300000</v>
+        <v>300299000</v>
       </c>
       <c r="V80" t="n">
-        <v>6000182508</v>
+        <v>6000182526</v>
       </c>
       <c r="W80" s="1" t="n">
         <v>46195</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>andias</t>
+          <t>mvssilva</t>
         </is>
       </c>
       <c r="Y80" t="n">
-        <v>1629.84</v>
+        <v>23160.83</v>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
@@ -12172,17 +12172,16 @@
         </is>
       </c>
       <c r="AB80" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="AD80" t="inlineStr">
         <is>
-          <t>NAO RECEBIDO, NF FORA DO PASSAPORTE.
-13/07 - NOTA INAPTA EMAIL ENVIADO .</t>
+          <t>FOI ALINHADO ENTRE USUARIO (BRENO LOPES) COM A DELLA VOLPE QUE ESSES TUBOS TEM QUE SER DIRETO NA AREA PARA RECEBIMENTO.CARGA LOTACAO.</t>
         </is>
       </c>
       <c r="AE80" t="inlineStr">
@@ -12197,7 +12196,7 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>OURO PRETO</t>
+          <t>NOVA LIMA</t>
         </is>
       </c>
       <c r="AH80" t="inlineStr">
@@ -12214,21 +12213,31 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>40871</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
+          <t>40839</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1398444</v>
+      </c>
       <c r="C81" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>TDV São Paulo - SP</t>
+        </is>
+      </c>
       <c r="E81" t="n">
-        <v>52773</v>
+        <v>20049</v>
       </c>
       <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>FRACIONADO</t>
+        </is>
+      </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -12246,7 +12255,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>35260601236739000160550010000527731100079220</t>
+          <t>35260457281743000102550010000200491151212390</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -12255,37 +12264,49 @@
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+      <c r="N81" t="n">
+        <v>4101153628</v>
+      </c>
       <c r="O81" t="inlineStr">
         <is>
           <t>CONTAGEM</t>
         </is>
       </c>
       <c r="P81" s="1" t="n">
-        <v>46203</v>
+        <v>46198</v>
       </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr">
         <is>
-          <t>ALMONT DO BRASIL IMPORTACAO COM E R</t>
-        </is>
-      </c>
-      <c r="S81" t="inlineStr"/>
+          <t>A EXPONENCIAL ESTANTES E MOVEIS DE</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>AC ARMARIO RECI</t>
+        </is>
+      </c>
       <c r="T81" t="inlineStr">
         <is>
           <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr"/>
-      <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr"/>
+      <c r="U81" t="n">
+        <v>300297000</v>
+      </c>
+      <c r="V81" t="n">
+        <v>6000182520</v>
+      </c>
+      <c r="W81" s="1" t="n">
+        <v>46195</v>
+      </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>allana</t>
+          <t>mvssilva</t>
         </is>
       </c>
       <c r="Y81" t="n">
-        <v>13000</v>
+        <v>13110</v>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
@@ -12298,7 +12319,7 @@
         </is>
       </c>
       <c r="AB81" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
@@ -12307,12 +12328,12 @@
       </c>
       <c r="AD81" t="inlineStr">
         <is>
-          <t>NOTA FISCAL FORA DO PASSAPORTE.</t>
+          <t>NOTA FISCAL INAPTA.</t>
         </is>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
-          <t>CONTAGEM/MG</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="AF81" t="inlineStr">
@@ -12322,20 +12343,28 @@
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>OURO PRETO</t>
-        </is>
-      </c>
-      <c r="AH81" t="inlineStr"/>
-      <c r="AI81" t="inlineStr"/>
+          <t>MARIANA</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>VALE SA</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>VALE SA</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>40874</t>
+          <t>40846</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1377716</v>
+        <v>1389618</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -12344,11 +12373,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>TDV São Paulo - SP</t>
+          <t>TDV Serra- ES</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>8294929</v>
+        <v>1569225</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
@@ -12373,7 +12402,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>35260654651716001150550000082949291382619716</t>
+          <t>32260646044053004607550010015692251038241990</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -12383,7 +12412,7 @@
       </c>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="n">
-        <v>4513070950</v>
+        <v>4513192045</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -12391,17 +12420,17 @@
         </is>
       </c>
       <c r="P82" s="1" t="n">
-        <v>46204</v>
+        <v>46199</v>
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr">
         <is>
-          <t>SUPRICORP SUPRIMENTOS LTDA</t>
+          <t>NORTEL SUPRIMENTOS INDUSTRIAIS S/A</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>CAFE PO TRAD BRASILEIRO 500G CORPORATE</t>
+          <t>CHAVE DESALIN ROL 500V 2NA+2NF ZV12H500</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
@@ -12410,17 +12439,21 @@
         </is>
       </c>
       <c r="U82" t="n">
-        <v>300292000</v>
-      </c>
-      <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
+        <v>300300000</v>
+      </c>
+      <c r="V82" t="n">
+        <v>6000182508</v>
+      </c>
+      <c r="W82" s="1" t="n">
+        <v>46195</v>
+      </c>
       <c r="X82" t="inlineStr">
         <is>
           <t>andias</t>
         </is>
       </c>
       <c r="Y82" t="n">
-        <v>772.66</v>
+        <v>1629.84</v>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
@@ -12433,7 +12466,7 @@
         </is>
       </c>
       <c r="AB82" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
@@ -12442,8 +12475,8 @@
       </c>
       <c r="AD82" t="inlineStr">
         <is>
-          <t>NOTA RECUSADA, DEVIDO A FALTA DE VOLUME DO PAPEL CHAMEX.
-13/07 - EMAIL ENVIADO .</t>
+          <t>NAO RECEBIDO, NF FORA DO PASSAPORTE.
+13/07 - NOTA INAPTA EMAIL ENVIADO .</t>
         </is>
       </c>
       <c r="AE82" t="inlineStr">
@@ -12458,7 +12491,7 @@
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>BRUMADINHO</t>
+          <t>OURO PRETO</t>
         </is>
       </c>
       <c r="AH82" t="inlineStr">
@@ -12475,31 +12508,21 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>40898</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>1387542</v>
-      </c>
+          <t>40871</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>TDV Rio de Janeiro - RJ</t>
-        </is>
-      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
-        <v>98950</v>
+        <v>52773</v>
       </c>
       <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>FRACIONADO</t>
-        </is>
-      </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -12517,7 +12540,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>31260633592510044798550030000989501562176825</t>
+          <t>35260601236739000160550010000527731100079220</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -12526,45 +12549,37 @@
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
-      <c r="N83" t="n">
-        <v>4512901040</v>
-      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr">
         <is>
           <t>CONTAGEM</t>
         </is>
       </c>
       <c r="P83" s="1" t="n">
-        <v>46206</v>
+        <v>46203</v>
       </c>
       <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr"/>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>CORREIA T</t>
-        </is>
-      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>ALMONT DO BRASIL IMPORTACAO COM E R</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr"/>
       <c r="T83" t="inlineStr">
         <is>
           <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
-      <c r="U83" t="n">
-        <v>300297000</v>
-      </c>
-      <c r="V83" t="n">
-        <v>6000179944</v>
-      </c>
-      <c r="W83" s="1" t="n">
-        <v>46189</v>
-      </c>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="inlineStr"/>
       <c r="X83" t="inlineStr">
         <is>
-          <t>mvssilva</t>
+          <t>allana</t>
         </is>
       </c>
       <c r="Y83" t="n">
-        <v>9340.67</v>
+        <v>13000</v>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
@@ -12577,7 +12592,7 @@
         </is>
       </c>
       <c r="AB83" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
@@ -12586,12 +12601,12 @@
       </c>
       <c r="AD83" t="inlineStr">
         <is>
-          <t>MATERIAL NAO DESCARREGA EM BARAO DE COCAIS, PERTENCE A MINA DE BRUCUTU</t>
+          <t>NOTA FISCAL FORA DO PASSAPORTE.</t>
         </is>
       </c>
       <c r="AE83" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>CONTAGEM/MG</t>
         </is>
       </c>
       <c r="AF83" t="inlineStr">
@@ -12601,38 +12616,40 @@
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>SAO GONCALO DO RIO ABAIXO</t>
-        </is>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>VALE SA</t>
-        </is>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>VALE SA</t>
-        </is>
-      </c>
+          <t>OURO PRETO</t>
+        </is>
+      </c>
+      <c r="AH83" t="inlineStr"/>
+      <c r="AI83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>40924</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr"/>
+          <t>40874</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1377716</v>
+      </c>
       <c r="C84" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>TDV São Paulo - SP</t>
+        </is>
+      </c>
       <c r="E84" t="n">
-        <v>27027</v>
+        <v>8294929</v>
       </c>
       <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>FRACIONADO</t>
+        </is>
+      </c>
       <c r="H84" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -12650,7 +12667,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>35260616622284000198550050000270271840093617</t>
+          <t>35260654651716001150550000082949291382619716</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -12659,57 +12676,334 @@
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+      <c r="N84" t="n">
+        <v>4513070950</v>
+      </c>
       <c r="O84" t="inlineStr">
         <is>
           <t>CONTAGEM</t>
         </is>
       </c>
       <c r="P84" s="1" t="n">
-        <v>46211</v>
+        <v>46204</v>
       </c>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr">
         <is>
-          <t>METSO</t>
-        </is>
-      </c>
-      <c r="S84" t="inlineStr"/>
+          <t>SUPRICORP SUPRIMENTOS LTDA</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>CAFE PO TRAD BRASILEIRO 500G CORPORATE</t>
+        </is>
+      </c>
       <c r="T84" t="inlineStr">
         <is>
           <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr"/>
+      <c r="U84" t="n">
+        <v>300292000</v>
+      </c>
       <c r="V84" t="inlineStr"/>
       <c r="W84" t="inlineStr"/>
       <c r="X84" t="inlineStr">
         <is>
+          <t>andias</t>
+        </is>
+      </c>
+      <c r="Y84" t="n">
+        <v>772.66</v>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>Em Aberto</t>
+        </is>
+      </c>
+      <c r="AB84" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>NOTA RECUSADA, DEVIDO A FALTA DE VOLUME DO PAPEL CHAMEX.
+13/07 - EMAIL ENVIADO .</t>
+        </is>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>Acima de 12 Dias</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>BRUMADINHO</t>
+        </is>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>VALE SA</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>VALE SA</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>40898</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1387542</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Devolução</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>TDV Rio de Janeiro - RJ</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>98950</v>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>FRACIONADO</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Contagem MG</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>31260633592510044798550030000989501562176825</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>VALE</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="n">
+        <v>4512901040</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="P85" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>CORREIA T</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
+        </is>
+      </c>
+      <c r="U85" t="n">
+        <v>300297000</v>
+      </c>
+      <c r="V85" t="n">
+        <v>6000179944</v>
+      </c>
+      <c r="W85" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>mvssilva</t>
+        </is>
+      </c>
+      <c r="Y85" t="n">
+        <v>9340.67</v>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>Em Aberto</t>
+        </is>
+      </c>
+      <c r="AB85" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>MATERIAL NAO DESCARREGA EM BARAO DE COCAIS, PERTENCE A MINA DE BRUCUTU</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>Acima de 12 Dias</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>SAO GONCALO DO RIO ABAIXO</t>
+        </is>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>VALE SA</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>VALE SA</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>40924</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Devolução</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="n">
+        <v>27027</v>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Contagem MG</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>35260616622284000198550050000270271840093617</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>VALE</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="P86" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>METSO</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
+      <c r="W86" t="inlineStr"/>
+      <c r="X86" t="inlineStr">
+        <is>
           <t>rfernanso</t>
         </is>
       </c>
-      <c r="Y84" t="n">
+      <c r="Y86" t="n">
         <v>837.02</v>
       </c>
-      <c r="Z84" t="inlineStr">
+      <c r="Z86" t="inlineStr">
         <is>
           <t>Atrasado</t>
         </is>
       </c>
-      <c r="AA84" t="inlineStr">
+      <c r="AA86" t="inlineStr">
         <is>
           <t>Em Aberto</t>
         </is>
       </c>
-      <c r="AB84" t="n">
+      <c r="AB86" t="n">
         <v>13</v>
       </c>
-      <c r="AC84" t="inlineStr">
+      <c r="AC86" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="AD84" t="inlineStr">
+      <c r="AD86" t="inlineStr">
         <is>
           <t>A MERCADORIA FOI RECUSADA DEVIDO A AUSENCIA DA NOTA FISCAL E DO CT-E.
 COMO SE TRATA DE UMA NOTA VALE, ACREDITO QUE SERA NECESSARIA A EMISS?O DE UM NOVO PVV PARA DAR CONTINUIDADE AO PROCESSO.
@@ -12717,321 +13011,32 @@
 PLACA:SVR2H77.</t>
         </is>
       </c>
-      <c r="AE84" t="inlineStr">
+      <c r="AE86" t="inlineStr">
         <is>
           <t>CONTAGEM/MG</t>
         </is>
       </c>
-      <c r="AF84" t="inlineStr">
+      <c r="AF86" t="inlineStr">
         <is>
           <t>Acima de 12 Dias</t>
         </is>
       </c>
-      <c r="AG84" t="inlineStr">
+      <c r="AG86" t="inlineStr">
         <is>
           <t>BRUMADINHO</t>
         </is>
       </c>
-      <c r="AH84" t="inlineStr"/>
-      <c r="AI84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>40925</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>1330800</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Devolução</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>TDV Piracicaba - SP</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>217997</v>
-      </c>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>FRACIONADO</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>Contagem MG</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>CONTAGEM</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>35260451482776000126550020002179971931797165</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>VALE</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="n">
-        <v>4101159920</v>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>CONTAGEM</t>
-        </is>
-      </c>
-      <c r="P85" s="1" t="n">
-        <v>46211</v>
-      </c>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr">
-        <is>
-          <t>IMBIL INDUSTRIA E MANUTENCAO DE BOM</t>
-        </is>
-      </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>CJ GIRANTE COMPLETO BP 100330 V02</t>
-        </is>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
-        </is>
-      </c>
-      <c r="U85" t="n">
-        <v>300300000</v>
-      </c>
-      <c r="V85" t="n">
-        <v>6000182530</v>
-      </c>
-      <c r="W85" s="1" t="n">
-        <v>46196</v>
-      </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>bmatozine</t>
-        </is>
-      </c>
-      <c r="Y85" t="n">
-        <v>19508.1</v>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>Atrasado</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>Em Aberto</t>
-        </is>
-      </c>
-      <c r="AB85" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="AD85" t="inlineStr">
-        <is>
-          <t>MATERIA N?O CONSTA NO AGENDAMENTO. 111190000021814.</t>
-        </is>
-      </c>
-      <c r="AE85" t="inlineStr">
-        <is>
-          <t>CONTAGEM/MG</t>
-        </is>
-      </c>
-      <c r="AF85" t="inlineStr">
-        <is>
-          <t>Acima de 12 Dias</t>
-        </is>
-      </c>
-      <c r="AG85" t="inlineStr">
-        <is>
-          <t>NOVA LIMA</t>
-        </is>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>VALE SA</t>
-        </is>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>VALE SA</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>41003</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>950538</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Devolução</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>TDV Contagem MG</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>233471</v>
-      </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>FRACIONADO</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>Contagem MG</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>CONTAGEM</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>31250300548473000128550010002334711219217356</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>VALE</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>CONTAGEM</t>
-        </is>
-      </c>
-      <c r="P86" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="Q86" s="1" t="n">
-        <v>45862.59861111111</v>
-      </c>
-      <c r="R86" t="inlineStr">
-        <is>
-          <t>HIDRAU MAQUINAS MANGUEIRAS E CONEXO</t>
-        </is>
-      </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>SERVIÇO DE TRANSPORTE</t>
-        </is>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr"/>
-      <c r="V86" t="inlineStr"/>
-      <c r="W86" t="inlineStr"/>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>bmatozine</t>
-        </is>
-      </c>
-      <c r="Y86" t="n">
-        <v>733.79</v>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>No Prazo</t>
-        </is>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>Em Aberto</t>
-        </is>
-      </c>
-      <c r="AB86" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="AD86" t="inlineStr">
-        <is>
-          <t>NOTA INAPTA.
-DEVOLUC?O A PEDIDO DO DAVI</t>
-        </is>
-      </c>
-      <c r="AE86" t="inlineStr">
-        <is>
-          <t>CONTAGEM/MG</t>
-        </is>
-      </c>
-      <c r="AF86" t="inlineStr">
-        <is>
-          <t>0 - 8 Dias</t>
-        </is>
-      </c>
-      <c r="AG86" t="inlineStr">
-        <is>
-          <t>NOVA ERA</t>
-        </is>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>VALE S.A.</t>
-        </is>
-      </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>TRANSPORTES DELLA VOLPE S A COMERCI</t>
-        </is>
-      </c>
+      <c r="AH86" t="inlineStr"/>
+      <c r="AI86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>40310</t>
+          <t>40925</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>915140</v>
+        <v>1330800</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -13040,11 +13045,11 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>TDV São Paulo - SP</t>
+          <t>TDV Piracicaba - SP</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>130303</v>
+        <v>217997</v>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
@@ -13059,17 +13064,17 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Itabira - MG</t>
+          <t>Contagem MG</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>ITABIRA</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>35251265837262000150550010001303031000700176</t>
+          <t>35260451482776000126550020002179971931797165</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -13079,25 +13084,25 @@
       </c>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="n">
-        <v>4512514510</v>
+        <v>4101159920</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>ITABIRA</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="P87" s="1" t="n">
-        <v>46147</v>
+        <v>46211</v>
       </c>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr">
         <is>
-          <t>ROLATEL COM DE ROLAMENTOS LT</t>
+          <t>IMBIL INDUSTRIA E MANUTENCAO DE BOM</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>OHA 3138H BUCHA</t>
+          <t>CJ GIRANTE COMPLETO BP 100330 V02</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
@@ -13106,21 +13111,21 @@
         </is>
       </c>
       <c r="U87" t="n">
-        <v>300192000</v>
+        <v>300300000</v>
       </c>
       <c r="V87" t="n">
-        <v>6000116068</v>
+        <v>6000182530</v>
       </c>
       <c r="W87" s="1" t="n">
-        <v>46030</v>
+        <v>46196</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>lbraz</t>
+          <t>bmatozine</t>
         </is>
       </c>
       <c r="Y87" t="n">
-        <v>4418.2</v>
+        <v>19508.1</v>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
@@ -13133,7 +13138,7 @@
         </is>
       </c>
       <c r="AB87" t="n">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
@@ -13142,12 +13147,12 @@
       </c>
       <c r="AD87" t="inlineStr">
         <is>
-          <t>MATERIAL ESTAVA PARADO NA VALE POR PROBLEMAS DE NOTA INAPTA, TENTEI COM O FORNECEDOR VALIDAC?O DA NF, POREM SEN SUCESSO, MATERIAL SEGUE PARA TDV CONTAGEM PAR ADEVOLVER AO FORNECEDOR.</t>
+          <t>MATERIA N?O CONSTA NO AGENDAMENTO. 111190000021814.</t>
         </is>
       </c>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>BOM JESUS DO AMPARO/MG</t>
+          <t>CONTAGEM/MG</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
@@ -13157,7 +13162,7 @@
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>BARAO DE COCAIS</t>
+          <t>NOVA LIMA</t>
         </is>
       </c>
       <c r="AH87" t="inlineStr">
@@ -13167,18 +13172,18 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>ROLATEL COM DE ROLAMENTOS LT</t>
+          <t>VALE SA</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>39820</t>
+          <t>41003</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1005753</v>
+        <v>950538</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -13187,11 +13192,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>TDV Piracicaba - SP</t>
+          <t>TDV Contagem MG</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1041040</v>
+        <v>233471</v>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
@@ -13206,17 +13211,17 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Parauapebas - PA</t>
+          <t>Contagem MG</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>PARAUAPEBAS</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>35260156215999000817550010010410401204604972</t>
+          <t>31250300548473000128550010002334711219217356</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -13225,53 +13230,47 @@
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
-      <c r="N88" t="n">
-        <v>4512750157</v>
-      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
         <is>
-          <t>PARAUAPEBAS</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="P88" s="1" t="n">
-        <v>46097</v>
-      </c>
-      <c r="Q88" t="inlineStr"/>
+        <v>46223</v>
+      </c>
+      <c r="Q88" s="1" t="n">
+        <v>45862.59861111111</v>
+      </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>INFORSHOP SUPRIMENTOS LT</t>
+          <t>HIDRAU MAQUINAS MANGUEIRAS E CONEXO</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>ACUCAR CRISTAL PREMIUM SACHE 5G CX C/ 40</t>
+          <t>SERVIÇO DE TRANSPORTE</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>NOTA FISCAL DIVERGENTE</t>
-        </is>
-      </c>
-      <c r="U88" t="n">
-        <v>300212000</v>
-      </c>
-      <c r="V88" t="n">
-        <v>6000128001</v>
-      </c>
-      <c r="W88" s="1" t="n">
-        <v>46058</v>
-      </c>
+          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="inlineStr"/>
       <c r="X88" t="inlineStr">
         <is>
-          <t>jsconceica</t>
+          <t>bmatozine</t>
         </is>
       </c>
       <c r="Y88" t="n">
-        <v>220.8</v>
+        <v>733.79</v>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>No Prazo</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -13280,7 +13279,7 @@
         </is>
       </c>
       <c r="AB88" t="n">
-        <v>127</v>
+        <v>1</v>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
@@ -13289,43 +13288,44 @@
       </c>
       <c r="AD88" t="inlineStr">
         <is>
-          <t>OM ENCERRADA</t>
+          <t>NOTA INAPTA.
+DEVOLUC?O A PEDIDO DO DAVI</t>
         </is>
       </c>
       <c r="AE88" t="inlineStr">
         <is>
-          <t>IPATINGA/MG</t>
+          <t>CONTAGEM/MG</t>
         </is>
       </c>
       <c r="AF88" t="inlineStr">
         <is>
-          <t>Acima de 12 Dias</t>
+          <t>0 - 8 Dias</t>
         </is>
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>PARAUAPEBAS</t>
+          <t>NOVA ERA</t>
         </is>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
-          <t>VALE SA</t>
+          <t>VALE S.A.</t>
         </is>
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>VALE SA</t>
+          <t>TRANSPORTES DELLA VOLPE S A COMERCI</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>40208</t>
+          <t>40310</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1215814</v>
+        <v>915140</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -13338,7 +13338,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>42349</v>
+        <v>130303</v>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
@@ -13353,17 +13353,17 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Parauapebas - PA</t>
+          <t>Itabira - MG</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>PARAUAPEBAS</t>
+          <t>ITABIRA</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>35260372908817000173550070000423491273779017</t>
+          <t>35251265837262000150550010001303031000700176</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -13373,48 +13373,48 @@
       </c>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="n">
-        <v>4511194843</v>
+        <v>4512514510</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>PARAUAPEBAS</t>
+          <t>ITABIRA</t>
         </is>
       </c>
       <c r="P89" s="1" t="n">
-        <v>46135</v>
+        <v>46147</v>
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr">
         <is>
-          <t>BOSCH REXROTH LTDA</t>
+          <t>ROLATEL COM DE ROLAMENTOS LT</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>CILINDRO HIDR DUP 600MM</t>
+          <t>OHA 3138H BUCHA</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>NOTA FISCAL DIVERGENTE</t>
+          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
       <c r="U89" t="n">
-        <v>300259000</v>
+        <v>300192000</v>
       </c>
       <c r="V89" t="n">
-        <v>6000155976</v>
+        <v>6000116068</v>
       </c>
       <c r="W89" s="1" t="n">
-        <v>46128</v>
+        <v>46030</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>jsconceica</t>
+          <t>lbraz</t>
         </is>
       </c>
       <c r="Y89" t="n">
-        <v>560813.85</v>
+        <v>4418.2</v>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         </is>
       </c>
       <c r="AB89" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
@@ -13436,12 +13436,12 @@
       </c>
       <c r="AD89" t="inlineStr">
         <is>
-          <t>ERRO DE XML</t>
+          <t>MATERIAL ESTAVA PARADO NA VALE POR PROBLEMAS DE NOTA INAPTA, TENTEI COM O FORNECEDOR VALIDAC?O DA NF, POREM SEN SUCESSO, MATERIAL SEGUE PARA TDV CONTAGEM PAR ADEVOLVER AO FORNECEDOR.</t>
         </is>
       </c>
       <c r="AE89" t="inlineStr">
         <is>
-          <t>IPATINGA/MG</t>
+          <t>BOM JESUS DO AMPARO/MG</t>
         </is>
       </c>
       <c r="AF89" t="inlineStr">
@@ -13451,28 +13451,28 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>PARAUAPEBAS</t>
+          <t>BARAO DE COCAIS</t>
         </is>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>VALE S.A.</t>
+          <t>VALE SA</t>
         </is>
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>VALE SA</t>
+          <t>ROLATEL COM DE ROLAMENTOS LT</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>40275</t>
+          <t>39820</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1221813</v>
+        <v>1005753</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -13481,11 +13481,11 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>TDV Contagem MG</t>
+          <t>TDV Piracicaba - SP</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>9023</v>
+        <v>1041040</v>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
@@ -13510,7 +13510,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>31260440568697000116550010000090231130621303</t>
+          <t>35260156215999000817550010010410401204604972</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -13520,7 +13520,7 @@
       </c>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="n">
-        <v>4101182236</v>
+        <v>4512750157</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -13528,32 +13528,32 @@
         </is>
       </c>
       <c r="P90" s="1" t="n">
-        <v>46140</v>
+        <v>46097</v>
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr">
         <is>
-          <t>MLM MECATRONICA E EQUIPAMENTOS LTD</t>
+          <t>INFORSHOP SUPRIMENTOS LT</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>GIROFLEX ROT. MULT. LED AM 24-110VCA/CC</t>
+          <t>ACUCAR CRISTAL PREMIUM SACHE 5G CX C/ 40</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>PEDIDO INEXISTENTE</t>
+          <t>NOTA FISCAL DIVERGENTE</t>
         </is>
       </c>
       <c r="U90" t="n">
-        <v>300258000</v>
+        <v>300212000</v>
       </c>
       <c r="V90" t="n">
-        <v>6000161543</v>
+        <v>6000128001</v>
       </c>
       <c r="W90" s="1" t="n">
-        <v>46142</v>
+        <v>46058</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         </is>
       </c>
       <c r="Y90" t="n">
-        <v>224.97</v>
+        <v>220.8</v>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
@@ -13574,7 +13574,7 @@
         </is>
       </c>
       <c r="AB90" t="n">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
       </c>
       <c r="AD90" t="inlineStr">
         <is>
-          <t>MATERIAL COM REMESSA INEXISTENTE</t>
+          <t>OM ENCERRADA</t>
         </is>
       </c>
       <c r="AE90" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>VALE S.A.</t>
+          <t>VALE SA</t>
         </is>
       </c>
       <c r="AI90" t="inlineStr">
@@ -13615,11 +13615,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>40759</t>
+          <t>40208</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1396947</v>
+        <v>1215814</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -13628,16 +13628,16 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>TDV Parauapebas - PA</t>
+          <t>TDV São Paulo - SP</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1864251</v>
+        <v>42349</v>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>LOTACAO</t>
+          <t>FRACIONADO</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -13657,7 +13657,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>15260634151100000645550010018642511004011363</t>
+          <t>35260372908817000173550070000423491273779017</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -13667,7 +13667,7 @@
       </c>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="n">
-        <v>4512125331</v>
+        <v>4511194843</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -13675,32 +13675,32 @@
         </is>
       </c>
       <c r="P91" s="1" t="n">
-        <v>46191</v>
+        <v>46135</v>
       </c>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr">
         <is>
-          <t>SOTREQ S/A</t>
+          <t>BOSCH REXROTH LTDA</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>RODA</t>
+          <t>CILINDRO HIDR DUP 600MM</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
+          <t>NOTA FISCAL DIVERGENTE</t>
         </is>
       </c>
       <c r="U91" t="n">
-        <v>300297000</v>
+        <v>300259000</v>
       </c>
       <c r="V91" t="n">
-        <v>6000180373</v>
+        <v>6000155976</v>
       </c>
       <c r="W91" s="1" t="n">
-        <v>46190</v>
+        <v>46128</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         </is>
       </c>
       <c r="Y91" t="n">
-        <v>523728.78</v>
+        <v>560813.85</v>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         </is>
       </c>
       <c r="AB91" t="n">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
       </c>
       <c r="AD91" t="inlineStr">
         <is>
-          <t>MATERIAL N?O FOI  DESCARREGADO NO ARMAZEM, PORQUER N?O DEU REPARO E N?O CONSEGUIRAM FALAR COM A AREA RECEBEDORA. LUCIANA LIMA</t>
+          <t>ERRO DE XML</t>
         </is>
       </c>
       <c r="AE91" t="inlineStr">
@@ -13745,7 +13745,7 @@
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>CANAA DOS CARAJAS</t>
+          <t>PARAUAPEBAS</t>
         </is>
       </c>
       <c r="AH91" t="inlineStr">
@@ -13762,11 +13762,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>40765</t>
+          <t>40275</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1333447</v>
+        <v>1221813</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>61748</v>
+        <v>9023</v>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>31260505166746000193550010000617481201912630</t>
+          <t>31260440568697000116550010000090231130621303</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -13814,7 +13814,7 @@
       </c>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="n">
-        <v>4512905097</v>
+        <v>4101182236</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -13822,32 +13822,32 @@
         </is>
       </c>
       <c r="P92" s="1" t="n">
-        <v>46191</v>
+        <v>46140</v>
       </c>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr">
         <is>
-          <t>USELIGAS INDUSTRIA E COMERCIO LTDA</t>
+          <t>MLM MECATRONICA E EQUIPAMENTOS LTD</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>Revestimento da Voluta (1022)</t>
+          <t>GIROFLEX ROT. MULT. LED AM 24-110VCA/CC</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
+          <t>PEDIDO INEXISTENTE</t>
         </is>
       </c>
       <c r="U92" t="n">
-        <v>300285000</v>
+        <v>300258000</v>
       </c>
       <c r="V92" t="n">
-        <v>6000176765</v>
+        <v>6000161543</v>
       </c>
       <c r="W92" s="1" t="n">
-        <v>46182</v>
+        <v>46142</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
         </is>
       </c>
       <c r="Y92" t="n">
-        <v>14911.43</v>
+        <v>224.97</v>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         </is>
       </c>
       <c r="AB92" t="n">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
       </c>
       <c r="AD92" t="inlineStr">
         <is>
-          <t>NF REJEITADA, COMPRADO ERRADO</t>
+          <t>MATERIAL COM REMESSA INEXISTENTE</t>
         </is>
       </c>
       <c r="AE92" t="inlineStr">
@@ -13892,7 +13892,7 @@
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>CURIONOPOLIS</t>
+          <t>PARAUAPEBAS</t>
         </is>
       </c>
       <c r="AH92" t="inlineStr">
@@ -13909,11 +13909,11 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>40841</t>
+          <t>40759</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1377780</v>
+        <v>1396947</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -13922,16 +13922,16 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>TDV Contagem MG</t>
+          <t>TDV Parauapebas - PA</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1479499</v>
+        <v>1864251</v>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>FRACIONADO</t>
+          <t>LOTACAO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>31260534151100001706550020014794991579085850</t>
+          <t>15260634151100000645550010018642511004011363</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -13961,7 +13961,7 @@
       </c>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="n">
-        <v>4511301221</v>
+        <v>4512125331</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -13969,17 +13969,17 @@
         </is>
       </c>
       <c r="P93" s="1" t="n">
-        <v>46198</v>
+        <v>46191</v>
       </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr">
         <is>
-          <t>Sotreq SA</t>
+          <t>SOTREQ S/A</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>Eixo</t>
+          <t>RODA</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
@@ -13988,13 +13988,13 @@
         </is>
       </c>
       <c r="U93" t="n">
-        <v>300295000</v>
+        <v>300297000</v>
       </c>
       <c r="V93" t="n">
-        <v>6000179346</v>
+        <v>6000180373</v>
       </c>
       <c r="W93" s="1" t="n">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         </is>
       </c>
       <c r="Y93" t="n">
-        <v>29382.76</v>
+        <v>523728.78</v>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         </is>
       </c>
       <c r="AB93" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
       </c>
       <c r="AD93" t="inlineStr">
         <is>
-          <t>DEVOLDIVO. CLIENTE N?O FEZ FDM.</t>
+          <t>MATERIAL N?O FOI  DESCARREGADO NO ARMAZEM, PORQUER N?O DEU REPARO E N?O CONSEGUIRAM FALAR COM A AREA RECEBEDORA. LUCIANA LIMA</t>
         </is>
       </c>
       <c r="AE93" t="inlineStr">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>PARAUAPEBAS</t>
+          <t>CANAA DOS CARAJAS</t>
         </is>
       </c>
       <c r="AH93" t="inlineStr">
@@ -14056,11 +14056,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>40842</t>
+          <t>40765</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1372058</v>
+        <v>1333447</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>13908</v>
+        <v>61748</v>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
@@ -14098,7 +14098,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>31260628763819000472550550000139081224019524</t>
+          <t>31260505166746000193550010000617481201912630</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -14108,7 +14108,7 @@
       </c>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="n">
-        <v>4512205579</v>
+        <v>4512905097</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -14116,17 +14116,17 @@
         </is>
       </c>
       <c r="P94" s="1" t="n">
-        <v>46198</v>
+        <v>46191</v>
       </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr">
         <is>
-          <t>EPIROC BRASIL COMERCIALIZACAO DE PR</t>
+          <t>USELIGAS INDUSTRIA E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>BOMBA</t>
+          <t>Revestimento da Voluta (1022)</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
@@ -14135,13 +14135,13 @@
         </is>
       </c>
       <c r="U94" t="n">
-        <v>300295000</v>
+        <v>300285000</v>
       </c>
       <c r="V94" t="n">
-        <v>6000179346</v>
+        <v>6000176765</v>
       </c>
       <c r="W94" s="1" t="n">
-        <v>46188</v>
+        <v>46182</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         </is>
       </c>
       <c r="Y94" t="n">
-        <v>57768.5</v>
+        <v>14911.43</v>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         </is>
       </c>
       <c r="AB94" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
       </c>
       <c r="AD94" t="inlineStr">
         <is>
-          <t>DEVOLDIVO. CLIENTE N?O FEZ FDM.</t>
+          <t>NF REJEITADA, COMPRADO ERRADO</t>
         </is>
       </c>
       <c r="AE94" t="inlineStr">
@@ -14186,7 +14186,7 @@
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>PARAUAPEBAS</t>
+          <t>CURIONOPOLIS</t>
         </is>
       </c>
       <c r="AH94" t="inlineStr">
@@ -14203,11 +14203,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>40843</t>
+          <t>40841</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1365867</v>
+        <v>1377780</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>16171</v>
+        <v>1479499</v>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
@@ -14245,7 +14245,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>31260610829962000101550010000161711807114092</t>
+          <t>31260534151100001706550020014794991579085850</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -14254,7 +14254,9 @@
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+      <c r="N95" t="n">
+        <v>4511301221</v>
+      </c>
       <c r="O95" t="inlineStr">
         <is>
           <t>PARAUAPEBAS</t>
@@ -14266,12 +14268,12 @@
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr">
         <is>
-          <t>POLIWAY INDUSTRIA E COMERCIO DE MAQ</t>
+          <t>Sotreq SA</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>AUTO ALINHADOR DE CARGA TD ZHD 84 PU VO</t>
+          <t>Eixo</t>
         </is>
       </c>
       <c r="T95" t="inlineStr">
@@ -14294,7 +14296,7 @@
         </is>
       </c>
       <c r="Y95" t="n">
-        <v>150</v>
+        <v>29382.76</v>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
@@ -14316,7 +14318,7 @@
       </c>
       <c r="AD95" t="inlineStr">
         <is>
-          <t>N?O FOI POSIVEL LOCALIZR  O CLIENTE. DEVOLVER PARA O FORNECEDOR.</t>
+          <t>DEVOLDIVO. CLIENTE N?O FEZ FDM.</t>
         </is>
       </c>
       <c r="AE95" t="inlineStr">
@@ -14348,11 +14350,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>40880</t>
+          <t>40842</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1231384</v>
+        <v>1372058</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -14361,11 +14363,11 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>TDV São Paulo - SP</t>
+          <t>TDV Contagem MG</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2731155</v>
+        <v>13908</v>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
@@ -14390,7 +14392,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>35260457582793000111550010027311551324126539</t>
+          <t>31260628763819000472550550000139081224019524</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -14400,7 +14402,7 @@
       </c>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="n">
-        <v>4513007972</v>
+        <v>4512205579</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -14408,32 +14410,32 @@
         </is>
       </c>
       <c r="P96" s="1" t="n">
-        <v>46205</v>
+        <v>46198</v>
       </c>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr">
         <is>
-          <t>FESTO  BRASIL LTDA</t>
+          <t>EPIROC BRASIL COMERCIALIZACAO DE PR</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>TUBO FLEXIVEL PUN-12X2-BL LINHA 10</t>
+          <t>BOMBA</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>PEDIDO INEXISTENTE</t>
+          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
       <c r="U96" t="n">
-        <v>300261000</v>
+        <v>300295000</v>
       </c>
       <c r="V96" t="n">
-        <v>6000157534</v>
+        <v>6000179346</v>
       </c>
       <c r="W96" s="1" t="n">
-        <v>46132</v>
+        <v>46188</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -14441,7 +14443,7 @@
         </is>
       </c>
       <c r="Y96" t="n">
-        <v>1366</v>
+        <v>57768.5</v>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
@@ -14454,7 +14456,7 @@
         </is>
       </c>
       <c r="AB96" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
@@ -14463,7 +14465,7 @@
       </c>
       <c r="AD96" t="inlineStr">
         <is>
-          <t>MATERIAL RECUSADO, PEDIDO EXCLUIDO.</t>
+          <t>DEVOLDIVO. CLIENTE N?O FEZ FDM.</t>
         </is>
       </c>
       <c r="AE96" t="inlineStr">
@@ -14483,7 +14485,7 @@
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>VALE SA</t>
+          <t>VALE S.A.</t>
         </is>
       </c>
       <c r="AI96" t="inlineStr">
@@ -14495,21 +14497,31 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>40881</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr"/>
+          <t>40843</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1365867</v>
+      </c>
       <c r="C97" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>TDV Contagem MG</t>
+        </is>
+      </c>
       <c r="E97" t="n">
-        <v>2731150</v>
+        <v>16171</v>
       </c>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>FRACIONADO</t>
+        </is>
+      </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -14527,7 +14539,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>352604575893000111550010027311501907938932</t>
+          <t>31260610829962000101550010000161711807114092</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -14543,30 +14555,40 @@
         </is>
       </c>
       <c r="P97" s="1" t="n">
-        <v>46205</v>
+        <v>46198</v>
       </c>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr">
         <is>
-          <t>FESTO  BRASIL LTDA</t>
-        </is>
-      </c>
-      <c r="S97" t="inlineStr"/>
+          <t>POLIWAY INDUSTRIA E COMERCIO DE MAQ</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>AUTO ALINHADOR DE CARGA TD ZHD 84 PU VO</t>
+        </is>
+      </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>PEDIDO INEXISTENTE</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr"/>
-      <c r="V97" t="inlineStr"/>
-      <c r="W97" t="inlineStr"/>
+          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
+        </is>
+      </c>
+      <c r="U97" t="n">
+        <v>300295000</v>
+      </c>
+      <c r="V97" t="n">
+        <v>6000179346</v>
+      </c>
+      <c r="W97" s="1" t="n">
+        <v>46188</v>
+      </c>
       <c r="X97" t="inlineStr">
         <is>
           <t>jsconceica</t>
         </is>
       </c>
       <c r="Y97" t="n">
-        <v>1366</v>
+        <v>150</v>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
@@ -14579,7 +14601,7 @@
         </is>
       </c>
       <c r="AB97" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
@@ -14588,7 +14610,7 @@
       </c>
       <c r="AD97" t="inlineStr">
         <is>
-          <t>MATERIAL RECUSADO, PEDIDO EXCLUIDO.</t>
+          <t>N?O FOI POSIVEL LOCALIZR  O CLIENTE. DEVOLVER PARA O FORNECEDOR.</t>
         </is>
       </c>
       <c r="AE97" t="inlineStr">
@@ -14606,17 +14628,25 @@
           <t>PARAUAPEBAS</t>
         </is>
       </c>
-      <c r="AH97" t="inlineStr"/>
-      <c r="AI97" t="inlineStr"/>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>VALE S.A.</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>VALE SA</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40880</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1419575</v>
+        <v>1231384</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -14629,7 +14659,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>398359</v>
+        <v>2731155</v>
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
@@ -14654,7 +14684,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>35260660806460000567550010003983591555267998</t>
+          <t>35260457582793000111550010027311551324126539</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -14664,7 +14694,7 @@
       </c>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="n">
-        <v>4513232064</v>
+        <v>4513007972</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -14677,27 +14707,35 @@
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr">
         <is>
-          <t>FERCOI S/A</t>
-        </is>
-      </c>
-      <c r="S98" t="inlineStr"/>
+          <t>FESTO  BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>TUBO FLEXIVEL PUN-12X2-BL LINHA 10</t>
+        </is>
+      </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
+          <t>PEDIDO INEXISTENTE</t>
         </is>
       </c>
       <c r="U98" t="n">
-        <v>300301000</v>
-      </c>
-      <c r="V98" t="inlineStr"/>
-      <c r="W98" t="inlineStr"/>
+        <v>300261000</v>
+      </c>
+      <c r="V98" t="n">
+        <v>6000157534</v>
+      </c>
+      <c r="W98" s="1" t="n">
+        <v>46132</v>
+      </c>
       <c r="X98" t="inlineStr">
         <is>
           <t>jsconceica</t>
         </is>
       </c>
       <c r="Y98" t="n">
-        <v>1123.7</v>
+        <v>1366</v>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
@@ -14714,12 +14752,12 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="AD98" t="inlineStr">
         <is>
-          <t>MATERIAL SENDO DEVOLVIDO POR ESTA MAL ACONDICIONADO.</t>
+          <t>MATERIAL RECUSADO, PEDIDO EXCLUIDO.</t>
         </is>
       </c>
       <c r="AE98" t="inlineStr">
@@ -14751,31 +14789,21 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>40891</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>1419431</v>
-      </c>
+          <t>40881</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>TDV São Paulo - SP</t>
-        </is>
-      </c>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="n">
-        <v>398377</v>
+        <v>2731150</v>
       </c>
       <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>FRACIONADO</t>
-        </is>
-      </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -14793,7 +14821,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>35260660806460000567550010003983771302318886</t>
+          <t>352604575893000111550010027311501907938932</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -14802,9 +14830,7 @@
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
-      <c r="N99" t="n">
-        <v>4513252772</v>
-      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr">
         <is>
           <t>PARAUAPEBAS</t>
@@ -14816,18 +14842,16 @@
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr">
         <is>
-          <t>FERCOI S/A</t>
+          <t>FESTO  BRASIL LTDA</t>
         </is>
       </c>
       <c r="S99" t="inlineStr"/>
       <c r="T99" t="inlineStr">
         <is>
-          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
-        </is>
-      </c>
-      <c r="U99" t="n">
-        <v>300301000</v>
-      </c>
+          <t>PEDIDO INEXISTENTE</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr"/>
       <c r="V99" t="inlineStr"/>
       <c r="W99" t="inlineStr"/>
       <c r="X99" t="inlineStr">
@@ -14836,7 +14860,7 @@
         </is>
       </c>
       <c r="Y99" t="n">
-        <v>22551.25</v>
+        <v>1366</v>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
@@ -14853,12 +14877,12 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="AD99" t="inlineStr">
         <is>
-          <t>MATERIAL SENDO DEVOLVIDO POR ESTA MAL ACONDICIONADO.</t>
+          <t>MATERIAL RECUSADO, PEDIDO EXCLUIDO.</t>
         </is>
       </c>
       <c r="AE99" t="inlineStr">
@@ -14876,25 +14900,17 @@
           <t>PARAUAPEBAS</t>
         </is>
       </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>VALE SA</t>
-        </is>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>VALE SA</t>
-        </is>
-      </c>
+      <c r="AH99" t="inlineStr"/>
+      <c r="AI99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>40892</t>
+          <t>40890</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1419505</v>
+        <v>1419575</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -14907,7 +14923,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>398362</v>
+        <v>398359</v>
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
@@ -14932,7 +14948,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>35260660806460000567550010003983621206357792</t>
+          <t>35260660806460000567550010003983591555267998</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -14942,7 +14958,7 @@
       </c>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="n">
-        <v>4513245163</v>
+        <v>4513232064</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
@@ -14975,7 +14991,7 @@
         </is>
       </c>
       <c r="Y100" t="n">
-        <v>2827.23</v>
+        <v>1123.7</v>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
@@ -15029,11 +15045,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>40893</t>
+          <t>40891</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1405708</v>
+        <v>1419431</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -15046,7 +15062,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>120961</v>
+        <v>398377</v>
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
@@ -15071,7 +15087,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>35260645010717000152550030001209611095001739</t>
+          <t>35260660806460000567550010003983771302318886</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -15081,7 +15097,7 @@
       </c>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="n">
-        <v>4101143886</v>
+        <v>4513252772</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -15094,21 +15110,17 @@
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr">
         <is>
-          <t>POLIERG IND COM LT</t>
-        </is>
-      </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>TUBO PEAD 180x20,1 PN20 PE100 PR ISO 2EX</t>
-        </is>
-      </c>
+          <t>FERCOI S/A</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr"/>
       <c r="T101" t="inlineStr">
         <is>
           <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
       <c r="U101" t="n">
-        <v>300299000</v>
+        <v>300301000</v>
       </c>
       <c r="V101" t="inlineStr"/>
       <c r="W101" t="inlineStr"/>
@@ -15118,7 +15130,7 @@
         </is>
       </c>
       <c r="Y101" t="n">
-        <v>74609.42</v>
+        <v>22551.25</v>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
@@ -15160,7 +15172,7 @@
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>VALE S.A.</t>
+          <t>VALE SA</t>
         </is>
       </c>
       <c r="AI101" t="inlineStr">
@@ -15172,11 +15184,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>40894</t>
+          <t>40892</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1393295</v>
+        <v>1419505</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -15189,7 +15201,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>474374</v>
+        <v>398362</v>
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
@@ -15214,7 +15226,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>35260653234274000101550010004743741776981518</t>
+          <t>35260660806460000567550010003983621206357792</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -15224,7 +15236,7 @@
       </c>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="n">
-        <v>4101185678</v>
+        <v>4513245163</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
@@ -15237,21 +15249,17 @@
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr">
         <is>
-          <t>PLASTIREAL INDUSTRIA E COMERCIO DE</t>
-        </is>
-      </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>TUBO LISO PEAD PE-100 SDR 9 PN 20 PRETO</t>
-        </is>
-      </c>
+          <t>FERCOI S/A</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr"/>
       <c r="T102" t="inlineStr">
         <is>
           <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
       <c r="U102" t="n">
-        <v>300297000</v>
+        <v>300301000</v>
       </c>
       <c r="V102" t="inlineStr"/>
       <c r="W102" t="inlineStr"/>
@@ -15261,7 +15269,7 @@
         </is>
       </c>
       <c r="Y102" t="n">
-        <v>9800</v>
+        <v>2827.23</v>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
@@ -15303,7 +15311,7 @@
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>VALE S.A.</t>
+          <t>VALE SA</t>
         </is>
       </c>
       <c r="AI102" t="inlineStr">
@@ -15315,11 +15323,11 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>40895</t>
+          <t>40893</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1392305</v>
+        <v>1405708</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -15332,7 +15340,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>474373</v>
+        <v>120961</v>
       </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
@@ -15357,7 +15365,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>35260653234274000101550010004743731813460906</t>
+          <t>35260645010717000152550030001209611095001739</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -15367,7 +15375,7 @@
       </c>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="n">
-        <v>4101185625</v>
+        <v>4101143886</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
@@ -15380,12 +15388,12 @@
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr">
         <is>
-          <t>PLASTIREAL INDUSTRIA E COMERCIO DE</t>
+          <t>POLIERG IND COM LT</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>TUBO LISO PEAD PE-100 SDR 9 PN 20 PRETO</t>
+          <t>TUBO PEAD 180x20,1 PN20 PE100 PR ISO 2EX</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
@@ -15394,7 +15402,7 @@
         </is>
       </c>
       <c r="U103" t="n">
-        <v>300297000</v>
+        <v>300299000</v>
       </c>
       <c r="V103" t="inlineStr"/>
       <c r="W103" t="inlineStr"/>
@@ -15404,7 +15412,7 @@
         </is>
       </c>
       <c r="Y103" t="n">
-        <v>9800</v>
+        <v>74609.42</v>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
@@ -15458,11 +15466,11 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>40896</t>
+          <t>40894</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1381667</v>
+        <v>1393295</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -15475,7 +15483,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>50132</v>
+        <v>474374</v>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
@@ -15500,7 +15508,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>35260673012411000170550010000501321802617296</t>
+          <t>35260653234274000101550010004743741776981518</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -15510,7 +15518,7 @@
       </c>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="n">
-        <v>4101196551</v>
+        <v>4101185678</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
@@ -15523,12 +15531,12 @@
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr">
         <is>
-          <t>EXIMPORT LUBEQUIP LTDA</t>
+          <t>PLASTIREAL INDUSTRIA E COMERCIO DE</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>TUBO ACO ST-37-2 DIN 2393 Ø16 X 1,5MM ZI</t>
+          <t>TUBO LISO PEAD PE-100 SDR 9 PN 20 PRETO</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
@@ -15537,7 +15545,7 @@
         </is>
       </c>
       <c r="U104" t="n">
-        <v>300294000</v>
+        <v>300297000</v>
       </c>
       <c r="V104" t="inlineStr"/>
       <c r="W104" t="inlineStr"/>
@@ -15547,7 +15555,7 @@
         </is>
       </c>
       <c r="Y104" t="n">
-        <v>513.98</v>
+        <v>9800</v>
       </c>
       <c r="Z104" t="inlineStr">
         <is>
@@ -15601,11 +15609,11 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>40897</t>
+          <t>40895</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1407137</v>
+        <v>1392305</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -15618,7 +15626,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>35646</v>
+        <v>474373</v>
       </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
@@ -15643,7 +15651,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>35260615659754000125550010000356461053504526</t>
+          <t>35260653234274000101550010004743731813460906</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -15653,7 +15661,7 @@
       </c>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="n">
-        <v>4101208477</v>
+        <v>4101185625</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
@@ -15666,12 +15674,12 @@
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr">
         <is>
-          <t>CGM DISTRIBUIDORA DE ACESSORIOS E P</t>
+          <t>PLASTIREAL INDUSTRIA E COMERCIO DE</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>CONTAINER DE LIXO LIXEIRA PLASTICO 1000L</t>
+          <t>TUBO LISO PEAD PE-100 SDR 9 PN 20 PRETO</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
@@ -15680,7 +15688,7 @@
         </is>
       </c>
       <c r="U105" t="n">
-        <v>300299000</v>
+        <v>300297000</v>
       </c>
       <c r="V105" t="inlineStr"/>
       <c r="W105" t="inlineStr"/>
@@ -15690,7 +15698,7 @@
         </is>
       </c>
       <c r="Y105" t="n">
-        <v>18940</v>
+        <v>9800</v>
       </c>
       <c r="Z105" t="inlineStr">
         <is>
@@ -15744,21 +15752,31 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>40918</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr"/>
+          <t>40896</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>1381667</v>
+      </c>
       <c r="C106" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>TDV São Paulo - SP</t>
+        </is>
+      </c>
       <c r="E106" t="n">
-        <v>8420</v>
+        <v>50132</v>
       </c>
       <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>FRACIONADO</t>
+        </is>
+      </c>
       <c r="H106" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -15776,7 +15794,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>31260344000941000524550010000084201428283759</t>
+          <t>35260673012411000170550010000501321802617296</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -15785,28 +15803,36 @@
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
+      <c r="N106" t="n">
+        <v>4101196551</v>
+      </c>
       <c r="O106" t="inlineStr">
         <is>
           <t>PARAUAPEBAS</t>
         </is>
       </c>
       <c r="P106" s="1" t="n">
-        <v>46210</v>
+        <v>46205</v>
       </c>
       <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr">
         <is>
-          <t>HAVER &amp; BOECKER LATINOAMERICANA MAQ</t>
-        </is>
-      </c>
-      <c r="S106" t="inlineStr"/>
+          <t>EXIMPORT LUBEQUIP LTDA</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>TUBO ACO ST-37-2 DIN 2393 Ø16 X 1,5MM ZI</t>
+        </is>
+      </c>
       <c r="T106" t="inlineStr">
         <is>
           <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr"/>
+      <c r="U106" t="n">
+        <v>300294000</v>
+      </c>
       <c r="V106" t="inlineStr"/>
       <c r="W106" t="inlineStr"/>
       <c r="X106" t="inlineStr">
@@ -15815,7 +15841,7 @@
         </is>
       </c>
       <c r="Y106" t="n">
-        <v>22683.4</v>
+        <v>513.98</v>
       </c>
       <c r="Z106" t="inlineStr">
         <is>
@@ -15828,7 +15854,7 @@
         </is>
       </c>
       <c r="AB106" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
@@ -15837,7 +15863,7 @@
       </c>
       <c r="AD106" t="inlineStr">
         <is>
-          <t>MATERIAL RECUSADO, PALETE FORA DO PADR?O, O CORRETO E 1,20X1,20</t>
+          <t>MATERIAL SENDO DEVOLVIDO POR ESTA MAL ACONDICIONADO.</t>
         </is>
       </c>
       <c r="AE106" t="inlineStr">
@@ -15855,27 +15881,45 @@
           <t>PARAUAPEBAS</t>
         </is>
       </c>
-      <c r="AH106" t="inlineStr"/>
-      <c r="AI106" t="inlineStr"/>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>VALE S.A.</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>VALE SA</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>40928</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr"/>
+          <t>40897</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>1407137</v>
+      </c>
       <c r="C107" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>TDV São Paulo - SP</t>
+        </is>
+      </c>
       <c r="E107" t="n">
-        <v>8761</v>
+        <v>35646</v>
       </c>
       <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>FRACIONADO</t>
+        </is>
+      </c>
       <c r="H107" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -15893,7 +15937,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>31260626101667000174550010000087611000029001</t>
+          <t>35260615659754000125550010000356461053504526</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -15902,28 +15946,36 @@
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
+      <c r="N107" t="n">
+        <v>4101208477</v>
+      </c>
       <c r="O107" t="inlineStr">
         <is>
           <t>PARAUAPEBAS</t>
         </is>
       </c>
       <c r="P107" s="1" t="n">
-        <v>46212</v>
+        <v>46205</v>
       </c>
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr">
         <is>
-          <t>CAMILO NOVIDADES LTDA</t>
-        </is>
-      </c>
-      <c r="S107" t="inlineStr"/>
+          <t>CGM DISTRIBUIDORA DE ACESSORIOS E P</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>CONTAINER DE LIXO LIXEIRA PLASTICO 1000L</t>
+        </is>
+      </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>MATERIAL DIVERGENTE</t>
-        </is>
-      </c>
-      <c r="U107" t="inlineStr"/>
+          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
+        </is>
+      </c>
+      <c r="U107" t="n">
+        <v>300299000</v>
+      </c>
       <c r="V107" t="inlineStr"/>
       <c r="W107" t="inlineStr"/>
       <c r="X107" t="inlineStr">
@@ -15932,11 +15984,11 @@
         </is>
       </c>
       <c r="Y107" t="n">
-        <v>18480</v>
+        <v>18940</v>
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>No Prazo</t>
+          <t>Atrasado</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -15945,16 +15997,16 @@
         </is>
       </c>
       <c r="AB107" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr">
         <is>
-          <t>MATERIAL REJEITADO DEVIDO N?O ATENDER SOLICITAC?O DO PEDIDO.</t>
+          <t>MATERIAL SENDO DEVOLVIDO POR ESTA MAL ACONDICIONADO.</t>
         </is>
       </c>
       <c r="AE107" t="inlineStr">
@@ -15964,7 +16016,7 @@
       </c>
       <c r="AF107" t="inlineStr">
         <is>
-          <t>9 - 12 Dias</t>
+          <t>Acima de 12 Dias</t>
         </is>
       </c>
       <c r="AG107" t="inlineStr">
@@ -15972,13 +16024,21 @@
           <t>PARAUAPEBAS</t>
         </is>
       </c>
-      <c r="AH107" t="inlineStr"/>
-      <c r="AI107" t="inlineStr"/>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>VALE S.A.</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>VALE SA</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>40929</t>
+          <t>40918</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -15989,7 +16049,7 @@
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="n">
-        <v>241771</v>
+        <v>8420</v>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
@@ -16010,7 +16070,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>31260629799921000490550000002417711974037095</t>
+          <t>31260344000941000524550010000084201428283759</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -16026,12 +16086,12 @@
         </is>
       </c>
       <c r="P108" s="1" t="n">
-        <v>46212</v>
+        <v>46210</v>
       </c>
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr">
         <is>
-          <t>ESAB IND E COM LTDA</t>
+          <t>HAVER &amp; BOECKER LATINOAMERICANA MAQ</t>
         </is>
       </c>
       <c r="S108" t="inlineStr"/>
@@ -16049,11 +16109,11 @@
         </is>
       </c>
       <c r="Y108" t="n">
-        <v>356529.68</v>
+        <v>22683.4</v>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>No Prazo</t>
+          <t>Atrasado</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -16062,16 +16122,16 @@
         </is>
       </c>
       <c r="AB108" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="AD108" t="inlineStr">
         <is>
-          <t>CARGA DEVOLVIDA DEVIDO, REMESSA SER FATURA E SEM ALINHAMENTO  VALE.</t>
+          <t>MATERIAL RECUSADO, PALETE FORA DO PADR?O, O CORRETO E 1,20X1,20</t>
         </is>
       </c>
       <c r="AE108" t="inlineStr">
@@ -16081,7 +16141,7 @@
       </c>
       <c r="AF108" t="inlineStr">
         <is>
-          <t>9 - 12 Dias</t>
+          <t>Acima de 12 Dias</t>
         </is>
       </c>
       <c r="AG108" t="inlineStr">
@@ -16095,7 +16155,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>40930</t>
+          <t>40928</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -16106,7 +16166,7 @@
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="n">
-        <v>241677</v>
+        <v>8761</v>
       </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
@@ -16127,7 +16187,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>31260629799921000490550000002416771937784212</t>
+          <t>31260626101667000174550010000087611000029001</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -16148,13 +16208,13 @@
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr">
         <is>
-          <t>ESAB IND E COM LTDA</t>
+          <t>CAMILO NOVIDADES LTDA</t>
         </is>
       </c>
       <c r="S109" t="inlineStr"/>
       <c r="T109" t="inlineStr">
         <is>
-          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
+          <t>MATERIAL DIVERGENTE</t>
         </is>
       </c>
       <c r="U109" t="inlineStr"/>
@@ -16166,7 +16226,7 @@
         </is>
       </c>
       <c r="Y109" t="n">
-        <v>369899.55</v>
+        <v>18480</v>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
@@ -16188,7 +16248,7 @@
       </c>
       <c r="AD109" t="inlineStr">
         <is>
-          <t>MATERIAL DEVOLVIDO , DEVIDO ESTAR COM A DATA REMESSA, FATURA SEM ALINHAMENTO VLE.</t>
+          <t>MATERIAL REJEITADO DEVIDO N?O ATENDER SOLICITAC?O DO PEDIDO.</t>
         </is>
       </c>
       <c r="AE109" t="inlineStr">
@@ -16212,31 +16272,21 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>40934</t>
-        </is>
-      </c>
-      <c r="B110" t="n">
-        <v>1345715</v>
-      </c>
+          <t>40929</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>TDV São Paulo - SP</t>
-        </is>
-      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="n">
-        <v>19880</v>
+        <v>241771</v>
       </c>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>FRACIONADO</t>
-        </is>
-      </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -16254,7 +16304,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>35260504483719000181550010000198801014347341</t>
+          <t>31260629799921000490550000002417711974037095</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -16275,35 +16325,25 @@
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr">
         <is>
-          <t>TRILHOS FERROVIARIOS LTDA</t>
-        </is>
-      </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>TRILHOS</t>
-        </is>
-      </c>
+          <t>ESAB IND E COM LTDA</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr"/>
       <c r="T110" t="inlineStr">
         <is>
           <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
-      <c r="U110" t="n">
-        <v>300286000</v>
-      </c>
-      <c r="V110" t="n">
-        <v>6000176656</v>
-      </c>
-      <c r="W110" s="1" t="n">
-        <v>46182</v>
-      </c>
+      <c r="U110" t="inlineStr"/>
+      <c r="V110" t="inlineStr"/>
+      <c r="W110" t="inlineStr"/>
       <c r="X110" t="inlineStr">
         <is>
           <t>jsconceica</t>
         </is>
       </c>
       <c r="Y110" t="n">
-        <v>6584.94</v>
+        <v>356529.68</v>
       </c>
       <c r="Z110" t="inlineStr">
         <is>
@@ -16320,12 +16360,12 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="AD110" t="inlineStr">
         <is>
-          <t>DELVOVER AO FORNECEDOR, SEM ESPACO NO ARMAZEM. CLIENTE N?O RESPONDE.</t>
+          <t>CARGA DEVOLVIDA DEVIDO, REMESSA SER FATURA E SEM ALINHAMENTO  VALE.</t>
         </is>
       </c>
       <c r="AE110" t="inlineStr">
@@ -16343,45 +16383,27 @@
           <t>PARAUAPEBAS</t>
         </is>
       </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>VALE S.A.</t>
-        </is>
-      </c>
-      <c r="AI110" t="inlineStr">
-        <is>
-          <t>VALE SA</t>
-        </is>
-      </c>
+      <c r="AH110" t="inlineStr"/>
+      <c r="AI110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>40935</t>
-        </is>
-      </c>
-      <c r="B111" t="n">
-        <v>1373906</v>
-      </c>
+          <t>40930</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>TDV São Paulo - SP</t>
-        </is>
-      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="n">
-        <v>832161</v>
+        <v>241677</v>
       </c>
       <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>FRACIONADO</t>
-        </is>
-      </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -16399,7 +16421,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>35260657599581000147550100008321611745969714</t>
+          <t>31260629799921000490550000002416771937784212</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -16408,9 +16430,7 @@
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
-      <c r="N111" t="n">
-        <v>4513157676</v>
-      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr">
         <is>
           <t>PARAUAPEBAS</t>
@@ -16422,35 +16442,25 @@
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr">
         <is>
-          <t>A.R.S. - INDUSTRIA E COMERCIO DE PA</t>
-        </is>
-      </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>PORCA SEXT M 16X2 CH 24 ZB-(4513157676)-</t>
-        </is>
-      </c>
+          <t>ESAB IND E COM LTDA</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr"/>
       <c r="T111" t="inlineStr">
         <is>
           <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
-      <c r="U111" t="n">
-        <v>300292000</v>
-      </c>
-      <c r="V111" t="n">
-        <v>6000177987</v>
-      </c>
-      <c r="W111" s="1" t="n">
-        <v>46184</v>
-      </c>
+      <c r="U111" t="inlineStr"/>
+      <c r="V111" t="inlineStr"/>
+      <c r="W111" t="inlineStr"/>
       <c r="X111" t="inlineStr">
         <is>
           <t>jsconceica</t>
         </is>
       </c>
       <c r="Y111" t="n">
-        <v>2.09</v>
+        <v>369899.55</v>
       </c>
       <c r="Z111" t="inlineStr">
         <is>
@@ -16467,12 +16477,12 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="AD111" t="inlineStr">
         <is>
-          <t>SEM CADASTRO.</t>
+          <t>MATERIAL DEVOLVIDO , DEVIDO ESTAR COM A DATA REMESSA, FATURA SEM ALINHAMENTO VLE.</t>
         </is>
       </c>
       <c r="AE111" t="inlineStr">
@@ -16490,25 +16500,17 @@
           <t>PARAUAPEBAS</t>
         </is>
       </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>VALE S.A.</t>
-        </is>
-      </c>
-      <c r="AI111" t="inlineStr">
-        <is>
-          <t>VALE SA</t>
-        </is>
-      </c>
+      <c r="AH111" t="inlineStr"/>
+      <c r="AI111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>40936</t>
+          <t>40934</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1373876</v>
+        <v>1345715</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -16521,7 +16523,7 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>832157</v>
+        <v>19880</v>
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
@@ -16546,7 +16548,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>35260657599581000147550100008321571940142103</t>
+          <t>35260504483719000181550010000198801014347341</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -16555,9 +16557,7 @@
         </is>
       </c>
       <c r="M112" t="inlineStr"/>
-      <c r="N112" t="n">
-        <v>4513156502</v>
-      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr">
         <is>
           <t>PARAUAPEBAS</t>
@@ -16569,12 +16569,12 @@
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr">
         <is>
-          <t>A.R.S. - INDUSTRIA E COMERCIO DE PA</t>
+          <t>TRILHOS FERROVIARIOS LTDA</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>PA MAQ LENT 1/4-20X3/4 BC-(4513156502)-(</t>
+          <t>TRILHOS</t>
         </is>
       </c>
       <c r="T112" t="inlineStr">
@@ -16583,13 +16583,13 @@
         </is>
       </c>
       <c r="U112" t="n">
-        <v>300292000</v>
+        <v>300286000</v>
       </c>
       <c r="V112" t="n">
-        <v>6000177987</v>
+        <v>6000176656</v>
       </c>
       <c r="W112" s="1" t="n">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="X112" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         </is>
       </c>
       <c r="Y112" t="n">
-        <v>4.69</v>
+        <v>6584.94</v>
       </c>
       <c r="Z112" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
       </c>
       <c r="AD112" t="inlineStr">
         <is>
-          <t>SEM CADASTRO.</t>
+          <t>DELVOVER AO FORNECEDOR, SEM ESPACO NO ARMAZEM. CLIENTE N?O RESPONDE.</t>
         </is>
       </c>
       <c r="AE112" t="inlineStr">
@@ -16651,11 +16651,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>40937</t>
+          <t>40935</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1373877</v>
+        <v>1373906</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -16668,7 +16668,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>832439</v>
+        <v>832161</v>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
@@ -16693,7 +16693,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>35260657599581000147550100008324391399034843</t>
+          <t>35260657599581000147550100008321611745969714</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -16703,7 +16703,7 @@
       </c>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="n">
-        <v>4513184897</v>
+        <v>4513157676</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>PORCA SEXT G.8 3/8-16-(4513184897)-(10)</t>
+          <t>PORCA SEXT M 16X2 CH 24 ZB-(4513157676)-</t>
         </is>
       </c>
       <c r="T113" t="inlineStr">
@@ -16744,7 +16744,7 @@
         </is>
       </c>
       <c r="Y113" t="n">
-        <v>29.82</v>
+        <v>2.09</v>
       </c>
       <c r="Z113" t="inlineStr">
         <is>
@@ -16798,11 +16798,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>40938</t>
+          <t>40936</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1373725</v>
+        <v>1373876</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>832250</v>
+        <v>832157</v>
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>35260657599581000147550100008322501737668575</t>
+          <t>35260657599581000147550100008321571940142103</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -16850,7 +16850,7 @@
       </c>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="n">
-        <v>4513169468</v>
+        <v>4513156502</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
@@ -16868,7 +16868,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>PA SEXT G.8 5/8-11X1.1/2  RI-(4513169468</t>
+          <t>PA MAQ LENT 1/4-20X3/4 BC-(4513156502)-(</t>
         </is>
       </c>
       <c r="T114" t="inlineStr">
@@ -16891,7 +16891,7 @@
         </is>
       </c>
       <c r="Y114" t="n">
-        <v>527.1799999999999</v>
+        <v>4.69</v>
       </c>
       <c r="Z114" t="inlineStr">
         <is>
@@ -16945,11 +16945,11 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>40939</t>
+          <t>40937</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1373833</v>
+        <v>1373877</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>832328</v>
+        <v>832439</v>
       </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
@@ -16987,7 +16987,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>35260657599581000147550100008323281853076349</t>
+          <t>35260657599581000147550100008324391399034843</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -16997,7 +16997,7 @@
       </c>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="n">
-        <v>4513176053</v>
+        <v>4513184897</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>PORCA SEXT G.5 1/2-13 CH 3/4-(4513176053</t>
+          <t>PORCA SEXT G.8 3/8-16-(4513184897)-(10)</t>
         </is>
       </c>
       <c r="T115" t="inlineStr">
@@ -17038,7 +17038,7 @@
         </is>
       </c>
       <c r="Y115" t="n">
-        <v>22.15</v>
+        <v>29.82</v>
       </c>
       <c r="Z115" t="inlineStr">
         <is>
@@ -17092,11 +17092,11 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>40940</t>
+          <t>40938</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>1373872</v>
+        <v>1373725</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>832297</v>
+        <v>832250</v>
       </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
@@ -17134,7 +17134,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>35260657599581000147550100008322971181221624</t>
+          <t>35260657599581000147550100008322501737668575</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -17144,7 +17144,7 @@
       </c>
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="n">
-        <v>4513176054</v>
+        <v>4513169468</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>PA SX G.5 1/2-13X1.1/2 RI ZB-(4513176054</t>
+          <t>PA SEXT G.8 5/8-11X1.1/2  RI-(4513169468</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
@@ -17185,7 +17185,7 @@
         </is>
       </c>
       <c r="Y116" t="n">
-        <v>76.68000000000001</v>
+        <v>527.1799999999999</v>
       </c>
       <c r="Z116" t="inlineStr">
         <is>
@@ -17239,11 +17239,11 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>40941</t>
+          <t>40939</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1373907</v>
+        <v>1373833</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -17256,7 +17256,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>832187</v>
+        <v>832328</v>
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
@@ -17281,7 +17281,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>35260657599581000147550100008321871884435103</t>
+          <t>35260657599581000147550100008323281853076349</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="n">
-        <v>4513160425</v>
+        <v>4513176053</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
@@ -17309,7 +17309,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>ARRUELA LISA DE ACO DIN 125 A M 18-(4513</t>
+          <t>PORCA SEXT G.5 1/2-13 CH 3/4-(4513176053</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
@@ -17332,7 +17332,7 @@
         </is>
       </c>
       <c r="Y117" t="n">
-        <v>11.72</v>
+        <v>22.15</v>
       </c>
       <c r="Z117" t="inlineStr">
         <is>
@@ -17386,21 +17386,31 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>40942</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr"/>
+          <t>40940</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1373872</v>
+      </c>
       <c r="C118" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>TDV São Paulo - SP</t>
+        </is>
+      </c>
       <c r="E118" t="n">
-        <v>19878</v>
+        <v>832297</v>
       </c>
       <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>FRACIONADO</t>
+        </is>
+      </c>
       <c r="H118" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -17418,7 +17428,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>41260611340390000165550040000198781801155209</t>
+          <t>35260657599581000147550100008322971181221624</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -17427,7 +17437,9 @@
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
+      <c r="N118" t="n">
+        <v>4513176054</v>
+      </c>
       <c r="O118" t="inlineStr">
         <is>
           <t>PARAUAPEBAS</t>
@@ -17439,25 +17451,35 @@
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr">
         <is>
-          <t>ECOFIBRA INDUSTRIA E COMERCIO DE CO</t>
-        </is>
-      </c>
-      <c r="S118" t="inlineStr"/>
+          <t>A.R.S. - INDUSTRIA E COMERCIO DE PA</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>PA SX G.5 1/2-13X1.1/2 RI ZB-(4513176054</t>
+        </is>
+      </c>
       <c r="T118" t="inlineStr">
         <is>
           <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr"/>
-      <c r="V118" t="inlineStr"/>
-      <c r="W118" t="inlineStr"/>
+      <c r="U118" t="n">
+        <v>300292000</v>
+      </c>
+      <c r="V118" t="n">
+        <v>6000177987</v>
+      </c>
+      <c r="W118" s="1" t="n">
+        <v>46184</v>
+      </c>
       <c r="X118" t="inlineStr">
         <is>
           <t>jsconceica</t>
         </is>
       </c>
       <c r="Y118" t="n">
-        <v>9584.99</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="Z118" t="inlineStr">
         <is>
@@ -17474,12 +17496,12 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="AD118" t="inlineStr">
         <is>
-          <t>DESTINO DIVERGENTE</t>
+          <t>SEM CADASTRO.</t>
         </is>
       </c>
       <c r="AE118" t="inlineStr">
@@ -17497,27 +17519,45 @@
           <t>PARAUAPEBAS</t>
         </is>
       </c>
-      <c r="AH118" t="inlineStr"/>
-      <c r="AI118" t="inlineStr"/>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>VALE S.A.</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>VALE SA</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>40945</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr"/>
+          <t>40941</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>1373907</v>
+      </c>
       <c r="C119" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>TDV São Paulo - SP</t>
+        </is>
+      </c>
       <c r="E119" t="n">
-        <v>241473</v>
+        <v>832187</v>
       </c>
       <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>FRACIONADO</t>
+        </is>
+      </c>
       <c r="H119" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -17535,7 +17575,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>31260629799921000490550000002414731266548790</t>
+          <t>35260657599581000147550100008321871884435103</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -17544,37 +17584,49 @@
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
+      <c r="N119" t="n">
+        <v>4513160425</v>
+      </c>
       <c r="O119" t="inlineStr">
         <is>
           <t>PARAUAPEBAS</t>
         </is>
       </c>
       <c r="P119" s="1" t="n">
-        <v>46213</v>
+        <v>46212</v>
       </c>
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr">
         <is>
-          <t>ESAB IND E COM LTDA</t>
-        </is>
-      </c>
-      <c r="S119" t="inlineStr"/>
+          <t>A.R.S. - INDUSTRIA E COMERCIO DE PA</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>ARRUELA LISA DE ACO DIN 125 A M 18-(4513</t>
+        </is>
+      </c>
       <c r="T119" t="inlineStr">
         <is>
           <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr"/>
-      <c r="V119" t="inlineStr"/>
-      <c r="W119" t="inlineStr"/>
+      <c r="U119" t="n">
+        <v>300292000</v>
+      </c>
+      <c r="V119" t="n">
+        <v>6000177987</v>
+      </c>
+      <c r="W119" s="1" t="n">
+        <v>46184</v>
+      </c>
       <c r="X119" t="inlineStr">
         <is>
           <t>jsconceica</t>
         </is>
       </c>
       <c r="Y119" t="n">
-        <v>267397.26</v>
+        <v>11.72</v>
       </c>
       <c r="Z119" t="inlineStr">
         <is>
@@ -17587,16 +17639,16 @@
         </is>
       </c>
       <c r="AB119" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="AD119" t="inlineStr">
         <is>
-          <t>RECUSADO DEVIDO A DATA REMESSA SER FUTURA E SEM ALINHAMENTO DA VALE</t>
+          <t>SEM CADASTRO.</t>
         </is>
       </c>
       <c r="AE119" t="inlineStr">
@@ -17614,13 +17666,21 @@
           <t>PARAUAPEBAS</t>
         </is>
       </c>
-      <c r="AH119" t="inlineStr"/>
-      <c r="AI119" t="inlineStr"/>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>VALE S.A.</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>VALE SA</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>40946</t>
+          <t>40942</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -17631,7 +17691,7 @@
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="n">
-        <v>241562</v>
+        <v>19878</v>
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
@@ -17652,7 +17712,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>31260629799921000490550000002415621553848879</t>
+          <t>41260611340390000165550040000198781801155209</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -17668,12 +17728,12 @@
         </is>
       </c>
       <c r="P120" s="1" t="n">
-        <v>46213</v>
+        <v>46212</v>
       </c>
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr">
         <is>
-          <t>ESAB IND E COM LTDA</t>
+          <t>ECOFIBRA INDUSTRIA E COMERCIO DE CO</t>
         </is>
       </c>
       <c r="S120" t="inlineStr"/>
@@ -17691,7 +17751,7 @@
         </is>
       </c>
       <c r="Y120" t="n">
-        <v>178264.84</v>
+        <v>9584.99</v>
       </c>
       <c r="Z120" t="inlineStr">
         <is>
@@ -17704,7 +17764,7 @@
         </is>
       </c>
       <c r="AB120" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
@@ -17713,7 +17773,7 @@
       </c>
       <c r="AD120" t="inlineStr">
         <is>
-          <t>RECUSADO DEVIDO A DATA REMESSA SER FUTURA E SEM ALINHAMENTO DA VALE</t>
+          <t>DESTINO DIVERGENTE</t>
         </is>
       </c>
       <c r="AE120" t="inlineStr">
@@ -17737,7 +17797,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>40977</t>
+          <t>40945</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -17748,7 +17808,7 @@
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="n">
-        <v>857543</v>
+        <v>241473</v>
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
@@ -17769,7 +17829,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>35260600536772003249550010008575431753933138</t>
+          <t>31260629799921000490550000002414731266548790</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -17785,18 +17845,18 @@
         </is>
       </c>
       <c r="P121" s="1" t="n">
-        <v>46217</v>
+        <v>46213</v>
       </c>
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr">
         <is>
-          <t>ECOLAB QUIMICA LTDA</t>
+          <t>ESAB IND E COM LTDA</t>
         </is>
       </c>
       <c r="S121" t="inlineStr"/>
       <c r="T121" t="inlineStr">
         <is>
-          <t>DEVOLUCAO INDEVIDA</t>
+          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
       <c r="U121" t="inlineStr"/>
@@ -17804,11 +17864,11 @@
       <c r="W121" t="inlineStr"/>
       <c r="X121" t="inlineStr">
         <is>
-          <t>erisoares</t>
+          <t>jsconceica</t>
         </is>
       </c>
       <c r="Y121" t="n">
-        <v>215462.1</v>
+        <v>267397.26</v>
       </c>
       <c r="Z121" t="inlineStr">
         <is>
@@ -17821,16 +17881,16 @@
         </is>
       </c>
       <c r="AB121" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="AD121" t="inlineStr">
         <is>
-          <t>MATERIAL DEVOLVIDO DEVIDO O CLIENTE ESTA SEM EQUIPAMENTO PRA DESCARREGAR, FAZER ALINHAMENTO COM CLIENTE E AREA.</t>
+          <t>RECUSADO DEVIDO A DATA REMESSA SER FUTURA E SEM ALINHAMENTO DA VALE</t>
         </is>
       </c>
       <c r="AE121" t="inlineStr">
@@ -17840,7 +17900,7 @@
       </c>
       <c r="AF121" t="inlineStr">
         <is>
-          <t>0 - 8 Dias</t>
+          <t>9 - 12 Dias</t>
         </is>
       </c>
       <c r="AG121" t="inlineStr">
@@ -17854,31 +17914,21 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>40219</t>
-        </is>
-      </c>
-      <c r="B122" t="n">
-        <v>1194154</v>
-      </c>
+          <t>40946</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>TDV Contagem MG</t>
-        </is>
-      </c>
+      <c r="D122" t="inlineStr"/>
       <c r="E122" t="n">
-        <v>2593</v>
+        <v>241562</v>
       </c>
       <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>FRACIONADO</t>
-        </is>
-      </c>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -17886,17 +17936,17 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>São Luíz - MA</t>
+          <t>Parauapebas - PA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>SAO LUIS</t>
+          <t>PARAUAPEBAS</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>31260415801747000116550030000025931705512966</t>
+          <t>31260629799921000490550000002415621553848879</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -17905,53 +17955,41 @@
         </is>
       </c>
       <c r="M122" t="inlineStr"/>
-      <c r="N122" t="n">
-        <v>4101104740</v>
-      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr">
         <is>
-          <t>SAO LUIS</t>
+          <t>PARAUAPEBAS</t>
         </is>
       </c>
       <c r="P122" s="1" t="n">
-        <v>46136</v>
+        <v>46213</v>
       </c>
       <c r="Q122" t="inlineStr"/>
       <c r="R122" t="inlineStr">
         <is>
-          <t>SEVEN SUPRIMENTOS INDUSTRIAIS LTDA</t>
-        </is>
-      </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>MANGUEIRA  P/COMPRESSOR PARAGUSO</t>
-        </is>
-      </c>
+          <t>ESAB IND E COM LTDA</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr"/>
       <c r="T122" t="inlineStr">
         <is>
-          <t>NOTA FISCAL DIVERGENTE</t>
-        </is>
-      </c>
-      <c r="U122" t="n">
-        <v>300254000</v>
-      </c>
-      <c r="V122" t="n">
-        <v>6000153276</v>
-      </c>
-      <c r="W122" s="1" t="n">
-        <v>46122</v>
-      </c>
+          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr"/>
+      <c r="V122" t="inlineStr"/>
+      <c r="W122" t="inlineStr"/>
       <c r="X122" t="inlineStr">
         <is>
-          <t>dluz</t>
+          <t>jsconceica</t>
         </is>
       </c>
       <c r="Y122" t="n">
-        <v>702.84</v>
+        <v>178264.84</v>
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>No Prazo</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -17960,7 +17998,7 @@
         </is>
       </c>
       <c r="AB122" t="n">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="AC122" t="inlineStr">
         <is>
@@ -17969,63 +18007,45 @@
       </c>
       <c r="AD122" t="inlineStr">
         <is>
-          <t>NF CONSTA DIVERGENCIA (INAPTA),NECESSARIO REGULARIZACAO DO XML. O FORNECEDOR DEVERA ABRIR CHAMADO NA FERRAMENTA V360</t>
+          <t>RECUSADO DEVIDO A DATA REMESSA SER FUTURA E SEM ALINHAMENTO DA VALE</t>
         </is>
       </c>
       <c r="AE122" t="inlineStr">
         <is>
-          <t>SAO LUIS</t>
+          <t>IPATINGA/MG</t>
         </is>
       </c>
       <c r="AF122" t="inlineStr">
         <is>
-          <t>Acima de 12 Dias</t>
+          <t>9 - 12 Dias</t>
         </is>
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>SAO LUIS</t>
-        </is>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>VALE S A</t>
-        </is>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>SEVEN SUPRIMENTOS INDUSTRIAIS LTDA</t>
-        </is>
-      </c>
+          <t>PARAUAPEBAS</t>
+        </is>
+      </c>
+      <c r="AH122" t="inlineStr"/>
+      <c r="AI122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>40547</t>
-        </is>
-      </c>
-      <c r="B123" t="n">
-        <v>392391</v>
-      </c>
+          <t>40977</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>TDV São Luiz - MA</t>
-        </is>
-      </c>
+      <c r="D123" t="inlineStr"/>
       <c r="E123" t="n">
-        <v>33540</v>
+        <v>857543</v>
       </c>
       <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>FRACIONADO</t>
-        </is>
-      </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -18033,17 +18053,17 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>São Luíz - MA</t>
+          <t>Parauapebas - PA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>SAO LUIS</t>
+          <t>PARAUAPEBAS</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>35250500017952000118550010000335401611802796</t>
+          <t>35260600536772003249550010008575431753933138</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -18052,31 +18072,25 @@
         </is>
       </c>
       <c r="M123" t="inlineStr"/>
-      <c r="N123" t="n">
-        <v>4100989446</v>
-      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr">
         <is>
-          <t>SAO LUIS</t>
+          <t>PARAUAPEBAS</t>
         </is>
       </c>
       <c r="P123" s="1" t="n">
-        <v>46171</v>
+        <v>46217</v>
       </c>
       <c r="Q123" t="inlineStr"/>
       <c r="R123" t="inlineStr">
         <is>
-          <t>MOLYGRAFIT INDUSTRIA E COMERCIO LTD</t>
-        </is>
-      </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>SERVIÇO DE TRANSPORTE</t>
-        </is>
-      </c>
+          <t>ECOLAB QUIMICA LTDA</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr"/>
       <c r="T123" t="inlineStr">
         <is>
-          <t>NOTA FISCAL DIVERGENTE</t>
+          <t>DEVOLUCAO INDEVIDA</t>
         </is>
       </c>
       <c r="U123" t="inlineStr"/>
@@ -18084,15 +18098,15 @@
       <c r="W123" t="inlineStr"/>
       <c r="X123" t="inlineStr">
         <is>
-          <t>dluz</t>
+          <t>erisoares</t>
         </is>
       </c>
       <c r="Y123" t="n">
-        <v>1029.23</v>
+        <v>215462.1</v>
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>No Prazo</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -18101,52 +18115,44 @@
         </is>
       </c>
       <c r="AB123" t="n">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="AD123" t="inlineStr">
         <is>
-          <t>FIZEMOS A TENTATIVA DE REENTREGA COM MESMA NF , JUNTO DA NF COMPLEMENTAR (33689) FONFORME TRATATIVAS , POREM NOTA CONTINUA INAPTA.</t>
+          <t>MATERIAL DEVOLVIDO DEVIDO O CLIENTE ESTA SEM EQUIPAMENTO PRA DESCARREGAR, FAZER ALINHAMENTO COM CLIENTE E AREA.</t>
         </is>
       </c>
       <c r="AE123" t="inlineStr">
         <is>
-          <t>SAO LUIS</t>
+          <t>IPATINGA/MG</t>
         </is>
       </c>
       <c r="AF123" t="inlineStr">
         <is>
-          <t>Acima de 12 Dias</t>
+          <t>0 - 8 Dias</t>
         </is>
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>SAO LUIS</t>
-        </is>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>VALE S A</t>
-        </is>
-      </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>MOLYGRAFIT INDUSTRIA E COMERCIO LTD</t>
-        </is>
-      </c>
+          <t>PARAUAPEBAS</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr"/>
+      <c r="AI123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>40810</t>
+          <t>40219</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1365998</v>
+        <v>1194154</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -18159,7 +18165,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>8466</v>
+        <v>2593</v>
       </c>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
@@ -18184,7 +18190,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>31260343711951000505550010000084661325509470</t>
+          <t>31260415801747000116550030000025931705512966</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -18193,47 +18199,49 @@
         </is>
       </c>
       <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
+      <c r="N124" t="n">
+        <v>4101104740</v>
+      </c>
       <c r="O124" t="inlineStr">
         <is>
           <t>SAO LUIS</t>
         </is>
       </c>
       <c r="P124" s="1" t="n">
-        <v>46196</v>
+        <v>46136</v>
       </c>
       <c r="Q124" t="inlineStr"/>
       <c r="R124" t="inlineStr">
         <is>
-          <t>FLSMIDTH INDUSTRIAL SOLUTIONS LTDA</t>
+          <t>SEVEN SUPRIMENTOS INDUSTRIAIS LTDA</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>PARTES</t>
+          <t>MANGUEIRA  P/COMPRESSOR PARAGUSO</t>
         </is>
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
+          <t>NOTA FISCAL DIVERGENTE</t>
         </is>
       </c>
       <c r="U124" t="n">
-        <v>300292000</v>
+        <v>300254000</v>
       </c>
       <c r="V124" t="n">
-        <v>6000181717</v>
+        <v>6000153276</v>
       </c>
       <c r="W124" s="1" t="n">
-        <v>46195</v>
+        <v>46122</v>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>proliveira</t>
+          <t>dluz</t>
         </is>
       </c>
       <c r="Y124" t="n">
-        <v>1281886.36</v>
+        <v>702.84</v>
       </c>
       <c r="Z124" t="inlineStr">
         <is>
@@ -18246,7 +18254,7 @@
         </is>
       </c>
       <c r="AB124" t="n">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
@@ -18255,7 +18263,7 @@
       </c>
       <c r="AD124" t="inlineStr">
         <is>
-          <t>O FORNECEDOR DEVERA ABRIR CHAMADO NA FERRAMENTA V360</t>
+          <t>NF CONSTA DIVERGENCIA (INAPTA),NECESSARIO REGULARIZACAO DO XML. O FORNECEDOR DEVERA ABRIR CHAMADO NA FERRAMENTA V360</t>
         </is>
       </c>
       <c r="AE124" t="inlineStr">
@@ -18275,23 +18283,23 @@
       </c>
       <c r="AH124" t="inlineStr">
         <is>
-          <t>VALE SA</t>
+          <t>VALE S A</t>
         </is>
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>VALE SA</t>
+          <t>SEVEN SUPRIMENTOS INDUSTRIAIS LTDA</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>40811</t>
+          <t>40547</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1328744</v>
+        <v>392391</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -18300,16 +18308,16 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>TDV Fortaleza - CE</t>
+          <t>TDV São Luiz - MA</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>27357</v>
+        <v>33540</v>
       </c>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>LOTACAO</t>
+          <t>FRACIONADO</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -18329,7 +18337,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>21260633592510037821550030000273571654701090</t>
+          <t>35250500017952000118550010000335401611802796</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -18339,7 +18347,7 @@
       </c>
       <c r="M125" t="inlineStr"/>
       <c r="N125" t="n">
-        <v>4512553116</v>
+        <v>4100989446</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
@@ -18347,36 +18355,34 @@
         </is>
       </c>
       <c r="P125" s="1" t="n">
-        <v>46196</v>
+        <v>46171</v>
       </c>
       <c r="Q125" t="inlineStr"/>
-      <c r="R125" t="inlineStr"/>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>MOLYGRAFIT INDUSTRIA E COMERCIO LTD</t>
+        </is>
+      </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>RODA FERVRIA 42POL 252,1MM</t>
+          <t>SERVIÇO DE TRANSPORTE</t>
         </is>
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
-        </is>
-      </c>
-      <c r="U125" t="n">
-        <v>300297000</v>
-      </c>
-      <c r="V125" t="n">
-        <v>6000180276</v>
-      </c>
-      <c r="W125" s="1" t="n">
-        <v>46190</v>
-      </c>
+          <t>NOTA FISCAL DIVERGENTE</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr"/>
+      <c r="V125" t="inlineStr"/>
+      <c r="W125" t="inlineStr"/>
       <c r="X125" t="inlineStr">
         <is>
-          <t>proliveira</t>
+          <t>dluz</t>
         </is>
       </c>
       <c r="Y125" t="n">
-        <v>318009.11</v>
+        <v>1029.23</v>
       </c>
       <c r="Z125" t="inlineStr">
         <is>
@@ -18389,16 +18395,16 @@
         </is>
       </c>
       <c r="AB125" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="AD125" t="inlineStr">
         <is>
-          <t>RECUSADO DEVIDO A INCAPACIDADE PARA DESCARGA DO MATERIAL DE FORMA SEGURA. MATERIL CARREGADO SEM ESTAR PALETIZADO, DIRETAMENTE NO ASSOALHO DO VEICULO.</t>
+          <t>FIZEMOS A TENTATIVA DE REENTREGA COM MESMA NF , JUNTO DA NF COMPLEMENTAR (33689) FONFORME TRATATIVAS , POREM NOTA CONTINUA INAPTA.</t>
         </is>
       </c>
       <c r="AE125" t="inlineStr">
@@ -18423,18 +18429,18 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>VALE SA</t>
+          <t>MOLYGRAFIT INDUSTRIA E COMERCIO LTD</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>40828</t>
+          <t>40810</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>1328772</v>
+        <v>1365998</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -18443,16 +18449,16 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>TDV Fortaleza - CE</t>
+          <t>TDV Contagem MG</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>27356</v>
+        <v>8466</v>
       </c>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>LOTACAO</t>
+          <t>FRACIONADO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -18472,7 +18478,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>21260633592510037821550030000273561817592450</t>
+          <t>31260343711951000505550010000084661325509470</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -18481,22 +18487,24 @@
         </is>
       </c>
       <c r="M126" t="inlineStr"/>
-      <c r="N126" t="n">
-        <v>4512553116</v>
-      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr">
         <is>
           <t>SAO LUIS</t>
         </is>
       </c>
       <c r="P126" s="1" t="n">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="Q126" t="inlineStr"/>
-      <c r="R126" t="inlineStr"/>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>FLSMIDTH INDUSTRIAL SOLUTIONS LTDA</t>
+        </is>
+      </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>RODA FERVRIA 42POL 252,1MM</t>
+          <t>PARTES</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
@@ -18508,10 +18516,10 @@
         <v>300292000</v>
       </c>
       <c r="V126" t="n">
-        <v>6000177916</v>
+        <v>6000181717</v>
       </c>
       <c r="W126" s="1" t="n">
-        <v>46184</v>
+        <v>46195</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
@@ -18519,7 +18527,7 @@
         </is>
       </c>
       <c r="Y126" t="n">
-        <v>289099.19</v>
+        <v>1281886.36</v>
       </c>
       <c r="Z126" t="inlineStr">
         <is>
@@ -18532,16 +18540,16 @@
         </is>
       </c>
       <c r="AB126" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="AD126" t="inlineStr">
         <is>
-          <t>RECUSADO DEVIDO A INCAPACIDADE DO MATERIAL PARA DESCARREGAR COM EMPILHADEIRA</t>
+          <t>O FORNECEDOR DEVERA ABRIR CHAMADO NA FERRAMENTA V360</t>
         </is>
       </c>
       <c r="AE126" t="inlineStr">
@@ -18561,7 +18569,7 @@
       </c>
       <c r="AH126" t="inlineStr">
         <is>
-          <t>VALE S A</t>
+          <t>VALE SA</t>
         </is>
       </c>
       <c r="AI126" t="inlineStr">
@@ -18573,11 +18581,11 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>40829</t>
+          <t>40811</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1328771</v>
+        <v>1328744</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -18590,7 +18598,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>27355</v>
+        <v>27357</v>
       </c>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
@@ -18615,7 +18623,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>21260633592510037821550030000273551780304343</t>
+          <t>21260633592510037821550030000273571654701090</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -18633,7 +18641,7 @@
         </is>
       </c>
       <c r="P127" s="1" t="n">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="Q127" t="inlineStr"/>
       <c r="R127" t="inlineStr"/>
@@ -18648,13 +18656,13 @@
         </is>
       </c>
       <c r="U127" t="n">
-        <v>300292000</v>
+        <v>300297000</v>
       </c>
       <c r="V127" t="n">
-        <v>6000177916</v>
+        <v>6000180276</v>
       </c>
       <c r="W127" s="1" t="n">
-        <v>46184</v>
+        <v>46190</v>
       </c>
       <c r="X127" t="inlineStr">
         <is>
@@ -18675,7 +18683,7 @@
         </is>
       </c>
       <c r="AB127" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AC127" t="inlineStr">
         <is>
@@ -18684,7 +18692,7 @@
       </c>
       <c r="AD127" t="inlineStr">
         <is>
-          <t>RECUSADO DEVIDO A INCAPACIDADE DO MATERIAL PARA DESCARREGAR COM EMPILHADEIRA</t>
+          <t>RECUSADO DEVIDO A INCAPACIDADE PARA DESCARGA DO MATERIAL DE FORMA SEGURA. MATERIL CARREGADO SEM ESTAR PALETIZADO, DIRETAMENTE NO ASSOALHO DO VEICULO.</t>
         </is>
       </c>
       <c r="AE127" t="inlineStr">
@@ -18716,11 +18724,11 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>40835</t>
+          <t>40828</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1331164</v>
+        <v>1328772</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -18729,16 +18737,16 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>TDV Serra- ES</t>
+          <t>TDV Fortaleza - CE</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>24102</v>
+        <v>27356</v>
       </c>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>FRACIONADO</t>
+          <t>LOTACAO</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -18758,7 +18766,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>32260501595865000100550010000241021803691646</t>
+          <t>21260633592510037821550030000273561817592450</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -18767,7 +18775,9 @@
         </is>
       </c>
       <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
+      <c r="N128" t="n">
+        <v>4512553116</v>
+      </c>
       <c r="O128" t="inlineStr">
         <is>
           <t>SAO LUIS</t>
@@ -18777,14 +18787,10 @@
         <v>46197</v>
       </c>
       <c r="Q128" t="inlineStr"/>
-      <c r="R128" t="inlineStr">
-        <is>
-          <t>CSV LTDA</t>
-        </is>
-      </c>
+      <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr">
         <is>
-          <t>BTN003</t>
+          <t>RODA FERVRIA 42POL 252,1MM</t>
         </is>
       </c>
       <c r="T128" t="inlineStr">
@@ -18793,10 +18799,10 @@
         </is>
       </c>
       <c r="U128" t="n">
-        <v>300289000</v>
+        <v>300292000</v>
       </c>
       <c r="V128" t="n">
-        <v>6000178002</v>
+        <v>6000177916</v>
       </c>
       <c r="W128" s="1" t="n">
         <v>46184</v>
@@ -18807,7 +18813,7 @@
         </is>
       </c>
       <c r="Y128" t="n">
-        <v>46150</v>
+        <v>289099.19</v>
       </c>
       <c r="Z128" t="inlineStr">
         <is>
@@ -18829,7 +18835,7 @@
       </c>
       <c r="AD128" t="inlineStr">
         <is>
-          <t>NAO RECEBIDO POR FALTA DA EQUIPE NO LOCAL PARA REALIZAR O DESCARREGAMENTO</t>
+          <t>RECUSADO DEVIDO A INCAPACIDADE DO MATERIAL PARA DESCARREGAR COM EMPILHADEIRA</t>
         </is>
       </c>
       <c r="AE128" t="inlineStr">
@@ -18861,119 +18867,407 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
+          <t>40829</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>1328771</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Devolução</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>TDV Fortaleza - CE</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>27355</v>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>LOTACAO</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>São Luíz - MA</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>SAO LUIS</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>21260633592510037821550030000273551780304343</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>VALE</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="n">
+        <v>4512553116</v>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>SAO LUIS</t>
+        </is>
+      </c>
+      <c r="P129" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="Q129" t="inlineStr"/>
+      <c r="R129" t="inlineStr"/>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>RODA FERVRIA 42POL 252,1MM</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
+        </is>
+      </c>
+      <c r="U129" t="n">
+        <v>300292000</v>
+      </c>
+      <c r="V129" t="n">
+        <v>6000177916</v>
+      </c>
+      <c r="W129" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>proliveira</t>
+        </is>
+      </c>
+      <c r="Y129" t="n">
+        <v>318009.11</v>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>Em Aberto</t>
+        </is>
+      </c>
+      <c r="AB129" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>RECUSADO DEVIDO A INCAPACIDADE DO MATERIAL PARA DESCARREGAR COM EMPILHADEIRA</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>SAO LUIS</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>Acima de 12 Dias</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>SAO LUIS</t>
+        </is>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>VALE S A</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>VALE SA</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>40835</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>1331164</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Devolução</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>TDV Serra- ES</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>24102</v>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>FRACIONADO</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>São Luíz - MA</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>SAO LUIS</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>32260501595865000100550010000241021803691646</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>VALE</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>SAO LUIS</t>
+        </is>
+      </c>
+      <c r="P130" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="Q130" t="inlineStr"/>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>CSV LTDA</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>BTN003</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
+        </is>
+      </c>
+      <c r="U130" t="n">
+        <v>300289000</v>
+      </c>
+      <c r="V130" t="n">
+        <v>6000178002</v>
+      </c>
+      <c r="W130" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>proliveira</t>
+        </is>
+      </c>
+      <c r="Y130" t="n">
+        <v>46150</v>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>Em Aberto</t>
+        </is>
+      </c>
+      <c r="AB130" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="AD130" t="inlineStr">
+        <is>
+          <t>NAO RECEBIDO POR FALTA DA EQUIPE NO LOCAL PARA REALIZAR O DESCARREGAMENTO</t>
+        </is>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>SAO LUIS</t>
+        </is>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>Acima de 12 Dias</t>
+        </is>
+      </c>
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t>SAO LUIS</t>
+        </is>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>VALE S A</t>
+        </is>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>VALE SA</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
           <t>41002</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr"/>
-      <c r="C129" t="inlineStr">
+      <c r="B131" t="inlineStr"/>
+      <c r="C131" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="n">
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="n">
         <v>65592</v>
       </c>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr">
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr">
         <is>
           <t>PENDENTE</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
+      <c r="I131" t="inlineStr">
         <is>
           <t>São Luíz - MA</t>
         </is>
       </c>
-      <c r="J129" t="inlineStr">
+      <c r="J131" t="inlineStr">
         <is>
           <t>SAO LUIS</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
+      <c r="K131" t="inlineStr">
         <is>
           <t>35260759511741000180550010000655921682706407</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr">
+      <c r="L131" t="inlineStr">
         <is>
           <t>VALE</t>
         </is>
       </c>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr">
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr">
         <is>
           <t>SAO LUIS</t>
         </is>
       </c>
-      <c r="P129" s="1" t="n">
+      <c r="P131" s="1" t="n">
         <v>46223</v>
       </c>
-      <c r="Q129" t="inlineStr"/>
-      <c r="R129" t="inlineStr">
+      <c r="Q131" t="inlineStr"/>
+      <c r="R131" t="inlineStr">
         <is>
           <t>ARGA FACIL DE DESCALVADO LTDA</t>
         </is>
       </c>
-      <c r="S129" t="inlineStr"/>
-      <c r="T129" t="inlineStr">
+      <c r="S131" t="inlineStr"/>
+      <c r="T131" t="inlineStr">
         <is>
           <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
-      <c r="U129" t="inlineStr"/>
-      <c r="V129" t="inlineStr"/>
-      <c r="W129" t="inlineStr"/>
-      <c r="X129" t="inlineStr">
+      <c r="U131" t="inlineStr"/>
+      <c r="V131" t="inlineStr"/>
+      <c r="W131" t="inlineStr"/>
+      <c r="X131" t="inlineStr">
         <is>
           <t>proliveira</t>
         </is>
       </c>
-      <c r="Y129" t="n">
+      <c r="Y131" t="n">
         <v>5775</v>
       </c>
-      <c r="Z129" t="inlineStr">
+      <c r="Z131" t="inlineStr">
         <is>
           <t>No Prazo</t>
         </is>
       </c>
-      <c r="AA129" t="inlineStr">
+      <c r="AA131" t="inlineStr">
         <is>
           <t>Em Aberto</t>
         </is>
       </c>
-      <c r="AB129" t="n">
+      <c r="AB131" t="n">
         <v>1</v>
       </c>
-      <c r="AC129" t="inlineStr">
+      <c r="AC131" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="AD129" t="inlineStr">
+      <c r="AD131" t="inlineStr">
         <is>
           <t>NF DEVOLVIDA DEVIDO O MATERIAL NAO ESTA PALETIZADO</t>
         </is>
       </c>
-      <c r="AE129" t="inlineStr">
+      <c r="AE131" t="inlineStr">
         <is>
           <t>SAO LUIS</t>
         </is>
       </c>
-      <c r="AF129" t="inlineStr">
+      <c r="AF131" t="inlineStr">
         <is>
           <t>0 - 8 Dias</t>
         </is>
       </c>
-      <c r="AG129" t="inlineStr">
+      <c r="AG131" t="inlineStr">
         <is>
           <t>SAO LUIS</t>
         </is>
       </c>
-      <c r="AH129" t="inlineStr"/>
-      <c r="AI129" t="inlineStr"/>
+      <c r="AH131" t="inlineStr"/>
+      <c r="AI131" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/apresentacoes/Devolucoes_Vale_tratada.xlsx
+++ b/apresentacoes/Devolucoes_Vale_tratada.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI131"/>
+  <dimension ref="A1:AI129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7343,11 +7343,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>39850</t>
+          <t>39935</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1121173</v>
+        <v>1141437</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -7356,11 +7356,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>TDV Contagem MG</t>
+          <t>TDV São Paulo - SP</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6798</v>
+        <v>8008645</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>31260138684304000198550010000067981160598130</t>
+          <t>35260154651716001150550000080086451981210555</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -7394,24 +7394,26 @@
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="N48" t="n">
+        <v>4512652547</v>
+      </c>
       <c r="O48" t="inlineStr">
         <is>
           <t>CONTAGEM</t>
         </is>
       </c>
       <c r="P48" s="1" t="n">
-        <v>46099</v>
+        <v>46102</v>
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
-          <t>UNIACO LTDA</t>
+          <t>SUPRICORP SUPRIMENTOS LTDA</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>CALHA DE CHUVA</t>
+          <t>PILHA ALCALINA PALITO AAA C/2 UNS ELGIN</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -7420,13 +7422,13 @@
         </is>
       </c>
       <c r="U48" t="n">
-        <v>300237000</v>
+        <v>300242000</v>
       </c>
       <c r="V48" t="n">
-        <v>6000144681</v>
+        <v>6000144592</v>
       </c>
       <c r="W48" s="1" t="n">
-        <v>46101</v>
+        <v>46100</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -7434,7 +7436,7 @@
         </is>
       </c>
       <c r="Y48" t="n">
-        <v>1000</v>
+        <v>371.61</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
@@ -7447,7 +7449,7 @@
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
@@ -7456,8 +7458,8 @@
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>MATERIAL  NAO PERTENCE AO ARMAZEM DE JANGADA, O MATERIAL TEM QUE SER ENTREGUE EM AREA COM A INDENTIFICACAO DO RESPONSAVEL DO MATERIAL.
-25/03-EMAIL SINALIZADO AGUARDANDO RETORNO</t>
+          <t>PEDIDO CANCELADO.
+23/03-EMAIL SINALIZADO AGUARDANDO RETORNO</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr">
@@ -7472,7 +7474,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>BRUMADINHO</t>
+          <t>OURO PRETO</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
@@ -7489,11 +7491,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>39935</t>
+          <t>39936</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1141437</v>
+        <v>1141520</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7506,7 +7508,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>8008645</v>
+        <v>8008651</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
@@ -7531,7 +7533,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>35260154651716001150550000080086451981210555</t>
+          <t>35260154651716001150550000080086511981212490</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -7541,7 +7543,7 @@
       </c>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="n">
-        <v>4512652547</v>
+        <v>4512648872</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -7559,7 +7561,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>PILHA ALCALINA PALITO AAA C/2 UNS ELGIN</t>
+          <t>DETERGENTE NEUTRO 5LT SANTOP</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -7568,13 +7570,13 @@
         </is>
       </c>
       <c r="U49" t="n">
-        <v>300242000</v>
+        <v>300241000</v>
       </c>
       <c r="V49" t="n">
-        <v>6000144592</v>
+        <v>6000152773</v>
       </c>
       <c r="W49" s="1" t="n">
-        <v>46100</v>
+        <v>46121</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -7582,7 +7584,7 @@
         </is>
       </c>
       <c r="Y49" t="n">
-        <v>371.61</v>
+        <v>37.34</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
@@ -7605,7 +7607,7 @@
       <c r="AD49" t="inlineStr">
         <is>
           <t>PEDIDO CANCELADO.
-23/03-EMAIL SINALIZADO AGUARDANDO RETORNO</t>
+05/06-EMAIL SINALIZADO 23/03</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr">
@@ -7637,11 +7639,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>39936</t>
+          <t>39937</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1141520</v>
+        <v>1141561</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7654,7 +7656,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>8008651</v>
+        <v>8008654</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
@@ -7679,7 +7681,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>35260154651716001150550000080086511981212490</t>
+          <t>35260154651716001150550000080086541981459463</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -7689,7 +7691,7 @@
       </c>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="n">
-        <v>4512648872</v>
+        <v>4512648457</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -7707,7 +7709,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>DETERGENTE NEUTRO 5LT SANTOP</t>
+          <t>APOIO P/MOUSE C/APOIO ERGON MP-50 C3TECH</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
@@ -7716,13 +7718,13 @@
         </is>
       </c>
       <c r="U50" t="n">
-        <v>300241000</v>
+        <v>300242000</v>
       </c>
       <c r="V50" t="n">
-        <v>6000152773</v>
+        <v>6000144592</v>
       </c>
       <c r="W50" s="1" t="n">
-        <v>46121</v>
+        <v>46100</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -7730,7 +7732,7 @@
         </is>
       </c>
       <c r="Y50" t="n">
-        <v>37.34</v>
+        <v>271.63</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
@@ -7785,11 +7787,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>39937</t>
+          <t>39938</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1141561</v>
+        <v>1141430</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7802,7 +7804,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>8008654</v>
+        <v>8008600</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
@@ -7827,7 +7829,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>35260154651716001150550000080086541981459463</t>
+          <t>35260154651716001150550000080086001981193004</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -7837,7 +7839,7 @@
       </c>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="n">
-        <v>4512648457</v>
+        <v>4512652479</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -7855,7 +7857,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>APOIO P/MOUSE C/APOIO ERGON MP-50 C3TECH</t>
+          <t>PILHA RECARREGAVEL 1.2V AA 2000MAH C/2</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
@@ -7878,7 +7880,7 @@
         </is>
       </c>
       <c r="Y51" t="n">
-        <v>271.63</v>
+        <v>459.53</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
@@ -7933,11 +7935,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>39938</t>
+          <t>40021</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1141430</v>
+        <v>1148722</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7946,11 +7948,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>TDV São Paulo - SP</t>
+          <t>TDV Contagem MG</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>8008600</v>
+        <v>29895</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
@@ -7975,7 +7977,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>35260154651716001150550000080086001981193004</t>
+          <t>31260331228009000188550010000298951388375076</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -7985,7 +7987,7 @@
       </c>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="n">
-        <v>4512652479</v>
+        <v>4512920695</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -7993,17 +7995,17 @@
         </is>
       </c>
       <c r="P52" s="1" t="n">
-        <v>46102</v>
+        <v>46108</v>
       </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr">
         <is>
-          <t>SUPRICORP SUPRIMENTOS LTDA</t>
+          <t>DEL REY RUBBER BORRACHA E POLIURETA</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>PILHA RECARREGAVEL 1.2V AA 2000MAH C/2</t>
+          <t>TUBO ACO PU DN18X6000MM 150LBS FX-FS</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
@@ -8012,13 +8014,13 @@
         </is>
       </c>
       <c r="U52" t="n">
-        <v>300242000</v>
+        <v>300246000</v>
       </c>
       <c r="V52" t="n">
-        <v>6000144592</v>
+        <v>6000147599</v>
       </c>
       <c r="W52" s="1" t="n">
-        <v>46100</v>
+        <v>46107</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -8026,7 +8028,7 @@
         </is>
       </c>
       <c r="Y52" t="n">
-        <v>459.53</v>
+        <v>29665.65</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
@@ -8039,17 +8041,18 @@
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>PEDIDO CANCELADO.
-05/06-EMAIL SINALIZADO 23/03</t>
+          <t>NOTA RECUSADA, MATERIAL NO MEIO DO CAMINH?O E A EMPILHADEIRA N?O CONSEGUE PEGAR COM A TARA TOTAL.
+05/06-EMAIL SINALIZADO 01/04
+01-04 - E-MAIL SINALIZADO AO FORNECEDOR .</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr">
@@ -8064,7 +8067,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>OURO PRETO</t>
+          <t>NOVA LIMA</t>
         </is>
       </c>
       <c r="AH52" t="inlineStr">
@@ -8081,11 +8084,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>40021</t>
+          <t>40036</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1148722</v>
+        <v>1162816</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -8098,7 +8101,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>29895</v>
+        <v>285807</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
@@ -8123,7 +8126,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>31260331228009000188550010000298951388375076</t>
+          <t>31260317185315000153550010002858071335925104</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -8133,7 +8136,7 @@
       </c>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="n">
-        <v>4512920695</v>
+        <v>4101171543</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -8141,17 +8144,17 @@
         </is>
       </c>
       <c r="P53" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr">
         <is>
-          <t>DEL REY RUBBER BORRACHA E POLIURETA</t>
+          <t>ACOCON INDUSTRIA E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>TUBO ACO PU DN18X6000MM 150LBS FX-FS</t>
+          <t>PERFIL L LAM A-36   6,35  76,20  76,20-X</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
@@ -8160,13 +8163,13 @@
         </is>
       </c>
       <c r="U53" t="n">
-        <v>300246000</v>
+        <v>300245000</v>
       </c>
       <c r="V53" t="n">
-        <v>6000147599</v>
+        <v>6000152852</v>
       </c>
       <c r="W53" s="1" t="n">
-        <v>46107</v>
+        <v>46121</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -8174,7 +8177,7 @@
         </is>
       </c>
       <c r="Y53" t="n">
-        <v>29665.65</v>
+        <v>360.8</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
@@ -8187,7 +8190,7 @@
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
@@ -8196,9 +8199,8 @@
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>NOTA RECUSADA, MATERIAL NO MEIO DO CAMINH?O E A EMPILHADEIRA N?O CONSEGUE PEGAR COM A TARA TOTAL.
-05/06-EMAIL SINALIZADO 01/04
-01-04 - E-MAIL SINALIZADO AO FORNECEDOR .</t>
+          <t>NF RECUSADA DEVIDO METRAGEM INCOMPATIVEL, ENTREGAR EM AREA.
+05/06- EMAIL SINALIZADO 11/03</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr">
@@ -8230,11 +8232,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>40036</t>
+          <t>40059</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1162816</v>
+        <v>1170366</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -8243,11 +8245,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>TDV Contagem MG</t>
+          <t>TDV São Paulo - SP</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>285807</v>
+        <v>274700</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
@@ -8272,7 +8274,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>31260317185315000153550010002858071335925104</t>
+          <t>35260357029431004780550150002747001845521932</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -8282,7 +8284,7 @@
       </c>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="n">
-        <v>4101171543</v>
+        <v>4101114909</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -8290,17 +8292,17 @@
         </is>
       </c>
       <c r="P54" s="1" t="n">
-        <v>46111</v>
+        <v>46114</v>
       </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr">
         <is>
-          <t>ACOCON INDUSTRIA E COMERCIO LTDA</t>
+          <t>ATLAS COPCO BRASIL LTDA</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>PERFIL L LAM A-36   6,35  76,20  76,20-X</t>
+          <t>SECADOR F4170+ W 460/60 -13431512 -COX81</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -8309,10 +8311,10 @@
         </is>
       </c>
       <c r="U54" t="n">
-        <v>300245000</v>
+        <v>300247000</v>
       </c>
       <c r="V54" t="n">
-        <v>6000152852</v>
+        <v>6000152779</v>
       </c>
       <c r="W54" s="1" t="n">
         <v>46121</v>
@@ -8323,7 +8325,7 @@
         </is>
       </c>
       <c r="Y54" t="n">
-        <v>360.8</v>
+        <v>376108.82</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
@@ -8336,7 +8338,7 @@
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
@@ -8345,8 +8347,8 @@
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>NF RECUSADA DEVIDO METRAGEM INCOMPATIVEL, ENTREGAR EM AREA.
-05/06- EMAIL SINALIZADO 11/03</t>
+          <t>SEM EQUIPAMENTO PARA DESCARREGAR NA AREA.
+05/06-EMAIL SINALIZANDO 10/04</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr">
@@ -8378,11 +8380,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>40059</t>
+          <t>40135</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1170366</v>
+        <v>1197891</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -8391,11 +8393,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>TDV São Paulo - SP</t>
+          <t>TDV Contagem MG</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>274700</v>
+        <v>286471</v>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
@@ -8420,7 +8422,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>35260357029431004780550150002747001845521932</t>
+          <t>31260417185315000153550010002864711335925101</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -8430,7 +8432,7 @@
       </c>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="n">
-        <v>4101114909</v>
+        <v>4101179935</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -8438,17 +8440,17 @@
         </is>
       </c>
       <c r="P55" s="1" t="n">
-        <v>46114</v>
+        <v>46123</v>
       </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr">
         <is>
-          <t>ATLAS COPCO BRASIL LTDA</t>
+          <t>ACOCON INDUSTRIA E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>SECADOR F4170+ W 460/60 -13431512 -COX81</t>
+          <t>REDONDO LAM 1020  50,80-X 6000</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
@@ -8457,13 +8459,13 @@
         </is>
       </c>
       <c r="U55" t="n">
-        <v>300247000</v>
+        <v>300255000</v>
       </c>
       <c r="V55" t="n">
-        <v>6000152779</v>
+        <v>6000153440</v>
       </c>
       <c r="W55" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -8471,7 +8473,7 @@
         </is>
       </c>
       <c r="Y55" t="n">
-        <v>376108.82</v>
+        <v>1522.9</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
@@ -8484,7 +8486,7 @@
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
@@ -8493,8 +8495,8 @@
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>SEM EQUIPAMENTO PARA DESCARREGAR NA AREA.
-05/06-EMAIL SINALIZANDO 10/04</t>
+          <t>RECUSADO ,MATERIAL MEDE 6 METROS E NAO ESTA PALETIZADO.
+05/06-EMAIL SINALIZANDO 14/04</t>
         </is>
       </c>
       <c r="AE55" t="inlineStr">
@@ -8526,11 +8528,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>40135</t>
+          <t>40136</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1197891</v>
+        <v>1169142</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -8543,7 +8545,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>286471</v>
+        <v>35778</v>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
@@ -8568,7 +8570,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>31260417185315000153550010002864711335925101</t>
+          <t>31260301527393000159550010000357781670978183</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -8578,7 +8580,7 @@
       </c>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="n">
-        <v>4101179935</v>
+        <v>4512762683</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -8591,12 +8593,12 @@
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr">
         <is>
-          <t>ACOCON INDUSTRIA E COMERCIO LTDA</t>
+          <t>POLLYRUBBER INDUSTRIA S.A.</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>REDONDO LAM 1020  50,80-X 6000</t>
+          <t>MANGOTE EM BORRACHA</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
@@ -8619,7 +8621,7 @@
         </is>
       </c>
       <c r="Y56" t="n">
-        <v>1522.9</v>
+        <v>17498.89</v>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
@@ -8641,7 +8643,7 @@
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>RECUSADO ,MATERIAL MEDE 6 METROS E NAO ESTA PALETIZADO.
+          <t>RECUSADO. MATERIAL MEDE 6 METROS E NAO ESTA PALETIZADO.
 05/06-EMAIL SINALIZANDO 14/04</t>
         </is>
       </c>
@@ -8674,11 +8676,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>40136</t>
+          <t>40140</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1169142</v>
+        <v>1190582</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8687,11 +8689,11 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>TDV Contagem MG</t>
+          <t>TDV Ribeirão Preto - SP</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>35778</v>
+        <v>24040</v>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
@@ -8716,7 +8718,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>31260301527393000159550010000357781670978183</t>
+          <t>35260367590265000168550010000240401000081739</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -8726,7 +8728,7 @@
       </c>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="n">
-        <v>4512762683</v>
+        <v>4512862100</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -8734,17 +8736,17 @@
         </is>
       </c>
       <c r="P57" s="1" t="n">
-        <v>46123</v>
+        <v>46126</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr">
         <is>
-          <t>POLLYRUBBER INDUSTRIA S.A.</t>
+          <t>SANTA RITA SOLUCOES TUBULARES LTDA</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>MANGOTE EM BORRACHA</t>
+          <t>TUBO LONGITUDINAL PL 18" (457MM) SCH XS</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
@@ -8753,13 +8755,13 @@
         </is>
       </c>
       <c r="U57" t="n">
-        <v>300255000</v>
+        <v>300253000</v>
       </c>
       <c r="V57" t="n">
-        <v>6000153440</v>
+        <v>6000151372</v>
       </c>
       <c r="W57" s="1" t="n">
-        <v>46122</v>
+        <v>46118</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -8767,7 +8769,7 @@
         </is>
       </c>
       <c r="Y57" t="n">
-        <v>17498.89</v>
+        <v>8447.809999999999</v>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
@@ -8780,7 +8782,7 @@
         </is>
       </c>
       <c r="AB57" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
@@ -8789,8 +8791,8 @@
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>RECUSADO. MATERIAL MEDE 6 METROS E NAO ESTA PALETIZADO.
-05/06-EMAIL SINALIZANDO 14/04</t>
+          <t>MATERIAL FORA DO PADRAO DE RECEBIMENTO.
+05/06-EMAIL SINALIZANDO 20/04</t>
         </is>
       </c>
       <c r="AE57" t="inlineStr">
@@ -8805,7 +8807,7 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>NOVA LIMA</t>
+          <t>ITABIRITO</t>
         </is>
       </c>
       <c r="AH57" t="inlineStr">
@@ -8822,11 +8824,11 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>40140</t>
+          <t>40141</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1190582</v>
+        <v>1189346</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8835,11 +8837,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>TDV Ribeirão Preto - SP</t>
+          <t>TDV São Paulo - SP</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>24040</v>
+        <v>8718</v>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
@@ -8864,7 +8866,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>35260367590265000168550010000240401000081739</t>
+          <t>35260337425216000109550010000087181439991645</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -8874,7 +8876,7 @@
       </c>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="n">
-        <v>4512862100</v>
+        <v>4512987386</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -8887,12 +8889,12 @@
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr">
         <is>
-          <t>SANTA RITA SOLUCOES TUBULARES LTDA</t>
+          <t>ALIANZA TUBOS COMERCIO IMPORTACAO E</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>TUBO LONGITUDINAL PL 18" (457MM) SCH XS</t>
+          <t>TUBO DE ACO SC PR N 219,10 X 8,18 NBR 55</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
@@ -8901,13 +8903,13 @@
         </is>
       </c>
       <c r="U58" t="n">
-        <v>300253000</v>
+        <v>300252000</v>
       </c>
       <c r="V58" t="n">
-        <v>6000151372</v>
+        <v>6000153989</v>
       </c>
       <c r="W58" s="1" t="n">
-        <v>46118</v>
+        <v>46123</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -8915,7 +8917,7 @@
         </is>
       </c>
       <c r="Y58" t="n">
-        <v>8447.809999999999</v>
+        <v>4340.34</v>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
@@ -8938,7 +8940,7 @@
       <c r="AD58" t="inlineStr">
         <is>
           <t>MATERIAL FORA DO PADRAO DE RECEBIMENTO.
-05/06-EMAIL SINALIZANDO 20/04</t>
+05/06-EMAIL SINALIZANDO 16/04</t>
         </is>
       </c>
       <c r="AE58" t="inlineStr">
@@ -8970,11 +8972,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>40141</t>
+          <t>40142</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1189346</v>
+        <v>1189360</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8987,7 +8989,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>8718</v>
+        <v>8710</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
@@ -9012,7 +9014,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>35260337425216000109550010000087181439991645</t>
+          <t>35260337425216000109550010000087101539492332</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -9022,7 +9024,7 @@
       </c>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="n">
-        <v>4512987386</v>
+        <v>4512926894</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -9032,7 +9034,9 @@
       <c r="P59" s="1" t="n">
         <v>46126</v>
       </c>
-      <c r="Q59" t="inlineStr"/>
+      <c r="Q59" s="1" t="n">
+        <v>45562.49097222222</v>
+      </c>
       <c r="R59" t="inlineStr">
         <is>
           <t>ALIANZA TUBOS COMERCIO IMPORTACAO E</t>
@@ -9040,7 +9044,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>TUBO DE ACO SC PR N 219,10 X 8,18 NBR 55</t>
+          <t>TUBO DE ACO SC PR N 88,90 X 5,49 A106/06</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
@@ -9052,10 +9056,10 @@
         <v>300252000</v>
       </c>
       <c r="V59" t="n">
-        <v>6000153989</v>
+        <v>6000157262</v>
       </c>
       <c r="W59" s="1" t="n">
-        <v>46123</v>
+        <v>46135</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -9063,7 +9067,7 @@
         </is>
       </c>
       <c r="Y59" t="n">
-        <v>4340.34</v>
+        <v>1878.82</v>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
@@ -9086,7 +9090,7 @@
       <c r="AD59" t="inlineStr">
         <is>
           <t>MATERIAL FORA DO PADRAO DE RECEBIMENTO.
-05/06-EMAIL SINALIZANDO 16/04</t>
+05/06- EMAIL SINALIZANDO 16/04</t>
         </is>
       </c>
       <c r="AE59" t="inlineStr">
@@ -9118,11 +9122,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>40142</t>
+          <t>40143</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1189360</v>
+        <v>1204829</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -9135,7 +9139,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>8710</v>
+        <v>8756</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
@@ -9160,7 +9164,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>35260337425216000109550010000087101539492332</t>
+          <t>35260437425216000109550010000087561735707896</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -9170,7 +9174,7 @@
       </c>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="n">
-        <v>4512926894</v>
+        <v>4513007234</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -9180,9 +9184,7 @@
       <c r="P60" s="1" t="n">
         <v>46126</v>
       </c>
-      <c r="Q60" s="1" t="n">
-        <v>45562.49097222222</v>
-      </c>
+      <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr">
         <is>
           <t>ALIANZA TUBOS COMERCIO IMPORTACAO E</t>
@@ -9190,7 +9192,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>TUBO DE ACO SC PR N 88,90 X 5,49 A106/06</t>
+          <t>TUBO DE ACO SC PR N 168,30 X 7,11 A106/0</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
@@ -9202,10 +9204,10 @@
         <v>300252000</v>
       </c>
       <c r="V60" t="n">
-        <v>6000157262</v>
+        <v>6000153989</v>
       </c>
       <c r="W60" s="1" t="n">
-        <v>46135</v>
+        <v>46123</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -9213,7 +9215,7 @@
         </is>
       </c>
       <c r="Y60" t="n">
-        <v>1878.82</v>
+        <v>2979.3</v>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
@@ -9235,8 +9237,8 @@
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>MATERIAL FORA DO PADRAO DE RECEBIMENTO.
-05/06- EMAIL SINALIZANDO 16/04</t>
+          <t>MATERIAL FORA DO PADRAODE RECEBIMENTO
+03/06-EMAIL ENVIADO 16/04</t>
         </is>
       </c>
       <c r="AE60" t="inlineStr">
@@ -9268,11 +9270,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>40143</t>
+          <t>40145</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1204829</v>
+        <v>1189344</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -9285,7 +9287,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>8756</v>
+        <v>8719</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
@@ -9310,7 +9312,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>35260437425216000109550010000087561735707896</t>
+          <t>35260337425216000109550010000087191489796495</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -9320,7 +9322,7 @@
       </c>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="n">
-        <v>4513007234</v>
+        <v>4512987906</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -9338,7 +9340,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>TUBO DE ACO SC PR N 168,30 X 7,11 A106/0</t>
+          <t>TUBO DE ACO SC PR N 168,30 X 7,11 NBR 55</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
@@ -9350,10 +9352,10 @@
         <v>300252000</v>
       </c>
       <c r="V61" t="n">
-        <v>6000153989</v>
+        <v>6000157262</v>
       </c>
       <c r="W61" s="1" t="n">
-        <v>46123</v>
+        <v>46135</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -9383,7 +9385,7 @@
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>MATERIAL FORA DO PADRAODE RECEBIMENTO
+          <t>MATERIAL FORA DO PADRAO DE RECEBIMENTO
 03/06-EMAIL ENVIADO 16/04</t>
         </is>
       </c>
@@ -9416,11 +9418,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>40145</t>
+          <t>40184</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1189344</v>
+        <v>1209703</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -9429,11 +9431,11 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>TDV São Paulo - SP</t>
+          <t>TDV Contagem MG</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>8719</v>
+        <v>80800</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
@@ -9458,7 +9460,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>35260337425216000109550010000087191489796495</t>
+          <t>31260326389015000187550010000808001184473414</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -9468,7 +9470,7 @@
       </c>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="n">
-        <v>4512987906</v>
+        <v>49276</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -9476,17 +9478,17 @@
         </is>
       </c>
       <c r="P62" s="1" t="n">
-        <v>46126</v>
+        <v>46130</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr">
         <is>
-          <t>ALIANZA TUBOS COMERCIO IMPORTACAO E</t>
+          <t>DATA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>TUBO DE ACO SC PR N 168,30 X 7,11 NBR 55</t>
+          <t>CONJUNTO COMPLETO FREIO BFK 458-90-10 16</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
@@ -9495,13 +9497,13 @@
         </is>
       </c>
       <c r="U62" t="n">
-        <v>300252000</v>
+        <v>300255000</v>
       </c>
       <c r="V62" t="n">
-        <v>6000157262</v>
+        <v>6000157904</v>
       </c>
       <c r="W62" s="1" t="n">
-        <v>46135</v>
+        <v>46134</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -9509,7 +9511,7 @@
         </is>
       </c>
       <c r="Y62" t="n">
-        <v>2979.3</v>
+        <v>100000</v>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
@@ -9522,7 +9524,7 @@
         </is>
       </c>
       <c r="AB62" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
@@ -9531,8 +9533,8 @@
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>MATERIAL FORA DO PADRAO DE RECEBIMENTO
-03/06-EMAIL ENVIADO 16/04</t>
+          <t>DEVOLUC?O POR FALTA DE MAQUINARIO ESPECIFICO PARA DESCARGA.
+03/06-EMAIL ENVIADO 20/04</t>
         </is>
       </c>
       <c r="AE62" t="inlineStr">
@@ -9547,7 +9549,7 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>ITABIRITO</t>
+          <t>OURO PRETO</t>
         </is>
       </c>
       <c r="AH62" t="inlineStr">
@@ -9564,11 +9566,11 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>40176</t>
+          <t>40255</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1212952</v>
+        <v>1229795</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -9577,11 +9579,11 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>TDV São Paulo - SP</t>
+          <t>TDV Contagem MG</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>447301</v>
+        <v>33632</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
@@ -9606,7 +9608,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>35260349050164000112550010004473011632007547</t>
+          <t>31260402690411000181550010000336321289218606</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -9616,7 +9618,7 @@
       </c>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="n">
-        <v>4512882197</v>
+        <v>4101184591</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -9624,17 +9626,17 @@
         </is>
       </c>
       <c r="P63" s="1" t="n">
-        <v>46127</v>
+        <v>46140</v>
       </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr">
         <is>
-          <t>SIDER COMERCIAL  INDUSTRIAL LTDA</t>
+          <t>CITYTUBOS COMERCIO DE TUBOS LTDA</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>PORCA SEXT 6V8190</t>
+          <t>TB PT NBR 5580 3" X 3.35</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
@@ -9643,21 +9645,21 @@
         </is>
       </c>
       <c r="U63" t="n">
-        <v>300257000</v>
+        <v>300261000</v>
       </c>
       <c r="V63" t="n">
-        <v>6000154577</v>
+        <v>6000163297</v>
       </c>
       <c r="W63" s="1" t="n">
-        <v>46126</v>
+        <v>46149</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>andias</t>
+          <t>jisantos</t>
         </is>
       </c>
       <c r="Y63" t="n">
-        <v>3.41</v>
+        <v>754</v>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
@@ -9670,17 +9672,16 @@
         </is>
       </c>
       <c r="AB63" t="n">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>REJEITADO POR DUPLICIDADE DE DOCUMENTO.
-03-06-EMAIL ENVIADO 20/04</t>
+          <t>NF RECUSADA DEVIDO OS TUBOS ESTAREM MAL ACONDICIONADOS EM CIMA DO CAMINH?O, APRESENTANDO RISCO NA DESCARGA.</t>
         </is>
       </c>
       <c r="AE63" t="inlineStr">
@@ -9695,7 +9696,7 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>BRUMADINHO</t>
+          <t>NOVA LIMA</t>
         </is>
       </c>
       <c r="AH63" t="inlineStr">
@@ -9712,11 +9713,11 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>40184</t>
+          <t>40292</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1209703</v>
+        <v>1229265</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9725,11 +9726,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>TDV Contagem MG</t>
+          <t>TDV São Paulo - SP</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>80800</v>
+        <v>193261</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
@@ -9754,7 +9755,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>31260326389015000187550010000808001184473414</t>
+          <t>35260408624328000190550010001932611011821700</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -9764,7 +9765,7 @@
       </c>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="n">
-        <v>49276</v>
+        <v>4101177719</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -9772,17 +9773,17 @@
         </is>
       </c>
       <c r="P64" s="1" t="n">
-        <v>46130</v>
+        <v>46141</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr">
         <is>
-          <t>DATA ENGENHARIA LTDA</t>
+          <t>DINAMICA MATERIAIS HIDRAULICOS LTD</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>CONJUNTO COMPLETO FREIO BFK 458-90-10 16</t>
+          <t>TUBO DE COND A/C PRETO C/C NBR-5580 M X</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
@@ -9791,13 +9792,13 @@
         </is>
       </c>
       <c r="U64" t="n">
-        <v>300255000</v>
+        <v>300264000</v>
       </c>
       <c r="V64" t="n">
-        <v>6000157904</v>
+        <v>6000163804</v>
       </c>
       <c r="W64" s="1" t="n">
-        <v>46134</v>
+        <v>46150</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -9805,7 +9806,7 @@
         </is>
       </c>
       <c r="Y64" t="n">
-        <v>100000</v>
+        <v>1010.2</v>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
@@ -9818,7 +9819,7 @@
         </is>
       </c>
       <c r="AB64" t="n">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
@@ -9827,8 +9828,8 @@
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>DEVOLUC?O POR FALTA DE MAQUINARIO ESPECIFICO PARA DESCARGA.
-03/06-EMAIL ENVIADO 20/04</t>
+          <t>MATERIAL N?O ESTA PALETIZADO E AMARRADO.
+06/085-EMAIL SINALIZADO AGUARDANDO RETORNO</t>
         </is>
       </c>
       <c r="AE64" t="inlineStr">
@@ -9843,7 +9844,7 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>OURO PRETO</t>
+          <t>NOVA LIMA</t>
         </is>
       </c>
       <c r="AH64" t="inlineStr">
@@ -9860,11 +9861,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>40255</t>
+          <t>40346</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1229795</v>
+        <v>1232626</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9873,11 +9874,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>TDV Contagem MG</t>
+          <t>TDV Piracicaba - SP</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>33632</v>
+        <v>216683</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
@@ -9902,7 +9903,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>31260402690411000181550010000336321289218606</t>
+          <t>35260351482776000126550020002166831840679534</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -9912,7 +9913,7 @@
       </c>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="n">
-        <v>4101184591</v>
+        <v>4101161955</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -9920,17 +9921,17 @@
         </is>
       </c>
       <c r="P65" s="1" t="n">
-        <v>46140</v>
+        <v>46150</v>
       </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr">
         <is>
-          <t>CITYTUBOS COMERCIO DE TUBOS LTDA</t>
+          <t>IMBIL INDUSTRIA E MANUTENCAO DE BOM</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>TB PT NBR 5580 3" X 3.35</t>
+          <t>BOMBA IS-M/G 300X250 AE M6 (BOCAL DE DES</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
@@ -9939,21 +9940,21 @@
         </is>
       </c>
       <c r="U65" t="n">
-        <v>300261000</v>
+        <v>300271000</v>
       </c>
       <c r="V65" t="n">
-        <v>6000163297</v>
+        <v>6000163740</v>
       </c>
       <c r="W65" s="1" t="n">
         <v>46149</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>jisantos</t>
+          <t>andias</t>
         </is>
       </c>
       <c r="Y65" t="n">
-        <v>754</v>
+        <v>300000</v>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
@@ -9966,16 +9967,17 @@
         </is>
       </c>
       <c r="AB65" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>NF RECUSADA DEVIDO OS TUBOS ESTAREM MAL ACONDICIONADOS EM CIMA DO CAMINH?O, APRESENTANDO RISCO NA DESCARGA.</t>
+          <t>MATERIAL RECUSADO ESTA VINCULADO A NF ,POIS O PEDIDO FOI GERADO POR SOLICITACAO DO CHAMADO,PARA REGULARIZAR O RECEBIMENTO DA NOTA 205858 DO PEDIDO 4101048986 QUE APRESENTOU ERRO.
+13/05-EMAIL ENVIADO AGUARDANDO RETORNO, ULTIMA COBRANCA 02/06</t>
         </is>
       </c>
       <c r="AE65" t="inlineStr">
@@ -10007,11 +10009,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>40292</t>
+          <t>40517</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1229265</v>
+        <v>528188</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -10020,11 +10022,11 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>TDV São Paulo - SP</t>
+          <t>TDV Contagem MG</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>193261</v>
+        <v>21819</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
@@ -10049,7 +10051,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>35260408624328000190550010001932611011821700</t>
+          <t>31250871442115000184550010000218191282682886</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -10059,7 +10061,7 @@
       </c>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="n">
-        <v>4101177719</v>
+        <v>4512216187</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -10067,17 +10069,17 @@
         </is>
       </c>
       <c r="P66" s="1" t="n">
-        <v>46141</v>
+        <v>46167</v>
       </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr">
         <is>
-          <t>DINAMICA MATERIAIS HIDRAULICOS LTD</t>
+          <t>SIMAO SERGIO RIBEIRO</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>TUBO DE COND A/C PRETO C/C NBR-5580 M X</t>
+          <t>THINNER ANJO ECO 5L</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
@@ -10086,21 +10088,21 @@
         </is>
       </c>
       <c r="U66" t="n">
-        <v>300264000</v>
+        <v>300109000</v>
       </c>
       <c r="V66" t="n">
-        <v>6000163804</v>
+        <v>6000170950</v>
       </c>
       <c r="W66" s="1" t="n">
-        <v>46150</v>
+        <v>46165</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>andias</t>
+          <t>lgsantos</t>
         </is>
       </c>
       <c r="Y66" t="n">
-        <v>1010.2</v>
+        <v>1057.85</v>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
@@ -10113,17 +10115,17 @@
         </is>
       </c>
       <c r="AB66" t="n">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>MATERIAL N?O ESTA PALETIZADO E AMARRADO.
-06/085-EMAIL SINALIZADO AGUARDANDO RETORNO</t>
+          <t>FORA DO PASSAPORTE. MOTORISTA: JEFERSON SILVA. PLACA: SUP4E70 // 
+EM TRATATIVA JUNTO AO PVV @ANDREZA.</t>
         </is>
       </c>
       <c r="AE66" t="inlineStr">
@@ -10138,7 +10140,7 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>NOVA LIMA</t>
+          <t>OURO PRETO</t>
         </is>
       </c>
       <c r="AH66" t="inlineStr">
@@ -10155,11 +10157,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>40346</t>
+          <t>40625</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1232626</v>
+        <v>1336063</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -10168,11 +10170,11 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>TDV Piracicaba - SP</t>
+          <t>TDV Araquari - SC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>216683</v>
+        <v>33434</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
@@ -10197,7 +10199,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>35260351482776000126550020002166831840679534</t>
+          <t>42260510507244000119550010000334341729345220</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -10207,7 +10209,7 @@
       </c>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="n">
-        <v>4101161955</v>
+        <v>4101172639</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -10215,17 +10217,17 @@
         </is>
       </c>
       <c r="P67" s="1" t="n">
-        <v>46150</v>
+        <v>46177</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr">
         <is>
-          <t>IMBIL INDUSTRIA E MANUTENCAO DE BOM</t>
+          <t>BAHER INDUSTRIA E COMERCIO DE MAQUI</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>BOMBA IS-M/G 300X250 AE M6 (BOCAL DE DES</t>
+          <t>CONSOLE TECNICO ERGONOMICO BAHER LINHA P</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
@@ -10234,13 +10236,13 @@
         </is>
       </c>
       <c r="U67" t="n">
-        <v>300271000</v>
+        <v>300286000</v>
       </c>
       <c r="V67" t="n">
-        <v>6000163740</v>
+        <v>6000173962</v>
       </c>
       <c r="W67" s="1" t="n">
-        <v>46149</v>
+        <v>46174</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -10248,7 +10250,7 @@
         </is>
       </c>
       <c r="Y67" t="n">
-        <v>300000</v>
+        <v>203203.39</v>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
@@ -10261,17 +10263,17 @@
         </is>
       </c>
       <c r="AB67" t="n">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>MATERIAL RECUSADO ESTA VINCULADO A NF ,POIS O PEDIDO FOI GERADO POR SOLICITACAO DO CHAMADO,PARA REGULARIZAR O RECEBIMENTO DA NOTA 205858 DO PEDIDO 4101048986 QUE APRESENTOU ERRO.
-13/05-EMAIL ENVIADO AGUARDANDO RETORNO, ULTIMA COBRANCA 02/06</t>
+          <t>MATERIAL RECUSADO POR SER MAIOR DO QUE A EMPILHADEIRA PODE PEGAR IMPEDINDO A DESCARGA DO MESMO NO LOCAL DE ENTREGA.
+09/06 - E-MAIL ENVIADO .</t>
         </is>
       </c>
       <c r="AE67" t="inlineStr">
@@ -10303,11 +10305,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>40517</t>
+          <t>40703</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>528188</v>
+        <v>1375700</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -10320,7 +10322,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>21819</v>
+        <v>2890</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
@@ -10345,7 +10347,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>31250871442115000184550010000218191282682886</t>
+          <t>31260305896430000157550010000028901000206644</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -10355,7 +10357,7 @@
       </c>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="n">
-        <v>4512216187</v>
+        <v>4101155100</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -10363,17 +10365,17 @@
         </is>
       </c>
       <c r="P68" s="1" t="n">
-        <v>46167</v>
+        <v>46184</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr">
         <is>
-          <t>SIMAO SERGIO RIBEIRO</t>
+          <t>TECNOFUSOS INDUSTRIA E COMERCIO LTD</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>THINNER ANJO ECO 5L</t>
+          <t>Parafuso Cab.Sextavada M48 x 360mm R.P 1</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
@@ -10382,21 +10384,21 @@
         </is>
       </c>
       <c r="U68" t="n">
-        <v>300109000</v>
+        <v>300292000</v>
       </c>
       <c r="V68" t="n">
-        <v>6000170950</v>
+        <v>6000182432</v>
       </c>
       <c r="W68" s="1" t="n">
-        <v>46165</v>
+        <v>46196</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>lgsantos</t>
+          <t>andias</t>
         </is>
       </c>
       <c r="Y68" t="n">
-        <v>1057.85</v>
+        <v>2495</v>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
@@ -10409,7 +10411,7 @@
         </is>
       </c>
       <c r="AB68" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
@@ -10418,8 +10420,8 @@
       </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>FORA DO PASSAPORTE. MOTORISTA: JEFERSON SILVA. PLACA: SUP4E70 // 
-EM TRATATIVA JUNTO AO PVV @ANDREZA.</t>
+          <t>NOTA INAPTA. MOTORISTA CLEBER EUSTAQUIO. PLACA: QKO1D40.
+17/06 AGUARDANDO RETORNO VALE.</t>
         </is>
       </c>
       <c r="AE68" t="inlineStr">
@@ -10451,11 +10453,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>40625</t>
+          <t>40740</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1336063</v>
+        <v>1349525</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -10464,11 +10466,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>TDV Araquari - SC</t>
+          <t>TDV Rio de Janeiro - RJ</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>33434</v>
+        <v>1112110</v>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
@@ -10493,7 +10495,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>42260510507244000119550010000334341729345220</t>
+          <t>33260550567288000744550040011121101168473870</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -10503,7 +10505,7 @@
       </c>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="n">
-        <v>4101172639</v>
+        <v>4513076977</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -10511,17 +10513,17 @@
         </is>
       </c>
       <c r="P69" s="1" t="n">
-        <v>46177</v>
+        <v>46190</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr">
         <is>
-          <t>BAHER INDUSTRIA E COMERCIO DE MAQUI</t>
+          <t>SOCIEDADE MICHELIN DE PARTICIPACOES</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>CONSOLE TECNICO ERGONOMICO BAHER LINHA P</t>
+          <t>PNEU 29.5R</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
@@ -10530,21 +10532,21 @@
         </is>
       </c>
       <c r="U69" t="n">
-        <v>300286000</v>
+        <v>300296000</v>
       </c>
       <c r="V69" t="n">
-        <v>6000173962</v>
+        <v>6000179557</v>
       </c>
       <c r="W69" s="1" t="n">
-        <v>46174</v>
+        <v>46189</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>andias</t>
+          <t>mvssilva</t>
         </is>
       </c>
       <c r="Y69" t="n">
-        <v>203203.39</v>
+        <v>117821.86</v>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
@@ -10557,7 +10559,7 @@
         </is>
       </c>
       <c r="AB69" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
@@ -10566,8 +10568,7 @@
       </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>MATERIAL RECUSADO POR SER MAIOR DO QUE A EMPILHADEIRA PODE PEGAR IMPEDINDO A DESCARGA DO MESMO NO LOCAL DE ENTREGA.
-09/06 - E-MAIL ENVIADO .</t>
+          <t>NOTA FISCAL RECUSADA, MATERIAL PAROU DO CENTRO 4143 DEVE SER ENTREGUE NA AREA.</t>
         </is>
       </c>
       <c r="AE69" t="inlineStr">
@@ -10599,11 +10600,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>40703</t>
+          <t>40741</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1375700</v>
+        <v>1084585</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -10612,11 +10613,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>TDV Contagem MG</t>
+          <t>TDV Rio de Janeiro - RJ</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2890</v>
+        <v>1098397</v>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
@@ -10641,7 +10642,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>31260305896430000157550010000028901000206644</t>
+          <t>33260250567288000744550040010983971165237497</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -10651,7 +10652,7 @@
       </c>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="n">
-        <v>4101155100</v>
+        <v>4142886970</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -10659,17 +10660,17 @@
         </is>
       </c>
       <c r="P70" s="1" t="n">
-        <v>46184</v>
+        <v>46190</v>
       </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr">
         <is>
-          <t>TECNOFUSOS INDUSTRIA E COMERCIO LTD</t>
+          <t>SOCIEDADE MICHELIN DE PARTICIPACOES</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>Parafuso Cab.Sextavada M48 x 360mm R.P 1</t>
+          <t>PNEU 24</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
@@ -10678,21 +10679,21 @@
         </is>
       </c>
       <c r="U70" t="n">
-        <v>300292000</v>
+        <v>300290000</v>
       </c>
       <c r="V70" t="n">
-        <v>6000182432</v>
+        <v>6000175263</v>
       </c>
       <c r="W70" s="1" t="n">
-        <v>46196</v>
+        <v>46176</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>andias</t>
+          <t>mvssilva</t>
         </is>
       </c>
       <c r="Y70" t="n">
-        <v>2495</v>
+        <v>71242.55</v>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
@@ -10705,17 +10706,16 @@
         </is>
       </c>
       <c r="AB70" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="AD70" t="inlineStr">
         <is>
-          <t>NOTA INAPTA. MOTORISTA CLEBER EUSTAQUIO. PLACA: QKO1D40.
-17/06 AGUARDANDO RETORNO VALE.</t>
+          <t>NOTA FISCAL RECUSA, MATERIAL PNEUS DO CENTRO 4143 DEVE SER ENTREGUE NA AREA.</t>
         </is>
       </c>
       <c r="AE70" t="inlineStr">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>OURO PRETO</t>
+          <t>NOVA LIMA</t>
         </is>
       </c>
       <c r="AH70" t="inlineStr">
@@ -10747,11 +10747,11 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>40740</t>
+          <t>40745</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1349525</v>
+        <v>1378572</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -10760,11 +10760,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>TDV Rio de Janeiro - RJ</t>
+          <t>TDV São Paulo - SP</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1112110</v>
+        <v>1343784</v>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>33260550567288000744550040011121101168473870</t>
+          <t>35260644357085001026550010013437841317059860</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="n">
-        <v>4513076977</v>
+        <v>4513161671</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -10812,12 +10812,12 @@
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr">
         <is>
-          <t>SOCIEDADE MICHELIN DE PARTICIPACOES</t>
+          <t>HIDRAU TORQUE INDUSTRIA COMERCIO IM</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>PNEU 29.5R</t>
+          <t>15252779-PNEU SUPORTE LEVE 23.5-25</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
@@ -10829,18 +10829,18 @@
         <v>300296000</v>
       </c>
       <c r="V71" t="n">
-        <v>6000179557</v>
+        <v>6000179485</v>
       </c>
       <c r="W71" s="1" t="n">
-        <v>46189</v>
+        <v>46188</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>mvssilva</t>
+          <t>allana</t>
         </is>
       </c>
       <c r="Y71" t="n">
-        <v>117821.86</v>
+        <v>126311.62</v>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
@@ -10862,12 +10862,12 @@
       </c>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>NOTA FISCAL RECUSADA, MATERIAL PAROU DO CENTRO 4143 DEVE SER ENTREGUE NA AREA.</t>
+          <t>NOTA RECUSADA MATERIAL COM CENTRO DE HZT KIT DEVE SER ENTREGUE NA AREA .</t>
         </is>
       </c>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>CONTAGEM/MG</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
@@ -10894,11 +10894,11 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>40741</t>
+          <t>40751</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1084585</v>
+        <v>1369066</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10907,11 +10907,11 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>TDV Rio de Janeiro - RJ</t>
+          <t>TDV Contagem MG</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1098397</v>
+        <v>26006</v>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>33260250567288000744550040010983971165237497</t>
+          <t>31260332651494000160550000000260061731636280</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -10946,7 +10946,7 @@
       </c>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="n">
-        <v>4142886970</v>
+        <v>4101177871</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -10954,17 +10954,17 @@
         </is>
       </c>
       <c r="P72" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr">
         <is>
-          <t>SOCIEDADE MICHELIN DE PARTICIPACOES</t>
+          <t>UNIUN EQUIPAMENTOS E FERRAMENTAS MR</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>PNEU 24</t>
+          <t>SOQUETE SEXTAVADO IMPACTO   3/4 X 1/4</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
@@ -10973,21 +10973,21 @@
         </is>
       </c>
       <c r="U72" t="n">
-        <v>300290000</v>
+        <v>300292000</v>
       </c>
       <c r="V72" t="n">
-        <v>6000175263</v>
+        <v>6000181699</v>
       </c>
       <c r="W72" s="1" t="n">
-        <v>46176</v>
+        <v>46193</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>mvssilva</t>
+          <t>rfernanso</t>
         </is>
       </c>
       <c r="Y72" t="n">
-        <v>71242.55</v>
+        <v>12574.4</v>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
@@ -11000,21 +11000,21 @@
         </is>
       </c>
       <c r="AB72" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="AD72" t="inlineStr">
         <is>
-          <t>NOTA FISCAL RECUSA, MATERIAL PNEUS DO CENTRO 4143 DEVE SER ENTREGUE NA AREA.</t>
+          <t>NOTA FISCAL FORA DO PASSAPORTE. MOTORISTA: CLEBER EUSTAQUIO. PLACA:QKO1D40.</t>
         </is>
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>CONTAGEM/MG</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>NOVA LIMA</t>
+          <t>OURO PRETO</t>
         </is>
       </c>
       <c r="AH72" t="inlineStr">
@@ -11041,11 +11041,11 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>40745</t>
+          <t>40767</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1378572</v>
+        <v>1378634</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -11054,11 +11054,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>TDV São Paulo - SP</t>
+          <t>TDV Araquari - SC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1343784</v>
+        <v>18686</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
@@ -11083,7 +11083,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>35260644357085001026550010013437841317059860</t>
+          <t>42260542284562000235550010000186861021484450</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -11093,7 +11093,7 @@
       </c>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="n">
-        <v>4513161671</v>
+        <v>4512914217</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -11101,17 +11101,17 @@
         </is>
       </c>
       <c r="P73" s="1" t="n">
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr">
         <is>
-          <t>HIDRAU TORQUE INDUSTRIA COMERCIO IM</t>
+          <t>PLASSER DO BRASIL COMERCIO IND E RE</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>15252779-PNEU SUPORTE LEVE 23.5-25</t>
+          <t>61.04.212 PINO DE CORRENTE</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
@@ -11120,21 +11120,21 @@
         </is>
       </c>
       <c r="U73" t="n">
-        <v>300296000</v>
+        <v>300294000</v>
       </c>
       <c r="V73" t="n">
-        <v>6000179485</v>
+        <v>6000179064</v>
       </c>
       <c r="W73" s="1" t="n">
-        <v>46188</v>
+        <v>46186</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>allana</t>
+          <t>rfernanso</t>
         </is>
       </c>
       <c r="Y73" t="n">
-        <v>126311.62</v>
+        <v>23032.76</v>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
@@ -11147,16 +11147,16 @@
         </is>
       </c>
       <c r="AB73" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>NOTA RECUSADA MATERIAL COM CENTRO DE HZT KIT DEVE SER ENTREGUE NA AREA .</t>
+          <t>MATERIAL DE 160KG FOI EM VEICULO DE PASSEIO ONDE N?O FOI POSSIVEL OPERAR COM A EMPILHADEIRA. MOTORISTA:ANTONIO CELIO. PLACA:QWY9G87.</t>
         </is>
       </c>
       <c r="AE73" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>NOVA LIMA</t>
+          <t>GOVERNADOR VALADARES</t>
         </is>
       </c>
       <c r="AH73" t="inlineStr">
@@ -11188,11 +11188,11 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>40751</t>
+          <t>40774</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1369066</v>
+        <v>1057514</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -11201,11 +11201,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>TDV Contagem MG</t>
+          <t>TDV Piracicaba - SP</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>26006</v>
+        <v>18714</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>31260332651494000160550000000260061731636280</t>
+          <t>35260229514960000151550010000187141118292253</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -11239,26 +11239,24 @@
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" t="n">
-        <v>4101177871</v>
-      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
         <is>
           <t>CONTAGEM</t>
         </is>
       </c>
       <c r="P74" s="1" t="n">
-        <v>46191</v>
+        <v>46193</v>
       </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr">
         <is>
-          <t>UNIUN EQUIPAMENTOS E FERRAMENTAS MR</t>
+          <t>BRG INDUSTRIA E COMERCIO DE MANCAIS</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>SOQUETE SEXTAVADO IMPACTO   3/4 X 1/4</t>
+          <t>SERVIÇO DE TRANSPORTE</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
@@ -11267,13 +11265,13 @@
         </is>
       </c>
       <c r="U74" t="n">
-        <v>300292000</v>
+        <v>300223000</v>
       </c>
       <c r="V74" t="n">
-        <v>6000181699</v>
+        <v>6000133073</v>
       </c>
       <c r="W74" s="1" t="n">
-        <v>46193</v>
+        <v>46073</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -11281,7 +11279,7 @@
         </is>
       </c>
       <c r="Y74" t="n">
-        <v>12574.4</v>
+        <v>2915.84</v>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
@@ -11294,7 +11292,7 @@
         </is>
       </c>
       <c r="AB74" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
@@ -11303,7 +11301,7 @@
       </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>NOTA FISCAL FORA DO PASSAPORTE. MOTORISTA: CLEBER EUSTAQUIO. PLACA:QKO1D40.</t>
+          <t>FORA DO PASSAPORTE. MOTORISTA:FRANCISCO GERALDO. PLACA:OQP1E86.</t>
         </is>
       </c>
       <c r="AE74" t="inlineStr">
@@ -11318,7 +11316,7 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>OURO PRETO</t>
+          <t>CONGONHAS</t>
         </is>
       </c>
       <c r="AH74" t="inlineStr">
@@ -11335,11 +11333,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>40767</t>
+          <t>40775</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1378634</v>
+        <v>1386712</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -11348,16 +11346,16 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>TDV Araquari - SC</t>
+          <t>TDV Rio de Janeiro - RJ</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>18686</v>
+        <v>98955</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>FRACIONADO</t>
+          <t>LOTACAO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -11377,7 +11375,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>42260542284562000235550010000186861021484450</t>
+          <t>31260633592510044798550030000989551114967957</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -11387,7 +11385,7 @@
       </c>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="n">
-        <v>4512914217</v>
+        <v>4512896531</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -11395,17 +11393,17 @@
         </is>
       </c>
       <c r="P75" s="1" t="n">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr">
         <is>
-          <t>PLASSER DO BRASIL COMERCIO IND E RE</t>
+          <t>DIVERSOS</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>61.04.212 PINO DE CORRENTE</t>
+          <t>CORREIA T</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
@@ -11414,21 +11412,21 @@
         </is>
       </c>
       <c r="U75" t="n">
-        <v>300294000</v>
+        <v>300295000</v>
       </c>
       <c r="V75" t="n">
-        <v>6000179064</v>
+        <v>6000178553</v>
       </c>
       <c r="W75" s="1" t="n">
-        <v>46186</v>
+        <v>46185</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>rfernanso</t>
+          <t>mvssilva</t>
         </is>
       </c>
       <c r="Y75" t="n">
-        <v>23032.76</v>
+        <v>25654.52</v>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
@@ -11441,7 +11439,7 @@
         </is>
       </c>
       <c r="AB75" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
@@ -11450,12 +11448,12 @@
       </c>
       <c r="AD75" t="inlineStr">
         <is>
-          <t>MATERIAL DE 160KG FOI EM VEICULO DE PASSEIO ONDE N?O FOI POSSIVEL OPERAR COM A EMPILHADEIRA. MOTORISTA:ANTONIO CELIO. PLACA:QWY9G87.</t>
+          <t>ESTOQUE EM S?O GONCALO DO RIO ABAIXO ( BRUCUTU )</t>
         </is>
       </c>
       <c r="AE75" t="inlineStr">
         <is>
-          <t>CONTAGEM/MG</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="AF75" t="inlineStr">
@@ -11465,7 +11463,7 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>GOVERNADOR VALADARES</t>
+          <t>SAO GONCALO DO RIO ABAIXO</t>
         </is>
       </c>
       <c r="AH75" t="inlineStr">
@@ -11482,11 +11480,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>40774</t>
+          <t>40793</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1057514</v>
+        <v>1388729</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -11495,11 +11493,11 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>TDV Piracicaba - SP</t>
+          <t>TDV São Paulo - SP</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>18714</v>
+        <v>19925</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
@@ -11524,7 +11522,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>35260229514960000151550010000187141118292253</t>
+          <t>35260604483719000181550010000199251540262338</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -11540,17 +11538,17 @@
         </is>
       </c>
       <c r="P76" s="1" t="n">
-        <v>46193</v>
+        <v>46195</v>
       </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr">
         <is>
-          <t>BRG INDUSTRIA E COMERCIO DE MANCAIS</t>
+          <t>TRILHOS FERROVIARIOS LTDA</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>SERVIÇO DE TRANSPORTE</t>
+          <t>TRILHOS</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
@@ -11559,13 +11557,13 @@
         </is>
       </c>
       <c r="U76" t="n">
-        <v>300223000</v>
+        <v>300294000</v>
       </c>
       <c r="V76" t="n">
-        <v>6000133073</v>
+        <v>6000181110</v>
       </c>
       <c r="W76" s="1" t="n">
-        <v>46073</v>
+        <v>46196</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -11573,7 +11571,7 @@
         </is>
       </c>
       <c r="Y76" t="n">
-        <v>2915.84</v>
+        <v>44492.85</v>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
@@ -11586,16 +11584,16 @@
         </is>
       </c>
       <c r="AB76" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>FORA DO PASSAPORTE. MOTORISTA:FRANCISCO GERALDO. PLACA:OQP1E86.</t>
+          <t>MATERIAL SEM CONDIC?ES DE DESCARGA NO ARMAZEM DE BAR?O. MOTORISTA: WEBERT SILVIO JUNIO APARECIDO.PLACA:QQT0C42.</t>
         </is>
       </c>
       <c r="AE76" t="inlineStr">
@@ -11610,7 +11608,7 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>CONGONHAS</t>
+          <t>BARAO DE COCAIS</t>
         </is>
       </c>
       <c r="AH76" t="inlineStr">
@@ -11627,11 +11625,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>40775</t>
+          <t>40814</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1386712</v>
+        <v>1385757</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -11640,16 +11638,16 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>TDV Rio de Janeiro - RJ</t>
+          <t>TDV São Paulo - SP</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>98955</v>
+        <v>17236</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>LOTACAO</t>
+          <t>FRACIONADO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -11669,7 +11667,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>31260633592510044798550030000989551114967957</t>
+          <t>35260604552842000107550010000172361019303890</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -11679,7 +11677,7 @@
       </c>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="n">
-        <v>4512896531</v>
+        <v>4513210303</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
@@ -11687,17 +11685,17 @@
         </is>
       </c>
       <c r="P77" s="1" t="n">
-        <v>46193</v>
+        <v>46196</v>
       </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr">
         <is>
-          <t>DIVERSOS</t>
+          <t>POWER MASTER - TECNOLOGIA EM ACIONA</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>CORREIA T</t>
+          <t>ELEMENTO ELASTICO E97</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
@@ -11706,21 +11704,21 @@
         </is>
       </c>
       <c r="U77" t="n">
-        <v>300295000</v>
+        <v>300294000</v>
       </c>
       <c r="V77" t="n">
-        <v>6000178553</v>
+        <v>6000181114</v>
       </c>
       <c r="W77" s="1" t="n">
-        <v>46185</v>
+        <v>46196</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>mvssilva</t>
+          <t>rfernanso</t>
         </is>
       </c>
       <c r="Y77" t="n">
-        <v>25654.52</v>
+        <v>210.97</v>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
@@ -11733,7 +11731,7 @@
         </is>
       </c>
       <c r="AB77" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
@@ -11742,12 +11740,12 @@
       </c>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>ESTOQUE EM S?O GONCALO DO RIO ABAIXO ( BRUCUTU )</t>
+          <t>FORA DO PASSAPORTE. MOTORISTA:ELI TOMAZ. PVV8D31.</t>
         </is>
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>CONTAGEM/MG</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
@@ -11757,7 +11755,7 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>SAO GONCALO DO RIO ABAIXO</t>
+          <t>OURO PRETO</t>
         </is>
       </c>
       <c r="AH77" t="inlineStr">
@@ -11774,11 +11772,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>40793</t>
+          <t>40830</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1388729</v>
+        <v>1400589</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -11787,11 +11785,11 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>TDV São Paulo - SP</t>
+          <t>TDV Contagem MG</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>19925</v>
+        <v>165499</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
@@ -11816,7 +11814,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>35260604483719000181550010000199251540262338</t>
+          <t>31260602226707000146550010001654991335925103</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -11825,24 +11823,26 @@
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+      <c r="N78" t="n">
+        <v>4513140471</v>
+      </c>
       <c r="O78" t="inlineStr">
         <is>
           <t>CONTAGEM</t>
         </is>
       </c>
       <c r="P78" s="1" t="n">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr">
         <is>
-          <t>TRILHOS FERROVIARIOS LTDA</t>
+          <t>PIPE SISTEMAS TUBULARES LTDA</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>TRILHOS</t>
+          <t>TUBO PIPE COR AC-40  368 X  4,75 X  6000</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -11851,21 +11851,21 @@
         </is>
       </c>
       <c r="U78" t="n">
-        <v>300294000</v>
+        <v>300299000</v>
       </c>
       <c r="V78" t="n">
-        <v>6000181110</v>
+        <v>6000182526</v>
       </c>
       <c r="W78" s="1" t="n">
-        <v>46196</v>
+        <v>46195</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>rfernanso</t>
+          <t>mvssilva</t>
         </is>
       </c>
       <c r="Y78" t="n">
-        <v>44492.85</v>
+        <v>23160.83</v>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         </is>
       </c>
       <c r="AB78" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
@@ -11887,12 +11887,12 @@
       </c>
       <c r="AD78" t="inlineStr">
         <is>
-          <t>MATERIAL SEM CONDIC?ES DE DESCARGA NO ARMAZEM DE BAR?O. MOTORISTA: WEBERT SILVIO JUNIO APARECIDO.PLACA:QQT0C42.</t>
+          <t>FOI ALINHADO ENTRE USUARIO (BRENO LOPES) COM A DELLA VOLPE QUE ESSES TUBOS TEM QUE SER DIRETO NA AREA PARA RECEBIMENTO.CARGA LOTACAO.</t>
         </is>
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>CONTAGEM/MG</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>BARAO DE COCAIS</t>
+          <t>NOVA LIMA</t>
         </is>
       </c>
       <c r="AH78" t="inlineStr">
@@ -11919,11 +11919,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>40814</t>
+          <t>40839</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1385757</v>
+        <v>1398444</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>17236</v>
+        <v>20049</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>35260604552842000107550010000172361019303890</t>
+          <t>35260457281743000102550010000200491151212390</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -11971,7 +11971,7 @@
       </c>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="n">
-        <v>4513210303</v>
+        <v>4101153628</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -11979,17 +11979,17 @@
         </is>
       </c>
       <c r="P79" s="1" t="n">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr">
         <is>
-          <t>POWER MASTER - TECNOLOGIA EM ACIONA</t>
+          <t>A EXPONENCIAL ESTANTES E MOVEIS DE</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>ELEMENTO ELASTICO E97</t>
+          <t>AC ARMARIO RECI</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
@@ -11998,21 +11998,21 @@
         </is>
       </c>
       <c r="U79" t="n">
-        <v>300294000</v>
+        <v>300297000</v>
       </c>
       <c r="V79" t="n">
-        <v>6000181114</v>
+        <v>6000182520</v>
       </c>
       <c r="W79" s="1" t="n">
-        <v>46196</v>
+        <v>46195</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>rfernanso</t>
+          <t>mvssilva</t>
         </is>
       </c>
       <c r="Y79" t="n">
-        <v>210.97</v>
+        <v>13110</v>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         </is>
       </c>
       <c r="AB79" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
@@ -12034,12 +12034,12 @@
       </c>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>FORA DO PASSAPORTE. MOTORISTA:ELI TOMAZ. PVV8D31.</t>
+          <t>NOTA FISCAL INAPTA.</t>
         </is>
       </c>
       <c r="AE79" t="inlineStr">
         <is>
-          <t>CONTAGEM/MG</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="AF79" t="inlineStr">
@@ -12049,7 +12049,7 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>OURO PRETO</t>
+          <t>MARIANA</t>
         </is>
       </c>
       <c r="AH79" t="inlineStr">
@@ -12066,11 +12066,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>40830</t>
+          <t>40846</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1400589</v>
+        <v>1389618</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -12079,11 +12079,11 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>TDV Contagem MG</t>
+          <t>TDV Serra- ES</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>165499</v>
+        <v>1569225</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
@@ -12108,7 +12108,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>31260602226707000146550010001654991335925103</t>
+          <t>32260646044053004607550010015692251038241990</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="n">
-        <v>4513140471</v>
+        <v>4513192045</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -12126,17 +12126,17 @@
         </is>
       </c>
       <c r="P80" s="1" t="n">
-        <v>46197</v>
+        <v>46199</v>
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr">
         <is>
-          <t>PIPE SISTEMAS TUBULARES LTDA</t>
+          <t>NORTEL SUPRIMENTOS INDUSTRIAIS S/A</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>TUBO PIPE COR AC-40  368 X  4,75 X  6000</t>
+          <t>CHAVE DESALIN ROL 500V 2NA+2NF ZV12H500</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
@@ -12145,21 +12145,21 @@
         </is>
       </c>
       <c r="U80" t="n">
-        <v>300299000</v>
+        <v>300300000</v>
       </c>
       <c r="V80" t="n">
-        <v>6000182526</v>
+        <v>6000182508</v>
       </c>
       <c r="W80" s="1" t="n">
         <v>46195</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>mvssilva</t>
+          <t>andias</t>
         </is>
       </c>
       <c r="Y80" t="n">
-        <v>23160.83</v>
+        <v>1629.84</v>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
@@ -12172,16 +12172,17 @@
         </is>
       </c>
       <c r="AB80" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="AD80" t="inlineStr">
         <is>
-          <t>FOI ALINHADO ENTRE USUARIO (BRENO LOPES) COM A DELLA VOLPE QUE ESSES TUBOS TEM QUE SER DIRETO NA AREA PARA RECEBIMENTO.CARGA LOTACAO.</t>
+          <t>NAO RECEBIDO, NF FORA DO PASSAPORTE.
+13/07 - NOTA INAPTA EMAIL ENVIADO .</t>
         </is>
       </c>
       <c r="AE80" t="inlineStr">
@@ -12196,7 +12197,7 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>NOVA LIMA</t>
+          <t>OURO PRETO</t>
         </is>
       </c>
       <c r="AH80" t="inlineStr">
@@ -12213,31 +12214,21 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>40839</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>1398444</v>
-      </c>
+          <t>40871</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>TDV São Paulo - SP</t>
-        </is>
-      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="n">
-        <v>20049</v>
+        <v>52773</v>
       </c>
       <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>FRACIONADO</t>
-        </is>
-      </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -12255,7 +12246,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>35260457281743000102550010000200491151212390</t>
+          <t>35260601236739000160550010000527731100079220</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -12264,49 +12255,37 @@
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
-      <c r="N81" t="n">
-        <v>4101153628</v>
-      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr">
         <is>
           <t>CONTAGEM</t>
         </is>
       </c>
       <c r="P81" s="1" t="n">
-        <v>46198</v>
+        <v>46203</v>
       </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr">
         <is>
-          <t>A EXPONENCIAL ESTANTES E MOVEIS DE</t>
-        </is>
-      </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>AC ARMARIO RECI</t>
-        </is>
-      </c>
+          <t>ALMONT DO BRASIL IMPORTACAO COM E R</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr">
         <is>
           <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
-      <c r="U81" t="n">
-        <v>300297000</v>
-      </c>
-      <c r="V81" t="n">
-        <v>6000182520</v>
-      </c>
-      <c r="W81" s="1" t="n">
-        <v>46195</v>
-      </c>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr">
         <is>
-          <t>mvssilva</t>
+          <t>allana</t>
         </is>
       </c>
       <c r="Y81" t="n">
-        <v>13110</v>
+        <v>13000</v>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
@@ -12319,7 +12298,7 @@
         </is>
       </c>
       <c r="AB81" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
@@ -12328,12 +12307,12 @@
       </c>
       <c r="AD81" t="inlineStr">
         <is>
-          <t>NOTA FISCAL INAPTA.</t>
+          <t>NOTA FISCAL FORA DO PASSAPORTE.</t>
         </is>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>CONTAGEM/MG</t>
         </is>
       </c>
       <c r="AF81" t="inlineStr">
@@ -12343,28 +12322,20 @@
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>MARIANA</t>
-        </is>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>VALE SA</t>
-        </is>
-      </c>
-      <c r="AI81" t="inlineStr">
-        <is>
-          <t>VALE SA</t>
-        </is>
-      </c>
+          <t>OURO PRETO</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr"/>
+      <c r="AI81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>40846</t>
+          <t>40874</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1389618</v>
+        <v>1377716</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -12373,11 +12344,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>TDV Serra- ES</t>
+          <t>TDV São Paulo - SP</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1569225</v>
+        <v>8294929</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
@@ -12402,7 +12373,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>32260646044053004607550010015692251038241990</t>
+          <t>35260654651716001150550000082949291382619716</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -12412,7 +12383,7 @@
       </c>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="n">
-        <v>4513192045</v>
+        <v>4513070950</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -12420,17 +12391,17 @@
         </is>
       </c>
       <c r="P82" s="1" t="n">
-        <v>46199</v>
+        <v>46204</v>
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr">
         <is>
-          <t>NORTEL SUPRIMENTOS INDUSTRIAIS S/A</t>
+          <t>SUPRICORP SUPRIMENTOS LTDA</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>CHAVE DESALIN ROL 500V 2NA+2NF ZV12H500</t>
+          <t>CAFE PO TRAD BRASILEIRO 500G CORPORATE</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
@@ -12439,21 +12410,17 @@
         </is>
       </c>
       <c r="U82" t="n">
-        <v>300300000</v>
-      </c>
-      <c r="V82" t="n">
-        <v>6000182508</v>
-      </c>
-      <c r="W82" s="1" t="n">
-        <v>46195</v>
-      </c>
+        <v>300292000</v>
+      </c>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr">
         <is>
           <t>andias</t>
         </is>
       </c>
       <c r="Y82" t="n">
-        <v>1629.84</v>
+        <v>772.66</v>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
@@ -12466,7 +12433,7 @@
         </is>
       </c>
       <c r="AB82" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
@@ -12475,8 +12442,8 @@
       </c>
       <c r="AD82" t="inlineStr">
         <is>
-          <t>NAO RECEBIDO, NF FORA DO PASSAPORTE.
-13/07 - NOTA INAPTA EMAIL ENVIADO .</t>
+          <t>NOTA RECUSADA, DEVIDO A FALTA DE VOLUME DO PAPEL CHAMEX.
+13/07 - EMAIL ENVIADO .</t>
         </is>
       </c>
       <c r="AE82" t="inlineStr">
@@ -12491,7 +12458,7 @@
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>OURO PRETO</t>
+          <t>BRUMADINHO</t>
         </is>
       </c>
       <c r="AH82" t="inlineStr">
@@ -12508,21 +12475,31 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>40871</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
+          <t>40898</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1387542</v>
+      </c>
       <c r="C83" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>TDV Rio de Janeiro - RJ</t>
+        </is>
+      </c>
       <c r="E83" t="n">
-        <v>52773</v>
+        <v>98950</v>
       </c>
       <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>FRACIONADO</t>
+        </is>
+      </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -12540,7 +12517,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>35260601236739000160550010000527731100079220</t>
+          <t>31260633592510044798550030000989501562176825</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -12549,37 +12526,45 @@
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+      <c r="N83" t="n">
+        <v>4512901040</v>
+      </c>
       <c r="O83" t="inlineStr">
         <is>
           <t>CONTAGEM</t>
         </is>
       </c>
       <c r="P83" s="1" t="n">
-        <v>46203</v>
+        <v>46206</v>
       </c>
       <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr">
-        <is>
-          <t>ALMONT DO BRASIL IMPORTACAO COM E R</t>
-        </is>
-      </c>
-      <c r="S83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>CORREIA T</t>
+        </is>
+      </c>
       <c r="T83" t="inlineStr">
         <is>
           <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr"/>
-      <c r="V83" t="inlineStr"/>
-      <c r="W83" t="inlineStr"/>
+      <c r="U83" t="n">
+        <v>300297000</v>
+      </c>
+      <c r="V83" t="n">
+        <v>6000179944</v>
+      </c>
+      <c r="W83" s="1" t="n">
+        <v>46189</v>
+      </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>allana</t>
+          <t>mvssilva</t>
         </is>
       </c>
       <c r="Y83" t="n">
-        <v>13000</v>
+        <v>9340.67</v>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
@@ -12592,7 +12577,7 @@
         </is>
       </c>
       <c r="AB83" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
@@ -12601,12 +12586,12 @@
       </c>
       <c r="AD83" t="inlineStr">
         <is>
-          <t>NOTA FISCAL FORA DO PASSAPORTE.</t>
+          <t>MATERIAL NAO DESCARREGA EM BARAO DE COCAIS, PERTENCE A MINA DE BRUCUTU</t>
         </is>
       </c>
       <c r="AE83" t="inlineStr">
         <is>
-          <t>CONTAGEM/MG</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="AF83" t="inlineStr">
@@ -12616,40 +12601,38 @@
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>OURO PRETO</t>
-        </is>
-      </c>
-      <c r="AH83" t="inlineStr"/>
-      <c r="AI83" t="inlineStr"/>
+          <t>SAO GONCALO DO RIO ABAIXO</t>
+        </is>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>VALE SA</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>VALE SA</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>40874</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>1377716</v>
-      </c>
+          <t>40924</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>TDV São Paulo - SP</t>
-        </is>
-      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="n">
-        <v>8294929</v>
+        <v>27027</v>
       </c>
       <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>FRACIONADO</t>
-        </is>
-      </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -12667,7 +12650,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>35260654651716001150550000082949291382619716</t>
+          <t>35260616622284000198550050000270271840093617</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -12676,45 +12659,37 @@
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
-      <c r="N84" t="n">
-        <v>4513070950</v>
-      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
         <is>
           <t>CONTAGEM</t>
         </is>
       </c>
       <c r="P84" s="1" t="n">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr">
         <is>
-          <t>SUPRICORP SUPRIMENTOS LTDA</t>
-        </is>
-      </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>CAFE PO TRAD BRASILEIRO 500G CORPORATE</t>
-        </is>
-      </c>
+          <t>METSO</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr"/>
       <c r="T84" t="inlineStr">
         <is>
           <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
-      <c r="U84" t="n">
-        <v>300292000</v>
-      </c>
+      <c r="U84" t="inlineStr"/>
       <c r="V84" t="inlineStr"/>
       <c r="W84" t="inlineStr"/>
       <c r="X84" t="inlineStr">
         <is>
-          <t>andias</t>
+          <t>rfernanso</t>
         </is>
       </c>
       <c r="Y84" t="n">
-        <v>772.66</v>
+        <v>837.02</v>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
@@ -12727,7 +12702,7 @@
         </is>
       </c>
       <c r="AB84" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
@@ -12736,13 +12711,15 @@
       </c>
       <c r="AD84" t="inlineStr">
         <is>
-          <t>NOTA RECUSADA, DEVIDO A FALTA DE VOLUME DO PAPEL CHAMEX.
-13/07 - EMAIL ENVIADO .</t>
+          <t>A MERCADORIA FOI RECUSADA DEVIDO A AUSENCIA DA NOTA FISCAL E DO CT-E.
+COMO SE TRATA DE UMA NOTA VALE, ACREDITO QUE SERA NECESSARIA A EMISS?O DE UM NOVO PVV PARA DAR CONTINUIDADE AO PROCESSO.
+MOTORISTA:VALDECIR DOS SANTOS ALVES.
+PLACA:SVR2H77.</t>
         </is>
       </c>
       <c r="AE84" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>CONTAGEM/MG</t>
         </is>
       </c>
       <c r="AF84" t="inlineStr">
@@ -12755,25 +12732,17 @@
           <t>BRUMADINHO</t>
         </is>
       </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>VALE SA</t>
-        </is>
-      </c>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>VALE SA</t>
-        </is>
-      </c>
+      <c r="AH84" t="inlineStr"/>
+      <c r="AI84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>40898</t>
+          <t>40925</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1387542</v>
+        <v>1330800</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -12782,11 +12751,11 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>TDV Rio de Janeiro - RJ</t>
+          <t>TDV Piracicaba - SP</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>98950</v>
+        <v>217997</v>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
@@ -12811,7 +12780,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>31260633592510044798550030000989501562176825</t>
+          <t>35260451482776000126550020002179971931797165</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -12821,7 +12790,7 @@
       </c>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="n">
-        <v>4512901040</v>
+        <v>4101159920</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -12829,13 +12798,17 @@
         </is>
       </c>
       <c r="P85" s="1" t="n">
-        <v>46206</v>
+        <v>46211</v>
       </c>
       <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>IMBIL INDUSTRIA E MANUTENCAO DE BOM</t>
+        </is>
+      </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>CORREIA T</t>
+          <t>CJ GIRANTE COMPLETO BP 100330 V02</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
@@ -12844,21 +12817,21 @@
         </is>
       </c>
       <c r="U85" t="n">
-        <v>300297000</v>
+        <v>300300000</v>
       </c>
       <c r="V85" t="n">
-        <v>6000179944</v>
+        <v>6000182530</v>
       </c>
       <c r="W85" s="1" t="n">
-        <v>46189</v>
+        <v>46196</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>mvssilva</t>
+          <t>bmatozine</t>
         </is>
       </c>
       <c r="Y85" t="n">
-        <v>9340.67</v>
+        <v>19508.1</v>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
@@ -12871,7 +12844,7 @@
         </is>
       </c>
       <c r="AB85" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
@@ -12880,12 +12853,12 @@
       </c>
       <c r="AD85" t="inlineStr">
         <is>
-          <t>MATERIAL NAO DESCARREGA EM BARAO DE COCAIS, PERTENCE A MINA DE BRUCUTU</t>
+          <t>MATERIA N?O CONSTA NO AGENDAMENTO. 111190000021814.</t>
         </is>
       </c>
       <c r="AE85" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>CONTAGEM/MG</t>
         </is>
       </c>
       <c r="AF85" t="inlineStr">
@@ -12895,7 +12868,7 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>SAO GONCALO DO RIO ABAIXO</t>
+          <t>NOVA LIMA</t>
         </is>
       </c>
       <c r="AH85" t="inlineStr">
@@ -12912,21 +12885,31 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>40924</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
+          <t>41003</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>950538</v>
+      </c>
       <c r="C86" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>TDV Contagem MG</t>
+        </is>
+      </c>
       <c r="E86" t="n">
-        <v>27027</v>
+        <v>233471</v>
       </c>
       <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>FRACIONADO</t>
+        </is>
+      </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -12944,7 +12927,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>35260616622284000198550050000270271840093617</t>
+          <t>31250300548473000128550010002334711219217356</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -12960,15 +12943,21 @@
         </is>
       </c>
       <c r="P86" s="1" t="n">
-        <v>46211</v>
-      </c>
-      <c r="Q86" t="inlineStr"/>
+        <v>46223</v>
+      </c>
+      <c r="Q86" s="1" t="n">
+        <v>45862.59861111111</v>
+      </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>METSO</t>
-        </is>
-      </c>
-      <c r="S86" t="inlineStr"/>
+          <t>HIDRAU MAQUINAS MANGUEIRAS E CONEXO</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>SERVIÇO DE TRANSPORTE</t>
+        </is>
+      </c>
       <c r="T86" t="inlineStr">
         <is>
           <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
@@ -12979,15 +12968,15 @@
       <c r="W86" t="inlineStr"/>
       <c r="X86" t="inlineStr">
         <is>
-          <t>rfernanso</t>
+          <t>bmatozine</t>
         </is>
       </c>
       <c r="Y86" t="n">
-        <v>837.02</v>
+        <v>733.79</v>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>No Prazo</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -12996,7 +12985,7 @@
         </is>
       </c>
       <c r="AB86" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
@@ -13005,10 +12994,8 @@
       </c>
       <c r="AD86" t="inlineStr">
         <is>
-          <t>A MERCADORIA FOI RECUSADA DEVIDO A AUSENCIA DA NOTA FISCAL E DO CT-E.
-COMO SE TRATA DE UMA NOTA VALE, ACREDITO QUE SERA NECESSARIA A EMISS?O DE UM NOVO PVV PARA DAR CONTINUIDADE AO PROCESSO.
-MOTORISTA:VALDECIR DOS SANTOS ALVES.
-PLACA:SVR2H77.</t>
+          <t>NOTA INAPTA.
+DEVOLUC?O A PEDIDO DO DAVI</t>
         </is>
       </c>
       <c r="AE86" t="inlineStr">
@@ -13018,25 +13005,33 @@
       </c>
       <c r="AF86" t="inlineStr">
         <is>
-          <t>Acima de 12 Dias</t>
+          <t>0 - 8 Dias</t>
         </is>
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>BRUMADINHO</t>
-        </is>
-      </c>
-      <c r="AH86" t="inlineStr"/>
-      <c r="AI86" t="inlineStr"/>
+          <t>NOVA ERA</t>
+        </is>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>VALE S.A.</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>TRANSPORTES DELLA VOLPE S A COMERCI</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>40925</t>
+          <t>40310</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1330800</v>
+        <v>915140</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -13045,11 +13040,11 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>TDV Piracicaba - SP</t>
+          <t>TDV São Paulo - SP</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>217997</v>
+        <v>130303</v>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
@@ -13064,17 +13059,17 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Contagem MG</t>
+          <t>Itabira - MG</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>ITABIRA</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>35260451482776000126550020002179971931797165</t>
+          <t>35251265837262000150550010001303031000700176</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -13084,25 +13079,25 @@
       </c>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="n">
-        <v>4101159920</v>
+        <v>4512514510</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>ITABIRA</t>
         </is>
       </c>
       <c r="P87" s="1" t="n">
-        <v>46211</v>
+        <v>46147</v>
       </c>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr">
         <is>
-          <t>IMBIL INDUSTRIA E MANUTENCAO DE BOM</t>
+          <t>ROLATEL COM DE ROLAMENTOS LT</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>CJ GIRANTE COMPLETO BP 100330 V02</t>
+          <t>OHA 3138H BUCHA</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
@@ -13111,21 +13106,21 @@
         </is>
       </c>
       <c r="U87" t="n">
-        <v>300300000</v>
+        <v>300192000</v>
       </c>
       <c r="V87" t="n">
-        <v>6000182530</v>
+        <v>6000116068</v>
       </c>
       <c r="W87" s="1" t="n">
-        <v>46196</v>
+        <v>46030</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>bmatozine</t>
+          <t>lbraz</t>
         </is>
       </c>
       <c r="Y87" t="n">
-        <v>19508.1</v>
+        <v>4418.2</v>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
@@ -13138,7 +13133,7 @@
         </is>
       </c>
       <c r="AB87" t="n">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
@@ -13147,12 +13142,12 @@
       </c>
       <c r="AD87" t="inlineStr">
         <is>
-          <t>MATERIA N?O CONSTA NO AGENDAMENTO. 111190000021814.</t>
+          <t>MATERIAL ESTAVA PARADO NA VALE POR PROBLEMAS DE NOTA INAPTA, TENTEI COM O FORNECEDOR VALIDAC?O DA NF, POREM SEN SUCESSO, MATERIAL SEGUE PARA TDV CONTAGEM PAR ADEVOLVER AO FORNECEDOR.</t>
         </is>
       </c>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>CONTAGEM/MG</t>
+          <t>BOM JESUS DO AMPARO/MG</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
@@ -13162,7 +13157,7 @@
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>NOVA LIMA</t>
+          <t>BARAO DE COCAIS</t>
         </is>
       </c>
       <c r="AH87" t="inlineStr">
@@ -13172,18 +13167,18 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>VALE SA</t>
+          <t>ROLATEL COM DE ROLAMENTOS LT</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>41003</t>
+          <t>39820</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>950538</v>
+        <v>1005753</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -13192,11 +13187,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>TDV Contagem MG</t>
+          <t>TDV Piracicaba - SP</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>233471</v>
+        <v>1041040</v>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
@@ -13211,17 +13206,17 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Contagem MG</t>
+          <t>Parauapebas - PA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>PARAUAPEBAS</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>31250300548473000128550010002334711219217356</t>
+          <t>35260156215999000817550010010410401204604972</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -13230,47 +13225,53 @@
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+      <c r="N88" t="n">
+        <v>4512750157</v>
+      </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>PARAUAPEBAS</t>
         </is>
       </c>
       <c r="P88" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="Q88" s="1" t="n">
-        <v>45862.59861111111</v>
-      </c>
+        <v>46097</v>
+      </c>
+      <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr">
         <is>
-          <t>HIDRAU MAQUINAS MANGUEIRAS E CONEXO</t>
+          <t>INFORSHOP SUPRIMENTOS LT</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>SERVIÇO DE TRANSPORTE</t>
+          <t>ACUCAR CRISTAL PREMIUM SACHE 5G CX C/ 40</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr"/>
-      <c r="V88" t="inlineStr"/>
-      <c r="W88" t="inlineStr"/>
+          <t>NOTA FISCAL DIVERGENTE</t>
+        </is>
+      </c>
+      <c r="U88" t="n">
+        <v>300212000</v>
+      </c>
+      <c r="V88" t="n">
+        <v>6000128001</v>
+      </c>
+      <c r="W88" s="1" t="n">
+        <v>46058</v>
+      </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>bmatozine</t>
+          <t>jsconceica</t>
         </is>
       </c>
       <c r="Y88" t="n">
-        <v>733.79</v>
+        <v>220.8</v>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>No Prazo</t>
+          <t>Atrasado</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -13279,7 +13280,7 @@
         </is>
       </c>
       <c r="AB88" t="n">
-        <v>1</v>
+        <v>127</v>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
@@ -13288,44 +13289,43 @@
       </c>
       <c r="AD88" t="inlineStr">
         <is>
-          <t>NOTA INAPTA.
-DEVOLUC?O A PEDIDO DO DAVI</t>
+          <t>OM ENCERRADA</t>
         </is>
       </c>
       <c r="AE88" t="inlineStr">
         <is>
-          <t>CONTAGEM/MG</t>
+          <t>IPATINGA/MG</t>
         </is>
       </c>
       <c r="AF88" t="inlineStr">
         <is>
-          <t>0 - 8 Dias</t>
+          <t>Acima de 12 Dias</t>
         </is>
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>NOVA ERA</t>
+          <t>PARAUAPEBAS</t>
         </is>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
-          <t>VALE S.A.</t>
+          <t>VALE SA</t>
         </is>
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>TRANSPORTES DELLA VOLPE S A COMERCI</t>
+          <t>VALE SA</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>40310</t>
+          <t>40208</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>915140</v>
+        <v>1215814</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -13338,7 +13338,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>130303</v>
+        <v>42349</v>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
@@ -13353,17 +13353,17 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Itabira - MG</t>
+          <t>Parauapebas - PA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>ITABIRA</t>
+          <t>PARAUAPEBAS</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>35251265837262000150550010001303031000700176</t>
+          <t>35260372908817000173550070000423491273779017</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -13373,48 +13373,48 @@
       </c>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="n">
-        <v>4512514510</v>
+        <v>4511194843</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>ITABIRA</t>
+          <t>PARAUAPEBAS</t>
         </is>
       </c>
       <c r="P89" s="1" t="n">
-        <v>46147</v>
+        <v>46135</v>
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr">
         <is>
-          <t>ROLATEL COM DE ROLAMENTOS LT</t>
+          <t>BOSCH REXROTH LTDA</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>OHA 3138H BUCHA</t>
+          <t>CILINDRO HIDR DUP 600MM</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
+          <t>NOTA FISCAL DIVERGENTE</t>
         </is>
       </c>
       <c r="U89" t="n">
-        <v>300192000</v>
+        <v>300259000</v>
       </c>
       <c r="V89" t="n">
-        <v>6000116068</v>
+        <v>6000155976</v>
       </c>
       <c r="W89" s="1" t="n">
-        <v>46030</v>
+        <v>46128</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>lbraz</t>
+          <t>jsconceica</t>
         </is>
       </c>
       <c r="Y89" t="n">
-        <v>4418.2</v>
+        <v>560813.85</v>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         </is>
       </c>
       <c r="AB89" t="n">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
@@ -13436,12 +13436,12 @@
       </c>
       <c r="AD89" t="inlineStr">
         <is>
-          <t>MATERIAL ESTAVA PARADO NA VALE POR PROBLEMAS DE NOTA INAPTA, TENTEI COM O FORNECEDOR VALIDAC?O DA NF, POREM SEN SUCESSO, MATERIAL SEGUE PARA TDV CONTAGEM PAR ADEVOLVER AO FORNECEDOR.</t>
+          <t>ERRO DE XML</t>
         </is>
       </c>
       <c r="AE89" t="inlineStr">
         <is>
-          <t>BOM JESUS DO AMPARO/MG</t>
+          <t>IPATINGA/MG</t>
         </is>
       </c>
       <c r="AF89" t="inlineStr">
@@ -13451,28 +13451,28 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>BARAO DE COCAIS</t>
+          <t>PARAUAPEBAS</t>
         </is>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>VALE SA</t>
+          <t>VALE S.A.</t>
         </is>
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>ROLATEL COM DE ROLAMENTOS LT</t>
+          <t>VALE SA</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>39820</t>
+          <t>40275</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1005753</v>
+        <v>1221813</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -13481,11 +13481,11 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>TDV Piracicaba - SP</t>
+          <t>TDV Contagem MG</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1041040</v>
+        <v>9023</v>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
@@ -13510,7 +13510,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>35260156215999000817550010010410401204604972</t>
+          <t>31260440568697000116550010000090231130621303</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -13520,7 +13520,7 @@
       </c>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="n">
-        <v>4512750157</v>
+        <v>4101182236</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -13528,32 +13528,32 @@
         </is>
       </c>
       <c r="P90" s="1" t="n">
-        <v>46097</v>
+        <v>46140</v>
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr">
         <is>
-          <t>INFORSHOP SUPRIMENTOS LT</t>
+          <t>MLM MECATRONICA E EQUIPAMENTOS LTD</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>ACUCAR CRISTAL PREMIUM SACHE 5G CX C/ 40</t>
+          <t>GIROFLEX ROT. MULT. LED AM 24-110VCA/CC</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>NOTA FISCAL DIVERGENTE</t>
+          <t>PEDIDO INEXISTENTE</t>
         </is>
       </c>
       <c r="U90" t="n">
-        <v>300212000</v>
+        <v>300258000</v>
       </c>
       <c r="V90" t="n">
-        <v>6000128001</v>
+        <v>6000161543</v>
       </c>
       <c r="W90" s="1" t="n">
-        <v>46058</v>
+        <v>46142</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         </is>
       </c>
       <c r="Y90" t="n">
-        <v>220.8</v>
+        <v>224.97</v>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
@@ -13574,7 +13574,7 @@
         </is>
       </c>
       <c r="AB90" t="n">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
       </c>
       <c r="AD90" t="inlineStr">
         <is>
-          <t>OM ENCERRADA</t>
+          <t>MATERIAL COM REMESSA INEXISTENTE</t>
         </is>
       </c>
       <c r="AE90" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>VALE SA</t>
+          <t>VALE S.A.</t>
         </is>
       </c>
       <c r="AI90" t="inlineStr">
@@ -13615,11 +13615,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>40208</t>
+          <t>40759</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1215814</v>
+        <v>1396947</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -13628,16 +13628,16 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>TDV São Paulo - SP</t>
+          <t>TDV Parauapebas - PA</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>42349</v>
+        <v>1864251</v>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>FRACIONADO</t>
+          <t>LOTACAO</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -13657,7 +13657,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>35260372908817000173550070000423491273779017</t>
+          <t>15260634151100000645550010018642511004011363</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -13667,7 +13667,7 @@
       </c>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="n">
-        <v>4511194843</v>
+        <v>4512125331</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -13675,32 +13675,32 @@
         </is>
       </c>
       <c r="P91" s="1" t="n">
-        <v>46135</v>
+        <v>46191</v>
       </c>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr">
         <is>
-          <t>BOSCH REXROTH LTDA</t>
+          <t>SOTREQ S/A</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>CILINDRO HIDR DUP 600MM</t>
+          <t>RODA</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>NOTA FISCAL DIVERGENTE</t>
+          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
       <c r="U91" t="n">
-        <v>300259000</v>
+        <v>300297000</v>
       </c>
       <c r="V91" t="n">
-        <v>6000155976</v>
+        <v>6000180373</v>
       </c>
       <c r="W91" s="1" t="n">
-        <v>46128</v>
+        <v>46190</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         </is>
       </c>
       <c r="Y91" t="n">
-        <v>560813.85</v>
+        <v>523728.78</v>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         </is>
       </c>
       <c r="AB91" t="n">
-        <v>89</v>
+        <v>33</v>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
       </c>
       <c r="AD91" t="inlineStr">
         <is>
-          <t>ERRO DE XML</t>
+          <t>MATERIAL N?O FOI  DESCARREGADO NO ARMAZEM, PORQUER N?O DEU REPARO E N?O CONSEGUIRAM FALAR COM A AREA RECEBEDORA. LUCIANA LIMA</t>
         </is>
       </c>
       <c r="AE91" t="inlineStr">
@@ -13745,7 +13745,7 @@
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>PARAUAPEBAS</t>
+          <t>CANAA DOS CARAJAS</t>
         </is>
       </c>
       <c r="AH91" t="inlineStr">
@@ -13762,11 +13762,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>40275</t>
+          <t>40765</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1221813</v>
+        <v>1333447</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>9023</v>
+        <v>61748</v>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>31260440568697000116550010000090231130621303</t>
+          <t>31260505166746000193550010000617481201912630</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -13814,7 +13814,7 @@
       </c>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="n">
-        <v>4101182236</v>
+        <v>4512905097</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -13822,32 +13822,32 @@
         </is>
       </c>
       <c r="P92" s="1" t="n">
-        <v>46140</v>
+        <v>46191</v>
       </c>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr">
         <is>
-          <t>MLM MECATRONICA E EQUIPAMENTOS LTD</t>
+          <t>USELIGAS INDUSTRIA E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>GIROFLEX ROT. MULT. LED AM 24-110VCA/CC</t>
+          <t>Revestimento da Voluta (1022)</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>PEDIDO INEXISTENTE</t>
+          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
       <c r="U92" t="n">
-        <v>300258000</v>
+        <v>300285000</v>
       </c>
       <c r="V92" t="n">
-        <v>6000161543</v>
+        <v>6000176765</v>
       </c>
       <c r="W92" s="1" t="n">
-        <v>46142</v>
+        <v>46182</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
         </is>
       </c>
       <c r="Y92" t="n">
-        <v>224.97</v>
+        <v>14911.43</v>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         </is>
       </c>
       <c r="AB92" t="n">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
       </c>
       <c r="AD92" t="inlineStr">
         <is>
-          <t>MATERIAL COM REMESSA INEXISTENTE</t>
+          <t>NF REJEITADA, COMPRADO ERRADO</t>
         </is>
       </c>
       <c r="AE92" t="inlineStr">
@@ -13892,7 +13892,7 @@
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>PARAUAPEBAS</t>
+          <t>CURIONOPOLIS</t>
         </is>
       </c>
       <c r="AH92" t="inlineStr">
@@ -13909,11 +13909,11 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>40759</t>
+          <t>40841</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1396947</v>
+        <v>1377780</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -13922,16 +13922,16 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>TDV Parauapebas - PA</t>
+          <t>TDV Contagem MG</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1864251</v>
+        <v>1479499</v>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>LOTACAO</t>
+          <t>FRACIONADO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>15260634151100000645550010018642511004011363</t>
+          <t>31260534151100001706550020014794991579085850</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -13961,7 +13961,7 @@
       </c>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="n">
-        <v>4512125331</v>
+        <v>4511301221</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -13969,17 +13969,17 @@
         </is>
       </c>
       <c r="P93" s="1" t="n">
-        <v>46191</v>
+        <v>46198</v>
       </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr">
         <is>
-          <t>SOTREQ S/A</t>
+          <t>Sotreq SA</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>RODA</t>
+          <t>Eixo</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
@@ -13988,13 +13988,13 @@
         </is>
       </c>
       <c r="U93" t="n">
-        <v>300297000</v>
+        <v>300295000</v>
       </c>
       <c r="V93" t="n">
-        <v>6000180373</v>
+        <v>6000179346</v>
       </c>
       <c r="W93" s="1" t="n">
-        <v>46190</v>
+        <v>46188</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         </is>
       </c>
       <c r="Y93" t="n">
-        <v>523728.78</v>
+        <v>29382.76</v>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         </is>
       </c>
       <c r="AB93" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
       </c>
       <c r="AD93" t="inlineStr">
         <is>
-          <t>MATERIAL N?O FOI  DESCARREGADO NO ARMAZEM, PORQUER N?O DEU REPARO E N?O CONSEGUIRAM FALAR COM A AREA RECEBEDORA. LUCIANA LIMA</t>
+          <t>DEVOLDIVO. CLIENTE N?O FEZ FDM.</t>
         </is>
       </c>
       <c r="AE93" t="inlineStr">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>CANAA DOS CARAJAS</t>
+          <t>PARAUAPEBAS</t>
         </is>
       </c>
       <c r="AH93" t="inlineStr">
@@ -14056,11 +14056,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>40765</t>
+          <t>40842</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1333447</v>
+        <v>1372058</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>61748</v>
+        <v>13908</v>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
@@ -14098,7 +14098,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>31260505166746000193550010000617481201912630</t>
+          <t>31260628763819000472550550000139081224019524</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -14108,7 +14108,7 @@
       </c>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="n">
-        <v>4512905097</v>
+        <v>4512205579</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -14116,17 +14116,17 @@
         </is>
       </c>
       <c r="P94" s="1" t="n">
-        <v>46191</v>
+        <v>46198</v>
       </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr">
         <is>
-          <t>USELIGAS INDUSTRIA E COMERCIO LTDA</t>
+          <t>EPIROC BRASIL COMERCIALIZACAO DE PR</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>Revestimento da Voluta (1022)</t>
+          <t>BOMBA</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
@@ -14135,13 +14135,13 @@
         </is>
       </c>
       <c r="U94" t="n">
-        <v>300285000</v>
+        <v>300295000</v>
       </c>
       <c r="V94" t="n">
-        <v>6000176765</v>
+        <v>6000179346</v>
       </c>
       <c r="W94" s="1" t="n">
-        <v>46182</v>
+        <v>46188</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         </is>
       </c>
       <c r="Y94" t="n">
-        <v>14911.43</v>
+        <v>57768.5</v>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         </is>
       </c>
       <c r="AB94" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
       </c>
       <c r="AD94" t="inlineStr">
         <is>
-          <t>NF REJEITADA, COMPRADO ERRADO</t>
+          <t>DEVOLDIVO. CLIENTE N?O FEZ FDM.</t>
         </is>
       </c>
       <c r="AE94" t="inlineStr">
@@ -14186,7 +14186,7 @@
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>CURIONOPOLIS</t>
+          <t>PARAUAPEBAS</t>
         </is>
       </c>
       <c r="AH94" t="inlineStr">
@@ -14203,11 +14203,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>40841</t>
+          <t>40843</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1377780</v>
+        <v>1365867</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1479499</v>
+        <v>16171</v>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
@@ -14245,7 +14245,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>31260534151100001706550020014794991579085850</t>
+          <t>31260610829962000101550010000161711807114092</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -14254,9 +14254,7 @@
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
-      <c r="N95" t="n">
-        <v>4511301221</v>
-      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
         <is>
           <t>PARAUAPEBAS</t>
@@ -14268,12 +14266,12 @@
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr">
         <is>
-          <t>Sotreq SA</t>
+          <t>POLIWAY INDUSTRIA E COMERCIO DE MAQ</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>Eixo</t>
+          <t>AUTO ALINHADOR DE CARGA TD ZHD 84 PU VO</t>
         </is>
       </c>
       <c r="T95" t="inlineStr">
@@ -14296,7 +14294,7 @@
         </is>
       </c>
       <c r="Y95" t="n">
-        <v>29382.76</v>
+        <v>150</v>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
@@ -14318,7 +14316,7 @@
       </c>
       <c r="AD95" t="inlineStr">
         <is>
-          <t>DEVOLDIVO. CLIENTE N?O FEZ FDM.</t>
+          <t>N?O FOI POSIVEL LOCALIZR  O CLIENTE. DEVOLVER PARA O FORNECEDOR.</t>
         </is>
       </c>
       <c r="AE95" t="inlineStr">
@@ -14350,11 +14348,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>40842</t>
+          <t>40880</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1372058</v>
+        <v>1231384</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -14363,11 +14361,11 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>TDV Contagem MG</t>
+          <t>TDV São Paulo - SP</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>13908</v>
+        <v>2731155</v>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
@@ -14392,7 +14390,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>31260628763819000472550550000139081224019524</t>
+          <t>35260457582793000111550010027311551324126539</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -14402,7 +14400,7 @@
       </c>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="n">
-        <v>4512205579</v>
+        <v>4513007972</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -14410,32 +14408,32 @@
         </is>
       </c>
       <c r="P96" s="1" t="n">
-        <v>46198</v>
+        <v>46205</v>
       </c>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr">
         <is>
-          <t>EPIROC BRASIL COMERCIALIZACAO DE PR</t>
+          <t>FESTO  BRASIL LTDA</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>BOMBA</t>
+          <t>TUBO FLEXIVEL PUN-12X2-BL LINHA 10</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
+          <t>PEDIDO INEXISTENTE</t>
         </is>
       </c>
       <c r="U96" t="n">
-        <v>300295000</v>
+        <v>300261000</v>
       </c>
       <c r="V96" t="n">
-        <v>6000179346</v>
+        <v>6000157534</v>
       </c>
       <c r="W96" s="1" t="n">
-        <v>46188</v>
+        <v>46132</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -14443,7 +14441,7 @@
         </is>
       </c>
       <c r="Y96" t="n">
-        <v>57768.5</v>
+        <v>1366</v>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
@@ -14456,7 +14454,7 @@
         </is>
       </c>
       <c r="AB96" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
@@ -14465,7 +14463,7 @@
       </c>
       <c r="AD96" t="inlineStr">
         <is>
-          <t>DEVOLDIVO. CLIENTE N?O FEZ FDM.</t>
+          <t>MATERIAL RECUSADO, PEDIDO EXCLUIDO.</t>
         </is>
       </c>
       <c r="AE96" t="inlineStr">
@@ -14485,7 +14483,7 @@
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>VALE S.A.</t>
+          <t>VALE SA</t>
         </is>
       </c>
       <c r="AI96" t="inlineStr">
@@ -14497,31 +14495,21 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>40843</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>1365867</v>
-      </c>
+          <t>40881</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>TDV Contagem MG</t>
-        </is>
-      </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="n">
-        <v>16171</v>
+        <v>2731150</v>
       </c>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>FRACIONADO</t>
-        </is>
-      </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -14539,7 +14527,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>31260610829962000101550010000161711807114092</t>
+          <t>352604575893000111550010027311501907938932</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -14555,40 +14543,30 @@
         </is>
       </c>
       <c r="P97" s="1" t="n">
-        <v>46198</v>
+        <v>46205</v>
       </c>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr">
         <is>
-          <t>POLIWAY INDUSTRIA E COMERCIO DE MAQ</t>
-        </is>
-      </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>AUTO ALINHADOR DE CARGA TD ZHD 84 PU VO</t>
-        </is>
-      </c>
+          <t>FESTO  BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr"/>
       <c r="T97" t="inlineStr">
         <is>
-          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
-        </is>
-      </c>
-      <c r="U97" t="n">
-        <v>300295000</v>
-      </c>
-      <c r="V97" t="n">
-        <v>6000179346</v>
-      </c>
-      <c r="W97" s="1" t="n">
-        <v>46188</v>
-      </c>
+          <t>PEDIDO INEXISTENTE</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr"/>
+      <c r="W97" t="inlineStr"/>
       <c r="X97" t="inlineStr">
         <is>
           <t>jsconceica</t>
         </is>
       </c>
       <c r="Y97" t="n">
-        <v>150</v>
+        <v>1366</v>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
@@ -14601,7 +14579,7 @@
         </is>
       </c>
       <c r="AB97" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
@@ -14610,7 +14588,7 @@
       </c>
       <c r="AD97" t="inlineStr">
         <is>
-          <t>N?O FOI POSIVEL LOCALIZR  O CLIENTE. DEVOLVER PARA O FORNECEDOR.</t>
+          <t>MATERIAL RECUSADO, PEDIDO EXCLUIDO.</t>
         </is>
       </c>
       <c r="AE97" t="inlineStr">
@@ -14628,25 +14606,17 @@
           <t>PARAUAPEBAS</t>
         </is>
       </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>VALE S.A.</t>
-        </is>
-      </c>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>VALE SA</t>
-        </is>
-      </c>
+      <c r="AH97" t="inlineStr"/>
+      <c r="AI97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>40880</t>
+          <t>40890</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1231384</v>
+        <v>1419575</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -14659,7 +14629,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2731155</v>
+        <v>398359</v>
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
@@ -14684,7 +14654,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>35260457582793000111550010027311551324126539</t>
+          <t>35260660806460000567550010003983591555267998</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -14694,7 +14664,7 @@
       </c>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="n">
-        <v>4513007972</v>
+        <v>4513232064</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -14707,35 +14677,27 @@
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr">
         <is>
-          <t>FESTO  BRASIL LTDA</t>
-        </is>
-      </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>TUBO FLEXIVEL PUN-12X2-BL LINHA 10</t>
-        </is>
-      </c>
+          <t>FERCOI S/A</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr"/>
       <c r="T98" t="inlineStr">
         <is>
-          <t>PEDIDO INEXISTENTE</t>
+          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
       <c r="U98" t="n">
-        <v>300261000</v>
-      </c>
-      <c r="V98" t="n">
-        <v>6000157534</v>
-      </c>
-      <c r="W98" s="1" t="n">
-        <v>46132</v>
-      </c>
+        <v>300301000</v>
+      </c>
+      <c r="V98" t="inlineStr"/>
+      <c r="W98" t="inlineStr"/>
       <c r="X98" t="inlineStr">
         <is>
           <t>jsconceica</t>
         </is>
       </c>
       <c r="Y98" t="n">
-        <v>1366</v>
+        <v>1123.7</v>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
@@ -14752,12 +14714,12 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="AD98" t="inlineStr">
         <is>
-          <t>MATERIAL RECUSADO, PEDIDO EXCLUIDO.</t>
+          <t>MATERIAL SENDO DEVOLVIDO POR ESTA MAL ACONDICIONADO.</t>
         </is>
       </c>
       <c r="AE98" t="inlineStr">
@@ -14789,21 +14751,31 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>40881</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr"/>
+          <t>40891</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>1419431</v>
+      </c>
       <c r="C99" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>TDV São Paulo - SP</t>
+        </is>
+      </c>
       <c r="E99" t="n">
-        <v>2731150</v>
+        <v>398377</v>
       </c>
       <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>FRACIONADO</t>
+        </is>
+      </c>
       <c r="H99" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -14821,7 +14793,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>352604575893000111550010027311501907938932</t>
+          <t>35260660806460000567550010003983771302318886</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -14830,7 +14802,9 @@
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+      <c r="N99" t="n">
+        <v>4513252772</v>
+      </c>
       <c r="O99" t="inlineStr">
         <is>
           <t>PARAUAPEBAS</t>
@@ -14842,16 +14816,18 @@
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr">
         <is>
-          <t>FESTO  BRASIL LTDA</t>
+          <t>FERCOI S/A</t>
         </is>
       </c>
       <c r="S99" t="inlineStr"/>
       <c r="T99" t="inlineStr">
         <is>
-          <t>PEDIDO INEXISTENTE</t>
-        </is>
-      </c>
-      <c r="U99" t="inlineStr"/>
+          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
+        </is>
+      </c>
+      <c r="U99" t="n">
+        <v>300301000</v>
+      </c>
       <c r="V99" t="inlineStr"/>
       <c r="W99" t="inlineStr"/>
       <c r="X99" t="inlineStr">
@@ -14860,7 +14836,7 @@
         </is>
       </c>
       <c r="Y99" t="n">
-        <v>1366</v>
+        <v>22551.25</v>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
@@ -14877,12 +14853,12 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="AD99" t="inlineStr">
         <is>
-          <t>MATERIAL RECUSADO, PEDIDO EXCLUIDO.</t>
+          <t>MATERIAL SENDO DEVOLVIDO POR ESTA MAL ACONDICIONADO.</t>
         </is>
       </c>
       <c r="AE99" t="inlineStr">
@@ -14900,17 +14876,25 @@
           <t>PARAUAPEBAS</t>
         </is>
       </c>
-      <c r="AH99" t="inlineStr"/>
-      <c r="AI99" t="inlineStr"/>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>VALE SA</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>VALE SA</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40892</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1419575</v>
+        <v>1419505</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -14923,7 +14907,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>398359</v>
+        <v>398362</v>
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
@@ -14948,7 +14932,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>35260660806460000567550010003983591555267998</t>
+          <t>35260660806460000567550010003983621206357792</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -14958,7 +14942,7 @@
       </c>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="n">
-        <v>4513232064</v>
+        <v>4513245163</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
@@ -14991,7 +14975,7 @@
         </is>
       </c>
       <c r="Y100" t="n">
-        <v>1123.7</v>
+        <v>2827.23</v>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
@@ -15045,11 +15029,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>40891</t>
+          <t>40893</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1419431</v>
+        <v>1405708</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -15062,7 +15046,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>398377</v>
+        <v>120961</v>
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
@@ -15087,7 +15071,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>35260660806460000567550010003983771302318886</t>
+          <t>35260645010717000152550030001209611095001739</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -15097,7 +15081,7 @@
       </c>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="n">
-        <v>4513252772</v>
+        <v>4101143886</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -15110,17 +15094,21 @@
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr">
         <is>
-          <t>FERCOI S/A</t>
-        </is>
-      </c>
-      <c r="S101" t="inlineStr"/>
+          <t>POLIERG IND COM LT</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>TUBO PEAD 180x20,1 PN20 PE100 PR ISO 2EX</t>
+        </is>
+      </c>
       <c r="T101" t="inlineStr">
         <is>
           <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
       <c r="U101" t="n">
-        <v>300301000</v>
+        <v>300299000</v>
       </c>
       <c r="V101" t="inlineStr"/>
       <c r="W101" t="inlineStr"/>
@@ -15130,7 +15118,7 @@
         </is>
       </c>
       <c r="Y101" t="n">
-        <v>22551.25</v>
+        <v>74609.42</v>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
@@ -15172,7 +15160,7 @@
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>VALE SA</t>
+          <t>VALE S.A.</t>
         </is>
       </c>
       <c r="AI101" t="inlineStr">
@@ -15184,11 +15172,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>40892</t>
+          <t>40894</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1419505</v>
+        <v>1393295</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -15201,7 +15189,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>398362</v>
+        <v>474374</v>
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
@@ -15226,7 +15214,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>35260660806460000567550010003983621206357792</t>
+          <t>35260653234274000101550010004743741776981518</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -15236,7 +15224,7 @@
       </c>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="n">
-        <v>4513245163</v>
+        <v>4101185678</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
@@ -15249,17 +15237,21 @@
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr">
         <is>
-          <t>FERCOI S/A</t>
-        </is>
-      </c>
-      <c r="S102" t="inlineStr"/>
+          <t>PLASTIREAL INDUSTRIA E COMERCIO DE</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>TUBO LISO PEAD PE-100 SDR 9 PN 20 PRETO</t>
+        </is>
+      </c>
       <c r="T102" t="inlineStr">
         <is>
           <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
       <c r="U102" t="n">
-        <v>300301000</v>
+        <v>300297000</v>
       </c>
       <c r="V102" t="inlineStr"/>
       <c r="W102" t="inlineStr"/>
@@ -15269,7 +15261,7 @@
         </is>
       </c>
       <c r="Y102" t="n">
-        <v>2827.23</v>
+        <v>9800</v>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
@@ -15311,7 +15303,7 @@
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>VALE SA</t>
+          <t>VALE S.A.</t>
         </is>
       </c>
       <c r="AI102" t="inlineStr">
@@ -15323,11 +15315,11 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>40893</t>
+          <t>40895</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1405708</v>
+        <v>1392305</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -15340,7 +15332,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>120961</v>
+        <v>474373</v>
       </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
@@ -15365,7 +15357,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>35260645010717000152550030001209611095001739</t>
+          <t>35260653234274000101550010004743731813460906</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -15375,7 +15367,7 @@
       </c>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="n">
-        <v>4101143886</v>
+        <v>4101185625</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
@@ -15388,12 +15380,12 @@
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr">
         <is>
-          <t>POLIERG IND COM LT</t>
+          <t>PLASTIREAL INDUSTRIA E COMERCIO DE</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>TUBO PEAD 180x20,1 PN20 PE100 PR ISO 2EX</t>
+          <t>TUBO LISO PEAD PE-100 SDR 9 PN 20 PRETO</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
@@ -15402,7 +15394,7 @@
         </is>
       </c>
       <c r="U103" t="n">
-        <v>300299000</v>
+        <v>300297000</v>
       </c>
       <c r="V103" t="inlineStr"/>
       <c r="W103" t="inlineStr"/>
@@ -15412,7 +15404,7 @@
         </is>
       </c>
       <c r="Y103" t="n">
-        <v>74609.42</v>
+        <v>9800</v>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
@@ -15466,11 +15458,11 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>40894</t>
+          <t>40896</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1393295</v>
+        <v>1381667</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -15483,7 +15475,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>474374</v>
+        <v>50132</v>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
@@ -15508,7 +15500,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>35260653234274000101550010004743741776981518</t>
+          <t>35260673012411000170550010000501321802617296</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -15518,7 +15510,7 @@
       </c>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="n">
-        <v>4101185678</v>
+        <v>4101196551</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
@@ -15531,12 +15523,12 @@
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr">
         <is>
-          <t>PLASTIREAL INDUSTRIA E COMERCIO DE</t>
+          <t>EXIMPORT LUBEQUIP LTDA</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>TUBO LISO PEAD PE-100 SDR 9 PN 20 PRETO</t>
+          <t>TUBO ACO ST-37-2 DIN 2393 Ø16 X 1,5MM ZI</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
@@ -15545,7 +15537,7 @@
         </is>
       </c>
       <c r="U104" t="n">
-        <v>300297000</v>
+        <v>300294000</v>
       </c>
       <c r="V104" t="inlineStr"/>
       <c r="W104" t="inlineStr"/>
@@ -15555,7 +15547,7 @@
         </is>
       </c>
       <c r="Y104" t="n">
-        <v>9800</v>
+        <v>513.98</v>
       </c>
       <c r="Z104" t="inlineStr">
         <is>
@@ -15609,11 +15601,11 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>40895</t>
+          <t>40897</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1392305</v>
+        <v>1407137</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -15626,7 +15618,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>474373</v>
+        <v>35646</v>
       </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
@@ -15651,7 +15643,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>35260653234274000101550010004743731813460906</t>
+          <t>35260615659754000125550010000356461053504526</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -15661,7 +15653,7 @@
       </c>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="n">
-        <v>4101185625</v>
+        <v>4101208477</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
@@ -15674,12 +15666,12 @@
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr">
         <is>
-          <t>PLASTIREAL INDUSTRIA E COMERCIO DE</t>
+          <t>CGM DISTRIBUIDORA DE ACESSORIOS E P</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>TUBO LISO PEAD PE-100 SDR 9 PN 20 PRETO</t>
+          <t>CONTAINER DE LIXO LIXEIRA PLASTICO 1000L</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
@@ -15688,7 +15680,7 @@
         </is>
       </c>
       <c r="U105" t="n">
-        <v>300297000</v>
+        <v>300299000</v>
       </c>
       <c r="V105" t="inlineStr"/>
       <c r="W105" t="inlineStr"/>
@@ -15698,7 +15690,7 @@
         </is>
       </c>
       <c r="Y105" t="n">
-        <v>9800</v>
+        <v>18940</v>
       </c>
       <c r="Z105" t="inlineStr">
         <is>
@@ -15752,31 +15744,21 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>40896</t>
-        </is>
-      </c>
-      <c r="B106" t="n">
-        <v>1381667</v>
-      </c>
+          <t>40918</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>TDV São Paulo - SP</t>
-        </is>
-      </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="n">
-        <v>50132</v>
+        <v>8420</v>
       </c>
       <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>FRACIONADO</t>
-        </is>
-      </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -15794,7 +15776,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>35260673012411000170550010000501321802617296</t>
+          <t>31260344000941000524550010000084201428283759</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -15803,36 +15785,28 @@
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
-      <c r="N106" t="n">
-        <v>4101196551</v>
-      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr">
         <is>
           <t>PARAUAPEBAS</t>
         </is>
       </c>
       <c r="P106" s="1" t="n">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr">
         <is>
-          <t>EXIMPORT LUBEQUIP LTDA</t>
-        </is>
-      </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>TUBO ACO ST-37-2 DIN 2393 Ø16 X 1,5MM ZI</t>
-        </is>
-      </c>
+          <t>HAVER &amp; BOECKER LATINOAMERICANA MAQ</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr"/>
       <c r="T106" t="inlineStr">
         <is>
           <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
-      <c r="U106" t="n">
-        <v>300294000</v>
-      </c>
+      <c r="U106" t="inlineStr"/>
       <c r="V106" t="inlineStr"/>
       <c r="W106" t="inlineStr"/>
       <c r="X106" t="inlineStr">
@@ -15841,7 +15815,7 @@
         </is>
       </c>
       <c r="Y106" t="n">
-        <v>513.98</v>
+        <v>22683.4</v>
       </c>
       <c r="Z106" t="inlineStr">
         <is>
@@ -15854,7 +15828,7 @@
         </is>
       </c>
       <c r="AB106" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
@@ -15863,7 +15837,7 @@
       </c>
       <c r="AD106" t="inlineStr">
         <is>
-          <t>MATERIAL SENDO DEVOLVIDO POR ESTA MAL ACONDICIONADO.</t>
+          <t>MATERIAL RECUSADO, PALETE FORA DO PADR?O, O CORRETO E 1,20X1,20</t>
         </is>
       </c>
       <c r="AE106" t="inlineStr">
@@ -15881,45 +15855,27 @@
           <t>PARAUAPEBAS</t>
         </is>
       </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>VALE S.A.</t>
-        </is>
-      </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>VALE SA</t>
-        </is>
-      </c>
+      <c r="AH106" t="inlineStr"/>
+      <c r="AI106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>40897</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>1407137</v>
-      </c>
+          <t>40928</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>TDV São Paulo - SP</t>
-        </is>
-      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="n">
-        <v>35646</v>
+        <v>8761</v>
       </c>
       <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>FRACIONADO</t>
-        </is>
-      </c>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -15937,7 +15893,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>35260615659754000125550010000356461053504526</t>
+          <t>31260626101667000174550010000087611000029001</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -15946,36 +15902,28 @@
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
-      <c r="N107" t="n">
-        <v>4101208477</v>
-      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
           <t>PARAUAPEBAS</t>
         </is>
       </c>
       <c r="P107" s="1" t="n">
-        <v>46205</v>
+        <v>46212</v>
       </c>
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr">
         <is>
-          <t>CGM DISTRIBUIDORA DE ACESSORIOS E P</t>
-        </is>
-      </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>CONTAINER DE LIXO LIXEIRA PLASTICO 1000L</t>
-        </is>
-      </c>
+          <t>CAMILO NOVIDADES LTDA</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr"/>
       <c r="T107" t="inlineStr">
         <is>
-          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
-        </is>
-      </c>
-      <c r="U107" t="n">
-        <v>300299000</v>
-      </c>
+          <t>MATERIAL DIVERGENTE</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr"/>
       <c r="V107" t="inlineStr"/>
       <c r="W107" t="inlineStr"/>
       <c r="X107" t="inlineStr">
@@ -15984,11 +15932,11 @@
         </is>
       </c>
       <c r="Y107" t="n">
-        <v>18940</v>
+        <v>18480</v>
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>No Prazo</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -15997,16 +15945,16 @@
         </is>
       </c>
       <c r="AB107" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr">
         <is>
-          <t>MATERIAL SENDO DEVOLVIDO POR ESTA MAL ACONDICIONADO.</t>
+          <t>MATERIAL REJEITADO DEVIDO N?O ATENDER SOLICITAC?O DO PEDIDO.</t>
         </is>
       </c>
       <c r="AE107" t="inlineStr">
@@ -16016,7 +15964,7 @@
       </c>
       <c r="AF107" t="inlineStr">
         <is>
-          <t>Acima de 12 Dias</t>
+          <t>9 - 12 Dias</t>
         </is>
       </c>
       <c r="AG107" t="inlineStr">
@@ -16024,21 +15972,13 @@
           <t>PARAUAPEBAS</t>
         </is>
       </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>VALE S.A.</t>
-        </is>
-      </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>VALE SA</t>
-        </is>
-      </c>
+      <c r="AH107" t="inlineStr"/>
+      <c r="AI107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>40918</t>
+          <t>40929</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -16049,7 +15989,7 @@
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="n">
-        <v>8420</v>
+        <v>241771</v>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
@@ -16070,7 +16010,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>31260344000941000524550010000084201428283759</t>
+          <t>31260629799921000490550000002417711974037095</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -16086,12 +16026,12 @@
         </is>
       </c>
       <c r="P108" s="1" t="n">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr">
         <is>
-          <t>HAVER &amp; BOECKER LATINOAMERICANA MAQ</t>
+          <t>ESAB IND E COM LTDA</t>
         </is>
       </c>
       <c r="S108" t="inlineStr"/>
@@ -16109,11 +16049,11 @@
         </is>
       </c>
       <c r="Y108" t="n">
-        <v>22683.4</v>
+        <v>356529.68</v>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>No Prazo</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -16122,16 +16062,16 @@
         </is>
       </c>
       <c r="AB108" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="AD108" t="inlineStr">
         <is>
-          <t>MATERIAL RECUSADO, PALETE FORA DO PADR?O, O CORRETO E 1,20X1,20</t>
+          <t>CARGA DEVOLVIDA DEVIDO, REMESSA SER FATURA E SEM ALINHAMENTO  VALE.</t>
         </is>
       </c>
       <c r="AE108" t="inlineStr">
@@ -16141,7 +16081,7 @@
       </c>
       <c r="AF108" t="inlineStr">
         <is>
-          <t>Acima de 12 Dias</t>
+          <t>9 - 12 Dias</t>
         </is>
       </c>
       <c r="AG108" t="inlineStr">
@@ -16155,7 +16095,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>40928</t>
+          <t>40930</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -16166,7 +16106,7 @@
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="n">
-        <v>8761</v>
+        <v>241677</v>
       </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
@@ -16187,7 +16127,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>31260626101667000174550010000087611000029001</t>
+          <t>31260629799921000490550000002416771937784212</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -16208,13 +16148,13 @@
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr">
         <is>
-          <t>CAMILO NOVIDADES LTDA</t>
+          <t>ESAB IND E COM LTDA</t>
         </is>
       </c>
       <c r="S109" t="inlineStr"/>
       <c r="T109" t="inlineStr">
         <is>
-          <t>MATERIAL DIVERGENTE</t>
+          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
       <c r="U109" t="inlineStr"/>
@@ -16226,7 +16166,7 @@
         </is>
       </c>
       <c r="Y109" t="n">
-        <v>18480</v>
+        <v>369899.55</v>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
@@ -16248,7 +16188,7 @@
       </c>
       <c r="AD109" t="inlineStr">
         <is>
-          <t>MATERIAL REJEITADO DEVIDO N?O ATENDER SOLICITAC?O DO PEDIDO.</t>
+          <t>MATERIAL DEVOLVIDO , DEVIDO ESTAR COM A DATA REMESSA, FATURA SEM ALINHAMENTO VLE.</t>
         </is>
       </c>
       <c r="AE109" t="inlineStr">
@@ -16272,21 +16212,31 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>40929</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr"/>
+          <t>40934</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>1345715</v>
+      </c>
       <c r="C110" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>TDV São Paulo - SP</t>
+        </is>
+      </c>
       <c r="E110" t="n">
-        <v>241771</v>
+        <v>19880</v>
       </c>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>FRACIONADO</t>
+        </is>
+      </c>
       <c r="H110" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -16304,7 +16254,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>31260629799921000490550000002417711974037095</t>
+          <t>35260504483719000181550010000198801014347341</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -16325,25 +16275,35 @@
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr">
         <is>
-          <t>ESAB IND E COM LTDA</t>
-        </is>
-      </c>
-      <c r="S110" t="inlineStr"/>
+          <t>TRILHOS FERROVIARIOS LTDA</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>TRILHOS</t>
+        </is>
+      </c>
       <c r="T110" t="inlineStr">
         <is>
           <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr"/>
-      <c r="V110" t="inlineStr"/>
-      <c r="W110" t="inlineStr"/>
+      <c r="U110" t="n">
+        <v>300286000</v>
+      </c>
+      <c r="V110" t="n">
+        <v>6000176656</v>
+      </c>
+      <c r="W110" s="1" t="n">
+        <v>46182</v>
+      </c>
       <c r="X110" t="inlineStr">
         <is>
           <t>jsconceica</t>
         </is>
       </c>
       <c r="Y110" t="n">
-        <v>356529.68</v>
+        <v>6584.94</v>
       </c>
       <c r="Z110" t="inlineStr">
         <is>
@@ -16360,12 +16320,12 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="AD110" t="inlineStr">
         <is>
-          <t>CARGA DEVOLVIDA DEVIDO, REMESSA SER FATURA E SEM ALINHAMENTO  VALE.</t>
+          <t>DELVOVER AO FORNECEDOR, SEM ESPACO NO ARMAZEM. CLIENTE N?O RESPONDE.</t>
         </is>
       </c>
       <c r="AE110" t="inlineStr">
@@ -16383,27 +16343,45 @@
           <t>PARAUAPEBAS</t>
         </is>
       </c>
-      <c r="AH110" t="inlineStr"/>
-      <c r="AI110" t="inlineStr"/>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>VALE S.A.</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>VALE SA</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>40930</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr"/>
+          <t>40935</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>1373906</v>
+      </c>
       <c r="C111" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>TDV São Paulo - SP</t>
+        </is>
+      </c>
       <c r="E111" t="n">
-        <v>241677</v>
+        <v>832161</v>
       </c>
       <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>FRACIONADO</t>
+        </is>
+      </c>
       <c r="H111" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -16421,7 +16399,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>31260629799921000490550000002416771937784212</t>
+          <t>35260657599581000147550100008321611745969714</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -16430,7 +16408,9 @@
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
+      <c r="N111" t="n">
+        <v>4513157676</v>
+      </c>
       <c r="O111" t="inlineStr">
         <is>
           <t>PARAUAPEBAS</t>
@@ -16442,25 +16422,35 @@
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr">
         <is>
-          <t>ESAB IND E COM LTDA</t>
-        </is>
-      </c>
-      <c r="S111" t="inlineStr"/>
+          <t>A.R.S. - INDUSTRIA E COMERCIO DE PA</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>PORCA SEXT M 16X2 CH 24 ZB-(4513157676)-</t>
+        </is>
+      </c>
       <c r="T111" t="inlineStr">
         <is>
           <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr"/>
-      <c r="V111" t="inlineStr"/>
-      <c r="W111" t="inlineStr"/>
+      <c r="U111" t="n">
+        <v>300292000</v>
+      </c>
+      <c r="V111" t="n">
+        <v>6000177987</v>
+      </c>
+      <c r="W111" s="1" t="n">
+        <v>46184</v>
+      </c>
       <c r="X111" t="inlineStr">
         <is>
           <t>jsconceica</t>
         </is>
       </c>
       <c r="Y111" t="n">
-        <v>369899.55</v>
+        <v>2.09</v>
       </c>
       <c r="Z111" t="inlineStr">
         <is>
@@ -16477,12 +16467,12 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="AD111" t="inlineStr">
         <is>
-          <t>MATERIAL DEVOLVIDO , DEVIDO ESTAR COM A DATA REMESSA, FATURA SEM ALINHAMENTO VLE.</t>
+          <t>SEM CADASTRO.</t>
         </is>
       </c>
       <c r="AE111" t="inlineStr">
@@ -16500,17 +16490,25 @@
           <t>PARAUAPEBAS</t>
         </is>
       </c>
-      <c r="AH111" t="inlineStr"/>
-      <c r="AI111" t="inlineStr"/>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>VALE S.A.</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>VALE SA</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>40934</t>
+          <t>40936</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1345715</v>
+        <v>1373876</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -16523,7 +16521,7 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>19880</v>
+        <v>832157</v>
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
@@ -16548,7 +16546,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>35260504483719000181550010000198801014347341</t>
+          <t>35260657599581000147550100008321571940142103</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -16557,7 +16555,9 @@
         </is>
       </c>
       <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
+      <c r="N112" t="n">
+        <v>4513156502</v>
+      </c>
       <c r="O112" t="inlineStr">
         <is>
           <t>PARAUAPEBAS</t>
@@ -16569,12 +16569,12 @@
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr">
         <is>
-          <t>TRILHOS FERROVIARIOS LTDA</t>
+          <t>A.R.S. - INDUSTRIA E COMERCIO DE PA</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>TRILHOS</t>
+          <t>PA MAQ LENT 1/4-20X3/4 BC-(4513156502)-(</t>
         </is>
       </c>
       <c r="T112" t="inlineStr">
@@ -16583,13 +16583,13 @@
         </is>
       </c>
       <c r="U112" t="n">
-        <v>300286000</v>
+        <v>300292000</v>
       </c>
       <c r="V112" t="n">
-        <v>6000176656</v>
+        <v>6000177987</v>
       </c>
       <c r="W112" s="1" t="n">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="X112" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         </is>
       </c>
       <c r="Y112" t="n">
-        <v>6584.94</v>
+        <v>4.69</v>
       </c>
       <c r="Z112" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
       </c>
       <c r="AD112" t="inlineStr">
         <is>
-          <t>DELVOVER AO FORNECEDOR, SEM ESPACO NO ARMAZEM. CLIENTE N?O RESPONDE.</t>
+          <t>SEM CADASTRO.</t>
         </is>
       </c>
       <c r="AE112" t="inlineStr">
@@ -16651,11 +16651,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>40935</t>
+          <t>40937</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1373906</v>
+        <v>1373877</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -16668,7 +16668,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>832161</v>
+        <v>832439</v>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
@@ -16693,7 +16693,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>35260657599581000147550100008321611745969714</t>
+          <t>35260657599581000147550100008324391399034843</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -16703,7 +16703,7 @@
       </c>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="n">
-        <v>4513157676</v>
+        <v>4513184897</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>PORCA SEXT M 16X2 CH 24 ZB-(4513157676)-</t>
+          <t>PORCA SEXT G.8 3/8-16-(4513184897)-(10)</t>
         </is>
       </c>
       <c r="T113" t="inlineStr">
@@ -16744,7 +16744,7 @@
         </is>
       </c>
       <c r="Y113" t="n">
-        <v>2.09</v>
+        <v>29.82</v>
       </c>
       <c r="Z113" t="inlineStr">
         <is>
@@ -16798,11 +16798,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>40936</t>
+          <t>40938</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1373876</v>
+        <v>1373725</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>832157</v>
+        <v>832250</v>
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>35260657599581000147550100008321571940142103</t>
+          <t>35260657599581000147550100008322501737668575</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -16850,7 +16850,7 @@
       </c>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="n">
-        <v>4513156502</v>
+        <v>4513169468</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
@@ -16868,7 +16868,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>PA MAQ LENT 1/4-20X3/4 BC-(4513156502)-(</t>
+          <t>PA SEXT G.8 5/8-11X1.1/2  RI-(4513169468</t>
         </is>
       </c>
       <c r="T114" t="inlineStr">
@@ -16891,7 +16891,7 @@
         </is>
       </c>
       <c r="Y114" t="n">
-        <v>4.69</v>
+        <v>527.1799999999999</v>
       </c>
       <c r="Z114" t="inlineStr">
         <is>
@@ -16945,11 +16945,11 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>40937</t>
+          <t>40939</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1373877</v>
+        <v>1373833</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>832439</v>
+        <v>832328</v>
       </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
@@ -16987,7 +16987,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>35260657599581000147550100008324391399034843</t>
+          <t>35260657599581000147550100008323281853076349</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -16997,7 +16997,7 @@
       </c>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="n">
-        <v>4513184897</v>
+        <v>4513176053</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>PORCA SEXT G.8 3/8-16-(4513184897)-(10)</t>
+          <t>PORCA SEXT G.5 1/2-13 CH 3/4-(4513176053</t>
         </is>
       </c>
       <c r="T115" t="inlineStr">
@@ -17038,7 +17038,7 @@
         </is>
       </c>
       <c r="Y115" t="n">
-        <v>29.82</v>
+        <v>22.15</v>
       </c>
       <c r="Z115" t="inlineStr">
         <is>
@@ -17092,11 +17092,11 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>40938</t>
+          <t>40940</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>1373725</v>
+        <v>1373872</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>832250</v>
+        <v>832297</v>
       </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
@@ -17134,7 +17134,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>35260657599581000147550100008322501737668575</t>
+          <t>35260657599581000147550100008322971181221624</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -17144,7 +17144,7 @@
       </c>
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="n">
-        <v>4513169468</v>
+        <v>4513176054</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>PA SEXT G.8 5/8-11X1.1/2  RI-(4513169468</t>
+          <t>PA SX G.5 1/2-13X1.1/2 RI ZB-(4513176054</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
@@ -17185,7 +17185,7 @@
         </is>
       </c>
       <c r="Y116" t="n">
-        <v>527.1799999999999</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="Z116" t="inlineStr">
         <is>
@@ -17239,11 +17239,11 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>40939</t>
+          <t>40941</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1373833</v>
+        <v>1373907</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -17256,7 +17256,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>832328</v>
+        <v>832187</v>
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
@@ -17281,7 +17281,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>35260657599581000147550100008323281853076349</t>
+          <t>35260657599581000147550100008321871884435103</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="n">
-        <v>4513176053</v>
+        <v>4513160425</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
@@ -17309,7 +17309,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>PORCA SEXT G.5 1/2-13 CH 3/4-(4513176053</t>
+          <t>ARRUELA LISA DE ACO DIN 125 A M 18-(4513</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
@@ -17332,7 +17332,7 @@
         </is>
       </c>
       <c r="Y117" t="n">
-        <v>22.15</v>
+        <v>11.72</v>
       </c>
       <c r="Z117" t="inlineStr">
         <is>
@@ -17386,31 +17386,21 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>40940</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
-        <v>1373872</v>
-      </c>
+          <t>40942</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>TDV São Paulo - SP</t>
-        </is>
-      </c>
+      <c r="D118" t="inlineStr"/>
       <c r="E118" t="n">
-        <v>832297</v>
+        <v>19878</v>
       </c>
       <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>FRACIONADO</t>
-        </is>
-      </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -17428,7 +17418,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>35260657599581000147550100008322971181221624</t>
+          <t>41260611340390000165550040000198781801155209</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -17437,9 +17427,7 @@
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
-      <c r="N118" t="n">
-        <v>4513176054</v>
-      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr">
         <is>
           <t>PARAUAPEBAS</t>
@@ -17451,35 +17439,25 @@
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr">
         <is>
-          <t>A.R.S. - INDUSTRIA E COMERCIO DE PA</t>
-        </is>
-      </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>PA SX G.5 1/2-13X1.1/2 RI ZB-(4513176054</t>
-        </is>
-      </c>
+          <t>ECOFIBRA INDUSTRIA E COMERCIO DE CO</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr"/>
       <c r="T118" t="inlineStr">
         <is>
           <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
-      <c r="U118" t="n">
-        <v>300292000</v>
-      </c>
-      <c r="V118" t="n">
-        <v>6000177987</v>
-      </c>
-      <c r="W118" s="1" t="n">
-        <v>46184</v>
-      </c>
+      <c r="U118" t="inlineStr"/>
+      <c r="V118" t="inlineStr"/>
+      <c r="W118" t="inlineStr"/>
       <c r="X118" t="inlineStr">
         <is>
           <t>jsconceica</t>
         </is>
       </c>
       <c r="Y118" t="n">
-        <v>76.68000000000001</v>
+        <v>9584.99</v>
       </c>
       <c r="Z118" t="inlineStr">
         <is>
@@ -17496,12 +17474,12 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="AD118" t="inlineStr">
         <is>
-          <t>SEM CADASTRO.</t>
+          <t>DESTINO DIVERGENTE</t>
         </is>
       </c>
       <c r="AE118" t="inlineStr">
@@ -17519,45 +17497,27 @@
           <t>PARAUAPEBAS</t>
         </is>
       </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>VALE S.A.</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>VALE SA</t>
-        </is>
-      </c>
+      <c r="AH118" t="inlineStr"/>
+      <c r="AI118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>40941</t>
-        </is>
-      </c>
-      <c r="B119" t="n">
-        <v>1373907</v>
-      </c>
+          <t>40945</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>TDV São Paulo - SP</t>
-        </is>
-      </c>
+      <c r="D119" t="inlineStr"/>
       <c r="E119" t="n">
-        <v>832187</v>
+        <v>241473</v>
       </c>
       <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>FRACIONADO</t>
-        </is>
-      </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -17575,7 +17535,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>35260657599581000147550100008321871884435103</t>
+          <t>31260629799921000490550000002414731266548790</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -17584,49 +17544,37 @@
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
-      <c r="N119" t="n">
-        <v>4513160425</v>
-      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr">
         <is>
           <t>PARAUAPEBAS</t>
         </is>
       </c>
       <c r="P119" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr">
         <is>
-          <t>A.R.S. - INDUSTRIA E COMERCIO DE PA</t>
-        </is>
-      </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>ARRUELA LISA DE ACO DIN 125 A M 18-(4513</t>
-        </is>
-      </c>
+          <t>ESAB IND E COM LTDA</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr"/>
       <c r="T119" t="inlineStr">
         <is>
           <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
-      <c r="U119" t="n">
-        <v>300292000</v>
-      </c>
-      <c r="V119" t="n">
-        <v>6000177987</v>
-      </c>
-      <c r="W119" s="1" t="n">
-        <v>46184</v>
-      </c>
+      <c r="U119" t="inlineStr"/>
+      <c r="V119" t="inlineStr"/>
+      <c r="W119" t="inlineStr"/>
       <c r="X119" t="inlineStr">
         <is>
           <t>jsconceica</t>
         </is>
       </c>
       <c r="Y119" t="n">
-        <v>11.72</v>
+        <v>267397.26</v>
       </c>
       <c r="Z119" t="inlineStr">
         <is>
@@ -17639,16 +17587,16 @@
         </is>
       </c>
       <c r="AB119" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="AD119" t="inlineStr">
         <is>
-          <t>SEM CADASTRO.</t>
+          <t>RECUSADO DEVIDO A DATA REMESSA SER FUTURA E SEM ALINHAMENTO DA VALE</t>
         </is>
       </c>
       <c r="AE119" t="inlineStr">
@@ -17666,21 +17614,13 @@
           <t>PARAUAPEBAS</t>
         </is>
       </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>VALE S.A.</t>
-        </is>
-      </c>
-      <c r="AI119" t="inlineStr">
-        <is>
-          <t>VALE SA</t>
-        </is>
-      </c>
+      <c r="AH119" t="inlineStr"/>
+      <c r="AI119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>40942</t>
+          <t>40946</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -17691,7 +17631,7 @@
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="n">
-        <v>19878</v>
+        <v>241562</v>
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
@@ -17712,7 +17652,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>41260611340390000165550040000198781801155209</t>
+          <t>31260629799921000490550000002415621553848879</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -17728,12 +17668,12 @@
         </is>
       </c>
       <c r="P120" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr">
         <is>
-          <t>ECOFIBRA INDUSTRIA E COMERCIO DE CO</t>
+          <t>ESAB IND E COM LTDA</t>
         </is>
       </c>
       <c r="S120" t="inlineStr"/>
@@ -17751,7 +17691,7 @@
         </is>
       </c>
       <c r="Y120" t="n">
-        <v>9584.99</v>
+        <v>178264.84</v>
       </c>
       <c r="Z120" t="inlineStr">
         <is>
@@ -17764,7 +17704,7 @@
         </is>
       </c>
       <c r="AB120" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
@@ -17773,7 +17713,7 @@
       </c>
       <c r="AD120" t="inlineStr">
         <is>
-          <t>DESTINO DIVERGENTE</t>
+          <t>RECUSADO DEVIDO A DATA REMESSA SER FUTURA E SEM ALINHAMENTO DA VALE</t>
         </is>
       </c>
       <c r="AE120" t="inlineStr">
@@ -17797,7 +17737,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>40945</t>
+          <t>40977</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -17808,7 +17748,7 @@
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="n">
-        <v>241473</v>
+        <v>857543</v>
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
@@ -17829,7 +17769,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>31260629799921000490550000002414731266548790</t>
+          <t>35260600536772003249550010008575431753933138</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -17845,18 +17785,18 @@
         </is>
       </c>
       <c r="P121" s="1" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr">
         <is>
-          <t>ESAB IND E COM LTDA</t>
+          <t>ECOLAB QUIMICA LTDA</t>
         </is>
       </c>
       <c r="S121" t="inlineStr"/>
       <c r="T121" t="inlineStr">
         <is>
-          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
+          <t>DEVOLUCAO INDEVIDA</t>
         </is>
       </c>
       <c r="U121" t="inlineStr"/>
@@ -17864,11 +17804,11 @@
       <c r="W121" t="inlineStr"/>
       <c r="X121" t="inlineStr">
         <is>
-          <t>jsconceica</t>
+          <t>erisoares</t>
         </is>
       </c>
       <c r="Y121" t="n">
-        <v>267397.26</v>
+        <v>215462.1</v>
       </c>
       <c r="Z121" t="inlineStr">
         <is>
@@ -17881,16 +17821,16 @@
         </is>
       </c>
       <c r="AB121" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="AD121" t="inlineStr">
         <is>
-          <t>RECUSADO DEVIDO A DATA REMESSA SER FUTURA E SEM ALINHAMENTO DA VALE</t>
+          <t>MATERIAL DEVOLVIDO DEVIDO O CLIENTE ESTA SEM EQUIPAMENTO PRA DESCARREGAR, FAZER ALINHAMENTO COM CLIENTE E AREA.</t>
         </is>
       </c>
       <c r="AE121" t="inlineStr">
@@ -17900,7 +17840,7 @@
       </c>
       <c r="AF121" t="inlineStr">
         <is>
-          <t>9 - 12 Dias</t>
+          <t>0 - 8 Dias</t>
         </is>
       </c>
       <c r="AG121" t="inlineStr">
@@ -17914,21 +17854,31 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>40946</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr"/>
+          <t>40219</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1194154</v>
+      </c>
       <c r="C122" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>TDV Contagem MG</t>
+        </is>
+      </c>
       <c r="E122" t="n">
-        <v>241562</v>
+        <v>2593</v>
       </c>
       <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>FRACIONADO</t>
+        </is>
+      </c>
       <c r="H122" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -17936,17 +17886,17 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Parauapebas - PA</t>
+          <t>São Luíz - MA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>PARAUAPEBAS</t>
+          <t>SAO LUIS</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>31260629799921000490550000002415621553848879</t>
+          <t>31260415801747000116550030000025931705512966</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -17955,41 +17905,53 @@
         </is>
       </c>
       <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
+      <c r="N122" t="n">
+        <v>4101104740</v>
+      </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>PARAUAPEBAS</t>
+          <t>SAO LUIS</t>
         </is>
       </c>
       <c r="P122" s="1" t="n">
-        <v>46213</v>
+        <v>46136</v>
       </c>
       <c r="Q122" t="inlineStr"/>
       <c r="R122" t="inlineStr">
         <is>
-          <t>ESAB IND E COM LTDA</t>
-        </is>
-      </c>
-      <c r="S122" t="inlineStr"/>
+          <t>SEVEN SUPRIMENTOS INDUSTRIAIS LTDA</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>MANGUEIRA  P/COMPRESSOR PARAGUSO</t>
+        </is>
+      </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
-        </is>
-      </c>
-      <c r="U122" t="inlineStr"/>
-      <c r="V122" t="inlineStr"/>
-      <c r="W122" t="inlineStr"/>
+          <t>NOTA FISCAL DIVERGENTE</t>
+        </is>
+      </c>
+      <c r="U122" t="n">
+        <v>300254000</v>
+      </c>
+      <c r="V122" t="n">
+        <v>6000153276</v>
+      </c>
+      <c r="W122" s="1" t="n">
+        <v>46122</v>
+      </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>jsconceica</t>
+          <t>dluz</t>
         </is>
       </c>
       <c r="Y122" t="n">
-        <v>178264.84</v>
+        <v>702.84</v>
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>No Prazo</t>
+          <t>Atrasado</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -17998,7 +17960,7 @@
         </is>
       </c>
       <c r="AB122" t="n">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="AC122" t="inlineStr">
         <is>
@@ -18007,45 +17969,63 @@
       </c>
       <c r="AD122" t="inlineStr">
         <is>
-          <t>RECUSADO DEVIDO A DATA REMESSA SER FUTURA E SEM ALINHAMENTO DA VALE</t>
+          <t>NF CONSTA DIVERGENCIA (INAPTA),NECESSARIO REGULARIZACAO DO XML. O FORNECEDOR DEVERA ABRIR CHAMADO NA FERRAMENTA V360</t>
         </is>
       </c>
       <c r="AE122" t="inlineStr">
         <is>
-          <t>IPATINGA/MG</t>
+          <t>SAO LUIS</t>
         </is>
       </c>
       <c r="AF122" t="inlineStr">
         <is>
-          <t>9 - 12 Dias</t>
+          <t>Acima de 12 Dias</t>
         </is>
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>PARAUAPEBAS</t>
-        </is>
-      </c>
-      <c r="AH122" t="inlineStr"/>
-      <c r="AI122" t="inlineStr"/>
+          <t>SAO LUIS</t>
+        </is>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>VALE S A</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>SEVEN SUPRIMENTOS INDUSTRIAIS LTDA</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>40977</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr"/>
+          <t>40547</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>392391</v>
+      </c>
       <c r="C123" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>TDV São Luiz - MA</t>
+        </is>
+      </c>
       <c r="E123" t="n">
-        <v>857543</v>
+        <v>33540</v>
       </c>
       <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>FRACIONADO</t>
+        </is>
+      </c>
       <c r="H123" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -18053,17 +18033,17 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Parauapebas - PA</t>
+          <t>São Luíz - MA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>PARAUAPEBAS</t>
+          <t>SAO LUIS</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>35260600536772003249550010008575431753933138</t>
+          <t>35250500017952000118550010000335401611802796</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -18072,25 +18052,31 @@
         </is>
       </c>
       <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
+      <c r="N123" t="n">
+        <v>4100989446</v>
+      </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>PARAUAPEBAS</t>
+          <t>SAO LUIS</t>
         </is>
       </c>
       <c r="P123" s="1" t="n">
-        <v>46217</v>
+        <v>46171</v>
       </c>
       <c r="Q123" t="inlineStr"/>
       <c r="R123" t="inlineStr">
         <is>
-          <t>ECOLAB QUIMICA LTDA</t>
-        </is>
-      </c>
-      <c r="S123" t="inlineStr"/>
+          <t>MOLYGRAFIT INDUSTRIA E COMERCIO LTD</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>SERVIÇO DE TRANSPORTE</t>
+        </is>
+      </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>DEVOLUCAO INDEVIDA</t>
+          <t>NOTA FISCAL DIVERGENTE</t>
         </is>
       </c>
       <c r="U123" t="inlineStr"/>
@@ -18098,15 +18084,15 @@
       <c r="W123" t="inlineStr"/>
       <c r="X123" t="inlineStr">
         <is>
-          <t>erisoares</t>
+          <t>dluz</t>
         </is>
       </c>
       <c r="Y123" t="n">
-        <v>215462.1</v>
+        <v>1029.23</v>
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>No Prazo</t>
+          <t>Atrasado</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -18115,44 +18101,52 @@
         </is>
       </c>
       <c r="AB123" t="n">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="AD123" t="inlineStr">
         <is>
-          <t>MATERIAL DEVOLVIDO DEVIDO O CLIENTE ESTA SEM EQUIPAMENTO PRA DESCARREGAR, FAZER ALINHAMENTO COM CLIENTE E AREA.</t>
+          <t>FIZEMOS A TENTATIVA DE REENTREGA COM MESMA NF , JUNTO DA NF COMPLEMENTAR (33689) FONFORME TRATATIVAS , POREM NOTA CONTINUA INAPTA.</t>
         </is>
       </c>
       <c r="AE123" t="inlineStr">
         <is>
-          <t>IPATINGA/MG</t>
+          <t>SAO LUIS</t>
         </is>
       </c>
       <c r="AF123" t="inlineStr">
         <is>
-          <t>0 - 8 Dias</t>
+          <t>Acima de 12 Dias</t>
         </is>
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>PARAUAPEBAS</t>
-        </is>
-      </c>
-      <c r="AH123" t="inlineStr"/>
-      <c r="AI123" t="inlineStr"/>
+          <t>SAO LUIS</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>VALE S A</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>MOLYGRAFIT INDUSTRIA E COMERCIO LTD</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>40219</t>
+          <t>40810</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1194154</v>
+        <v>1365998</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -18165,7 +18159,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2593</v>
+        <v>8466</v>
       </c>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
@@ -18190,7 +18184,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>31260415801747000116550030000025931705512966</t>
+          <t>31260343711951000505550010000084661325509470</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -18199,49 +18193,47 @@
         </is>
       </c>
       <c r="M124" t="inlineStr"/>
-      <c r="N124" t="n">
-        <v>4101104740</v>
-      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr">
         <is>
           <t>SAO LUIS</t>
         </is>
       </c>
       <c r="P124" s="1" t="n">
-        <v>46136</v>
+        <v>46196</v>
       </c>
       <c r="Q124" t="inlineStr"/>
       <c r="R124" t="inlineStr">
         <is>
-          <t>SEVEN SUPRIMENTOS INDUSTRIAIS LTDA</t>
+          <t>FLSMIDTH INDUSTRIAL SOLUTIONS LTDA</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>MANGUEIRA  P/COMPRESSOR PARAGUSO</t>
+          <t>PARTES</t>
         </is>
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>NOTA FISCAL DIVERGENTE</t>
+          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
       <c r="U124" t="n">
-        <v>300254000</v>
+        <v>300292000</v>
       </c>
       <c r="V124" t="n">
-        <v>6000153276</v>
+        <v>6000181717</v>
       </c>
       <c r="W124" s="1" t="n">
-        <v>46122</v>
+        <v>46195</v>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>dluz</t>
+          <t>proliveira</t>
         </is>
       </c>
       <c r="Y124" t="n">
-        <v>702.84</v>
+        <v>1281886.36</v>
       </c>
       <c r="Z124" t="inlineStr">
         <is>
@@ -18254,7 +18246,7 @@
         </is>
       </c>
       <c r="AB124" t="n">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
@@ -18263,7 +18255,7 @@
       </c>
       <c r="AD124" t="inlineStr">
         <is>
-          <t>NF CONSTA DIVERGENCIA (INAPTA),NECESSARIO REGULARIZACAO DO XML. O FORNECEDOR DEVERA ABRIR CHAMADO NA FERRAMENTA V360</t>
+          <t>O FORNECEDOR DEVERA ABRIR CHAMADO NA FERRAMENTA V360</t>
         </is>
       </c>
       <c r="AE124" t="inlineStr">
@@ -18283,23 +18275,23 @@
       </c>
       <c r="AH124" t="inlineStr">
         <is>
-          <t>VALE S A</t>
+          <t>VALE SA</t>
         </is>
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>SEVEN SUPRIMENTOS INDUSTRIAIS LTDA</t>
+          <t>VALE SA</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>40547</t>
+          <t>40811</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>392391</v>
+        <v>1328744</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -18308,16 +18300,16 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>TDV São Luiz - MA</t>
+          <t>TDV Fortaleza - CE</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>33540</v>
+        <v>27357</v>
       </c>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>FRACIONADO</t>
+          <t>LOTACAO</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -18337,7 +18329,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>35250500017952000118550010000335401611802796</t>
+          <t>21260633592510037821550030000273571654701090</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -18347,7 +18339,7 @@
       </c>
       <c r="M125" t="inlineStr"/>
       <c r="N125" t="n">
-        <v>4100989446</v>
+        <v>4512553116</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
@@ -18355,34 +18347,36 @@
         </is>
       </c>
       <c r="P125" s="1" t="n">
-        <v>46171</v>
+        <v>46196</v>
       </c>
       <c r="Q125" t="inlineStr"/>
-      <c r="R125" t="inlineStr">
-        <is>
-          <t>MOLYGRAFIT INDUSTRIA E COMERCIO LTD</t>
-        </is>
-      </c>
+      <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr">
         <is>
-          <t>SERVIÇO DE TRANSPORTE</t>
+          <t>RODA FERVRIA 42POL 252,1MM</t>
         </is>
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>NOTA FISCAL DIVERGENTE</t>
-        </is>
-      </c>
-      <c r="U125" t="inlineStr"/>
-      <c r="V125" t="inlineStr"/>
-      <c r="W125" t="inlineStr"/>
+          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
+        </is>
+      </c>
+      <c r="U125" t="n">
+        <v>300297000</v>
+      </c>
+      <c r="V125" t="n">
+        <v>6000180276</v>
+      </c>
+      <c r="W125" s="1" t="n">
+        <v>46190</v>
+      </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>dluz</t>
+          <t>proliveira</t>
         </is>
       </c>
       <c r="Y125" t="n">
-        <v>1029.23</v>
+        <v>318009.11</v>
       </c>
       <c r="Z125" t="inlineStr">
         <is>
@@ -18395,16 +18389,16 @@
         </is>
       </c>
       <c r="AB125" t="n">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="AD125" t="inlineStr">
         <is>
-          <t>FIZEMOS A TENTATIVA DE REENTREGA COM MESMA NF , JUNTO DA NF COMPLEMENTAR (33689) FONFORME TRATATIVAS , POREM NOTA CONTINUA INAPTA.</t>
+          <t>RECUSADO DEVIDO A INCAPACIDADE PARA DESCARGA DO MATERIAL DE FORMA SEGURA. MATERIL CARREGADO SEM ESTAR PALETIZADO, DIRETAMENTE NO ASSOALHO DO VEICULO.</t>
         </is>
       </c>
       <c r="AE125" t="inlineStr">
@@ -18429,18 +18423,18 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>MOLYGRAFIT INDUSTRIA E COMERCIO LTD</t>
+          <t>VALE SA</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>40810</t>
+          <t>40828</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>1365998</v>
+        <v>1328772</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -18449,16 +18443,16 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>TDV Contagem MG</t>
+          <t>TDV Fortaleza - CE</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>8466</v>
+        <v>27356</v>
       </c>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>FRACIONADO</t>
+          <t>LOTACAO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -18478,7 +18472,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>31260343711951000505550010000084661325509470</t>
+          <t>21260633592510037821550030000273561817592450</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -18487,24 +18481,22 @@
         </is>
       </c>
       <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
+      <c r="N126" t="n">
+        <v>4512553116</v>
+      </c>
       <c r="O126" t="inlineStr">
         <is>
           <t>SAO LUIS</t>
         </is>
       </c>
       <c r="P126" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="Q126" t="inlineStr"/>
-      <c r="R126" t="inlineStr">
-        <is>
-          <t>FLSMIDTH INDUSTRIAL SOLUTIONS LTDA</t>
-        </is>
-      </c>
+      <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr">
         <is>
-          <t>PARTES</t>
+          <t>RODA FERVRIA 42POL 252,1MM</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
@@ -18516,10 +18508,10 @@
         <v>300292000</v>
       </c>
       <c r="V126" t="n">
-        <v>6000181717</v>
+        <v>6000177916</v>
       </c>
       <c r="W126" s="1" t="n">
-        <v>46195</v>
+        <v>46184</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
@@ -18527,7 +18519,7 @@
         </is>
       </c>
       <c r="Y126" t="n">
-        <v>1281886.36</v>
+        <v>289099.19</v>
       </c>
       <c r="Z126" t="inlineStr">
         <is>
@@ -18540,16 +18532,16 @@
         </is>
       </c>
       <c r="AB126" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="AD126" t="inlineStr">
         <is>
-          <t>O FORNECEDOR DEVERA ABRIR CHAMADO NA FERRAMENTA V360</t>
+          <t>RECUSADO DEVIDO A INCAPACIDADE DO MATERIAL PARA DESCARREGAR COM EMPILHADEIRA</t>
         </is>
       </c>
       <c r="AE126" t="inlineStr">
@@ -18569,7 +18561,7 @@
       </c>
       <c r="AH126" t="inlineStr">
         <is>
-          <t>VALE SA</t>
+          <t>VALE S A</t>
         </is>
       </c>
       <c r="AI126" t="inlineStr">
@@ -18581,11 +18573,11 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>40811</t>
+          <t>40829</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1328744</v>
+        <v>1328771</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -18598,7 +18590,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>27357</v>
+        <v>27355</v>
       </c>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
@@ -18623,7 +18615,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>21260633592510037821550030000273571654701090</t>
+          <t>21260633592510037821550030000273551780304343</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -18641,7 +18633,7 @@
         </is>
       </c>
       <c r="P127" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="Q127" t="inlineStr"/>
       <c r="R127" t="inlineStr"/>
@@ -18656,13 +18648,13 @@
         </is>
       </c>
       <c r="U127" t="n">
-        <v>300297000</v>
+        <v>300292000</v>
       </c>
       <c r="V127" t="n">
-        <v>6000180276</v>
+        <v>6000177916</v>
       </c>
       <c r="W127" s="1" t="n">
-        <v>46190</v>
+        <v>46184</v>
       </c>
       <c r="X127" t="inlineStr">
         <is>
@@ -18683,7 +18675,7 @@
         </is>
       </c>
       <c r="AB127" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AC127" t="inlineStr">
         <is>
@@ -18692,7 +18684,7 @@
       </c>
       <c r="AD127" t="inlineStr">
         <is>
-          <t>RECUSADO DEVIDO A INCAPACIDADE PARA DESCARGA DO MATERIAL DE FORMA SEGURA. MATERIL CARREGADO SEM ESTAR PALETIZADO, DIRETAMENTE NO ASSOALHO DO VEICULO.</t>
+          <t>RECUSADO DEVIDO A INCAPACIDADE DO MATERIAL PARA DESCARREGAR COM EMPILHADEIRA</t>
         </is>
       </c>
       <c r="AE127" t="inlineStr">
@@ -18724,11 +18716,11 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>40828</t>
+          <t>40835</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1328772</v>
+        <v>1331164</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -18737,16 +18729,16 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>TDV Fortaleza - CE</t>
+          <t>TDV Serra- ES</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>27356</v>
+        <v>24102</v>
       </c>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>LOTACAO</t>
+          <t>FRACIONADO</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -18766,7 +18758,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>21260633592510037821550030000273561817592450</t>
+          <t>32260501595865000100550010000241021803691646</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -18775,9 +18767,7 @@
         </is>
       </c>
       <c r="M128" t="inlineStr"/>
-      <c r="N128" t="n">
-        <v>4512553116</v>
-      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr">
         <is>
           <t>SAO LUIS</t>
@@ -18787,10 +18777,14 @@
         <v>46197</v>
       </c>
       <c r="Q128" t="inlineStr"/>
-      <c r="R128" t="inlineStr"/>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>CSV LTDA</t>
+        </is>
+      </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>RODA FERVRIA 42POL 252,1MM</t>
+          <t>BTN003</t>
         </is>
       </c>
       <c r="T128" t="inlineStr">
@@ -18799,10 +18793,10 @@
         </is>
       </c>
       <c r="U128" t="n">
-        <v>300292000</v>
+        <v>300289000</v>
       </c>
       <c r="V128" t="n">
-        <v>6000177916</v>
+        <v>6000178002</v>
       </c>
       <c r="W128" s="1" t="n">
         <v>46184</v>
@@ -18813,7 +18807,7 @@
         </is>
       </c>
       <c r="Y128" t="n">
-        <v>289099.19</v>
+        <v>46150</v>
       </c>
       <c r="Z128" t="inlineStr">
         <is>
@@ -18835,7 +18829,7 @@
       </c>
       <c r="AD128" t="inlineStr">
         <is>
-          <t>RECUSADO DEVIDO A INCAPACIDADE DO MATERIAL PARA DESCARREGAR COM EMPILHADEIRA</t>
+          <t>NAO RECEBIDO POR FALTA DA EQUIPE NO LOCAL PARA REALIZAR O DESCARREGAMENTO</t>
         </is>
       </c>
       <c r="AE128" t="inlineStr">
@@ -18867,31 +18861,21 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>40829</t>
-        </is>
-      </c>
-      <c r="B129" t="n">
-        <v>1328771</v>
-      </c>
+          <t>41002</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
           <t>Devolução</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>TDV Fortaleza - CE</t>
-        </is>
-      </c>
+      <c r="D129" t="inlineStr"/>
       <c r="E129" t="n">
-        <v>27355</v>
+        <v>65592</v>
       </c>
       <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>LOTACAO</t>
-        </is>
-      </c>
+      <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
           <t>PENDENTE</t>
@@ -18909,7 +18893,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>21260633592510037821550030000273551780304343</t>
+          <t>35260759511741000180550010000655921682706407</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -18918,49 +18902,41 @@
         </is>
       </c>
       <c r="M129" t="inlineStr"/>
-      <c r="N129" t="n">
-        <v>4512553116</v>
-      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr">
         <is>
           <t>SAO LUIS</t>
         </is>
       </c>
       <c r="P129" s="1" t="n">
-        <v>46197</v>
+        <v>46223</v>
       </c>
       <c r="Q129" t="inlineStr"/>
-      <c r="R129" t="inlineStr"/>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>RODA FERVRIA 42POL 252,1MM</t>
-        </is>
-      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>ARGA FACIL DE DESCALVADO LTDA</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr"/>
       <c r="T129" t="inlineStr">
         <is>
           <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
         </is>
       </c>
-      <c r="U129" t="n">
-        <v>300292000</v>
-      </c>
-      <c r="V129" t="n">
-        <v>6000177916</v>
-      </c>
-      <c r="W129" s="1" t="n">
-        <v>46184</v>
-      </c>
+      <c r="U129" t="inlineStr"/>
+      <c r="V129" t="inlineStr"/>
+      <c r="W129" t="inlineStr"/>
       <c r="X129" t="inlineStr">
         <is>
           <t>proliveira</t>
         </is>
       </c>
       <c r="Y129" t="n">
-        <v>318009.11</v>
+        <v>5775</v>
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>No Prazo</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -18969,7 +18945,7 @@
         </is>
       </c>
       <c r="AB129" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="AC129" t="inlineStr">
         <is>
@@ -18978,7 +18954,7 @@
       </c>
       <c r="AD129" t="inlineStr">
         <is>
-          <t>RECUSADO DEVIDO A INCAPACIDADE DO MATERIAL PARA DESCARREGAR COM EMPILHADEIRA</t>
+          <t>NF DEVOLVIDA DEVIDO O MATERIAL NAO ESTA PALETIZADO</t>
         </is>
       </c>
       <c r="AE129" t="inlineStr">
@@ -18988,7 +18964,7 @@
       </c>
       <c r="AF129" t="inlineStr">
         <is>
-          <t>Acima de 12 Dias</t>
+          <t>0 - 8 Dias</t>
         </is>
       </c>
       <c r="AG129" t="inlineStr">
@@ -18996,278 +18972,8 @@
           <t>SAO LUIS</t>
         </is>
       </c>
-      <c r="AH129" t="inlineStr">
-        <is>
-          <t>VALE S A</t>
-        </is>
-      </c>
-      <c r="AI129" t="inlineStr">
-        <is>
-          <t>VALE SA</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>40835</t>
-        </is>
-      </c>
-      <c r="B130" t="n">
-        <v>1331164</v>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Devolução</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>TDV Serra- ES</t>
-        </is>
-      </c>
-      <c r="E130" t="n">
-        <v>24102</v>
-      </c>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>FRACIONADO</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>São Luíz - MA</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>SAO LUIS</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>32260501595865000100550010000241021803691646</t>
-        </is>
-      </c>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t>VALE</t>
-        </is>
-      </c>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr">
-        <is>
-          <t>SAO LUIS</t>
-        </is>
-      </c>
-      <c r="P130" s="1" t="n">
-        <v>46197</v>
-      </c>
-      <c r="Q130" t="inlineStr"/>
-      <c r="R130" t="inlineStr">
-        <is>
-          <t>CSV LTDA</t>
-        </is>
-      </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>BTN003</t>
-        </is>
-      </c>
-      <c r="T130" t="inlineStr">
-        <is>
-          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
-        </is>
-      </c>
-      <c r="U130" t="n">
-        <v>300289000</v>
-      </c>
-      <c r="V130" t="n">
-        <v>6000178002</v>
-      </c>
-      <c r="W130" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="X130" t="inlineStr">
-        <is>
-          <t>proliveira</t>
-        </is>
-      </c>
-      <c r="Y130" t="n">
-        <v>46150</v>
-      </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>Atrasado</t>
-        </is>
-      </c>
-      <c r="AA130" t="inlineStr">
-        <is>
-          <t>Em Aberto</t>
-        </is>
-      </c>
-      <c r="AB130" t="n">
-        <v>27</v>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="AD130" t="inlineStr">
-        <is>
-          <t>NAO RECEBIDO POR FALTA DA EQUIPE NO LOCAL PARA REALIZAR O DESCARREGAMENTO</t>
-        </is>
-      </c>
-      <c r="AE130" t="inlineStr">
-        <is>
-          <t>SAO LUIS</t>
-        </is>
-      </c>
-      <c r="AF130" t="inlineStr">
-        <is>
-          <t>Acima de 12 Dias</t>
-        </is>
-      </c>
-      <c r="AG130" t="inlineStr">
-        <is>
-          <t>SAO LUIS</t>
-        </is>
-      </c>
-      <c r="AH130" t="inlineStr">
-        <is>
-          <t>VALE S A</t>
-        </is>
-      </c>
-      <c r="AI130" t="inlineStr">
-        <is>
-          <t>VALE SA</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>41002</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr"/>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Devolução</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" t="n">
-        <v>65592</v>
-      </c>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>São Luíz - MA</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>SAO LUIS</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>35260759511741000180550010000655921682706407</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t>VALE</t>
-        </is>
-      </c>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr">
-        <is>
-          <t>SAO LUIS</t>
-        </is>
-      </c>
-      <c r="P131" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="Q131" t="inlineStr"/>
-      <c r="R131" t="inlineStr">
-        <is>
-          <t>ARGA FACIL DE DESCALVADO LTDA</t>
-        </is>
-      </c>
-      <c r="S131" t="inlineStr"/>
-      <c r="T131" t="inlineStr">
-        <is>
-          <t>SEM AUTORIZACAO DE RECEBIMENTO</t>
-        </is>
-      </c>
-      <c r="U131" t="inlineStr"/>
-      <c r="V131" t="inlineStr"/>
-      <c r="W131" t="inlineStr"/>
-      <c r="X131" t="inlineStr">
-        <is>
-          <t>proliveira</t>
-        </is>
-      </c>
-      <c r="Y131" t="n">
-        <v>5775</v>
-      </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>No Prazo</t>
-        </is>
-      </c>
-      <c r="AA131" t="inlineStr">
-        <is>
-          <t>Em Aberto</t>
-        </is>
-      </c>
-      <c r="AB131" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="AD131" t="inlineStr">
-        <is>
-          <t>NF DEVOLVIDA DEVIDO O MATERIAL NAO ESTA PALETIZADO</t>
-        </is>
-      </c>
-      <c r="AE131" t="inlineStr">
-        <is>
-          <t>SAO LUIS</t>
-        </is>
-      </c>
-      <c r="AF131" t="inlineStr">
-        <is>
-          <t>0 - 8 Dias</t>
-        </is>
-      </c>
-      <c r="AG131" t="inlineStr">
-        <is>
-          <t>SAO LUIS</t>
-        </is>
-      </c>
-      <c r="AH131" t="inlineStr"/>
-      <c r="AI131" t="inlineStr"/>
+      <c r="AH129" t="inlineStr"/>
+      <c r="AI129" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
